--- a/Tabela com codigos operativos.xlsx
+++ b/Tabela com codigos operativos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Engeselt\Documents\GitHub\ASPO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{588A4B28-70D1-4C76-93DC-8123D2487687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EF6D4C1-9033-4700-9D97-44947FE30D7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21701,51 +21701,27 @@
     <t>124TR01-EAE</t>
   </si>
   <si>
-    <t>SE CN PARECIS TR-01 13,8KV-EAE</t>
-  </si>
-  <si>
     <t>124TR01-EAR</t>
   </si>
   <si>
-    <t>SE CN PARECIS TR-01 13,8KV-EAR</t>
-  </si>
-  <si>
     <t>124TR01-ERE</t>
   </si>
   <si>
-    <t>SE CN PARECIS TR-01 13,8KV-ERE</t>
-  </si>
-  <si>
     <t>124TR01-ERR</t>
   </si>
   <si>
-    <t>SE CN PARECIS TR-01 13,8KV-ERR</t>
-  </si>
-  <si>
     <t>124TR02-EAE</t>
   </si>
   <si>
-    <t>SE CN PARECIS TR-02 34.5KV-EAE</t>
-  </si>
-  <si>
     <t>124TR02-EAR</t>
   </si>
   <si>
-    <t>SE CN PARECIS TR-02 34.5KV-EAR</t>
-  </si>
-  <si>
     <t>124TR02-ERE</t>
   </si>
   <si>
-    <t>SE CN PARECIS TR-02 34.5KV-ERE</t>
-  </si>
-  <si>
     <t>124TR02-ERR</t>
   </si>
   <si>
-    <t>SE CN PARECIS TR-02 34.5KV-ERR</t>
-  </si>
-  <si>
     <t>027001-EAE</t>
   </si>
   <si>
@@ -26424,6 +26400,30 @@
   </si>
   <si>
     <t>224011-ERR</t>
+  </si>
+  <si>
+    <t>SE CN PARECIS TR-01 34.5KV-EAE</t>
+  </si>
+  <si>
+    <t>SE CN PARECIS TR-01 34.5KV-EAR</t>
+  </si>
+  <si>
+    <t>SE CN PARECIS TR-01 34.5KV-ERE</t>
+  </si>
+  <si>
+    <t>SE CN PARECIS TR-01 34.5KV-ERR</t>
+  </si>
+  <si>
+    <t>SE CN PARECIS TR-02 13.8KV-EAE</t>
+  </si>
+  <si>
+    <t>SE CN PARECIS TR-02 13.8KV-EAR</t>
+  </si>
+  <si>
+    <t>SE CN PARECIS TR-02 13.8KV-ERE</t>
+  </si>
+  <si>
+    <t>SE CN PARECIS TR-02 13.8KV-ERR</t>
   </si>
 </sst>
 </file>
@@ -57332,1535 +57332,1535 @@
         <v>7220</v>
       </c>
       <c r="B3758" t="s">
-        <v>7221</v>
+        <v>8788</v>
       </c>
     </row>
     <row r="3759" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3759" t="s">
-        <v>7222</v>
+        <v>7221</v>
       </c>
       <c r="B3759" t="s">
-        <v>7223</v>
+        <v>8789</v>
       </c>
     </row>
     <row r="3760" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3760" t="s">
-        <v>7224</v>
+        <v>7222</v>
       </c>
       <c r="B3760" t="s">
-        <v>7225</v>
+        <v>8790</v>
       </c>
     </row>
     <row r="3761" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3761" t="s">
-        <v>7226</v>
+        <v>7223</v>
       </c>
       <c r="B3761" t="s">
-        <v>7227</v>
+        <v>8791</v>
       </c>
     </row>
     <row r="3762" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3762" t="s">
-        <v>7228</v>
+        <v>7224</v>
       </c>
       <c r="B3762" t="s">
-        <v>7229</v>
+        <v>8792</v>
       </c>
     </row>
     <row r="3763" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3763" t="s">
-        <v>7230</v>
+        <v>7225</v>
       </c>
       <c r="B3763" t="s">
-        <v>7231</v>
+        <v>8793</v>
       </c>
     </row>
     <row r="3764" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3764" t="s">
-        <v>7232</v>
+        <v>7226</v>
       </c>
       <c r="B3764" t="s">
-        <v>7233</v>
+        <v>8794</v>
       </c>
     </row>
     <row r="3765" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3765" t="s">
-        <v>7234</v>
+        <v>7227</v>
       </c>
       <c r="B3765" t="s">
-        <v>7235</v>
+        <v>8795</v>
       </c>
     </row>
     <row r="3766" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3766" t="s">
-        <v>7236</v>
+        <v>7228</v>
       </c>
       <c r="B3766" t="s">
-        <v>7237</v>
+        <v>7229</v>
       </c>
     </row>
     <row r="3767" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3767" t="s">
-        <v>7238</v>
+        <v>7230</v>
       </c>
       <c r="B3767" t="s">
-        <v>7239</v>
+        <v>7231</v>
       </c>
     </row>
     <row r="3768" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3768" t="s">
-        <v>7240</v>
+        <v>7232</v>
       </c>
       <c r="B3768" t="s">
-        <v>7241</v>
+        <v>7233</v>
       </c>
     </row>
     <row r="3769" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3769" t="s">
-        <v>7242</v>
+        <v>7234</v>
       </c>
       <c r="B3769" t="s">
-        <v>7243</v>
+        <v>7235</v>
       </c>
     </row>
     <row r="3770" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3770" t="s">
-        <v>7244</v>
+        <v>7236</v>
       </c>
       <c r="B3770" t="s">
-        <v>7245</v>
+        <v>7237</v>
       </c>
     </row>
     <row r="3771" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3771" t="s">
-        <v>7246</v>
+        <v>7238</v>
       </c>
       <c r="B3771" t="s">
-        <v>7247</v>
+        <v>7239</v>
       </c>
     </row>
     <row r="3772" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3772" t="s">
-        <v>7248</v>
+        <v>7240</v>
       </c>
       <c r="B3772" t="s">
-        <v>7249</v>
+        <v>7241</v>
       </c>
     </row>
     <row r="3773" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3773" t="s">
-        <v>7250</v>
+        <v>7242</v>
       </c>
       <c r="B3773" t="s">
-        <v>7251</v>
+        <v>7243</v>
       </c>
     </row>
     <row r="3774" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3774" t="s">
-        <v>7252</v>
+        <v>7244</v>
       </c>
       <c r="B3774" t="s">
-        <v>7253</v>
+        <v>7245</v>
       </c>
     </row>
     <row r="3775" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3775" t="s">
-        <v>7254</v>
+        <v>7246</v>
       </c>
       <c r="B3775" t="s">
-        <v>7255</v>
+        <v>7247</v>
       </c>
     </row>
     <row r="3776" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3776" t="s">
-        <v>7256</v>
+        <v>7248</v>
       </c>
       <c r="B3776" t="s">
-        <v>7257</v>
+        <v>7249</v>
       </c>
     </row>
     <row r="3777" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3777" t="s">
-        <v>7258</v>
+        <v>7250</v>
       </c>
       <c r="B3777" t="s">
-        <v>7259</v>
+        <v>7251</v>
       </c>
     </row>
     <row r="3778" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3778" t="s">
-        <v>7260</v>
+        <v>7252</v>
       </c>
       <c r="B3778" t="s">
-        <v>7261</v>
+        <v>7253</v>
       </c>
     </row>
     <row r="3779" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3779" t="s">
-        <v>7262</v>
+        <v>7254</v>
       </c>
       <c r="B3779" t="s">
-        <v>7263</v>
+        <v>7255</v>
       </c>
     </row>
     <row r="3780" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3780" t="s">
-        <v>7264</v>
+        <v>7256</v>
       </c>
       <c r="B3780" t="s">
-        <v>7265</v>
+        <v>7257</v>
       </c>
     </row>
     <row r="3781" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3781" t="s">
-        <v>7266</v>
+        <v>7258</v>
       </c>
       <c r="B3781" t="s">
-        <v>7267</v>
+        <v>7259</v>
       </c>
     </row>
     <row r="3782" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3782" t="s">
-        <v>7268</v>
+        <v>7260</v>
       </c>
       <c r="B3782" t="s">
-        <v>7269</v>
+        <v>7261</v>
       </c>
     </row>
     <row r="3783" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3783" t="s">
-        <v>7270</v>
+        <v>7262</v>
       </c>
       <c r="B3783" t="s">
-        <v>7271</v>
+        <v>7263</v>
       </c>
     </row>
     <row r="3784" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3784" t="s">
-        <v>7272</v>
+        <v>7264</v>
       </c>
       <c r="B3784" t="s">
-        <v>7273</v>
+        <v>7265</v>
       </c>
     </row>
     <row r="3785" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3785" t="s">
-        <v>7274</v>
+        <v>7266</v>
       </c>
       <c r="B3785" t="s">
-        <v>7275</v>
+        <v>7267</v>
       </c>
     </row>
     <row r="3786" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3786" t="s">
-        <v>7276</v>
+        <v>7268</v>
       </c>
       <c r="B3786" t="s">
-        <v>7277</v>
+        <v>7269</v>
       </c>
     </row>
     <row r="3787" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3787" t="s">
-        <v>7278</v>
+        <v>7270</v>
       </c>
       <c r="B3787" t="s">
-        <v>7279</v>
+        <v>7271</v>
       </c>
     </row>
     <row r="3788" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3788" t="s">
-        <v>7280</v>
+        <v>7272</v>
       </c>
       <c r="B3788" t="s">
-        <v>7281</v>
+        <v>7273</v>
       </c>
     </row>
     <row r="3789" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3789" t="s">
-        <v>7282</v>
+        <v>7274</v>
       </c>
       <c r="B3789" t="s">
-        <v>7283</v>
+        <v>7275</v>
       </c>
     </row>
     <row r="3790" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3790" t="s">
-        <v>7284</v>
+        <v>7276</v>
       </c>
       <c r="B3790" t="s">
-        <v>7285</v>
+        <v>7277</v>
       </c>
     </row>
     <row r="3791" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3791" t="s">
-        <v>7286</v>
+        <v>7278</v>
       </c>
       <c r="B3791" t="s">
-        <v>7287</v>
+        <v>7279</v>
       </c>
     </row>
     <row r="3792" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3792" t="s">
-        <v>7288</v>
+        <v>7280</v>
       </c>
       <c r="B3792" t="s">
-        <v>7289</v>
+        <v>7281</v>
       </c>
     </row>
     <row r="3793" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3793" t="s">
-        <v>7290</v>
+        <v>7282</v>
       </c>
       <c r="B3793" t="s">
-        <v>7291</v>
+        <v>7283</v>
       </c>
     </row>
     <row r="3794" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3794" t="s">
-        <v>7292</v>
+        <v>7284</v>
       </c>
       <c r="B3794" t="s">
-        <v>7293</v>
+        <v>7285</v>
       </c>
     </row>
     <row r="3795" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3795" t="s">
-        <v>7294</v>
+        <v>7286</v>
       </c>
       <c r="B3795" t="s">
-        <v>7295</v>
+        <v>7287</v>
       </c>
     </row>
     <row r="3796" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3796" t="s">
-        <v>7296</v>
+        <v>7288</v>
       </c>
       <c r="B3796" t="s">
-        <v>7297</v>
+        <v>7289</v>
       </c>
     </row>
     <row r="3797" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3797" t="s">
-        <v>7298</v>
+        <v>7290</v>
       </c>
       <c r="B3797" t="s">
-        <v>7299</v>
+        <v>7291</v>
       </c>
     </row>
     <row r="3798" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3798" t="s">
-        <v>7300</v>
+        <v>7292</v>
       </c>
       <c r="B3798" t="s">
-        <v>7301</v>
+        <v>7293</v>
       </c>
     </row>
     <row r="3799" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3799" t="s">
-        <v>7302</v>
+        <v>7294</v>
       </c>
       <c r="B3799" t="s">
-        <v>7303</v>
+        <v>7295</v>
       </c>
     </row>
     <row r="3800" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3800" t="s">
-        <v>7304</v>
+        <v>7296</v>
       </c>
       <c r="B3800" t="s">
-        <v>7305</v>
+        <v>7297</v>
       </c>
     </row>
     <row r="3801" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3801" t="s">
-        <v>7306</v>
+        <v>7298</v>
       </c>
       <c r="B3801" t="s">
-        <v>7307</v>
+        <v>7299</v>
       </c>
     </row>
     <row r="3802" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3802" t="s">
-        <v>7308</v>
+        <v>7300</v>
       </c>
       <c r="B3802" t="s">
-        <v>7309</v>
+        <v>7301</v>
       </c>
     </row>
     <row r="3803" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3803" t="s">
-        <v>7310</v>
+        <v>7302</v>
       </c>
       <c r="B3803" t="s">
-        <v>7311</v>
+        <v>7303</v>
       </c>
     </row>
     <row r="3804" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3804" t="s">
-        <v>7312</v>
+        <v>7304</v>
       </c>
       <c r="B3804" t="s">
-        <v>7313</v>
+        <v>7305</v>
       </c>
     </row>
     <row r="3805" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3805" t="s">
-        <v>7314</v>
+        <v>7306</v>
       </c>
       <c r="B3805" t="s">
-        <v>7315</v>
+        <v>7307</v>
       </c>
     </row>
     <row r="3806" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3806" t="s">
-        <v>7316</v>
+        <v>7308</v>
       </c>
       <c r="B3806" t="s">
-        <v>7317</v>
+        <v>7309</v>
       </c>
     </row>
     <row r="3807" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3807" t="s">
-        <v>7318</v>
+        <v>7310</v>
       </c>
       <c r="B3807" t="s">
-        <v>7319</v>
+        <v>7311</v>
       </c>
     </row>
     <row r="3808" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3808" t="s">
-        <v>7320</v>
+        <v>7312</v>
       </c>
       <c r="B3808" t="s">
-        <v>7321</v>
+        <v>7313</v>
       </c>
     </row>
     <row r="3809" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3809" t="s">
-        <v>7322</v>
+        <v>7314</v>
       </c>
       <c r="B3809" t="s">
-        <v>7323</v>
+        <v>7315</v>
       </c>
     </row>
     <row r="3810" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3810" t="s">
-        <v>7324</v>
+        <v>7316</v>
       </c>
       <c r="B3810" t="s">
-        <v>7325</v>
+        <v>7317</v>
       </c>
     </row>
     <row r="3811" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3811" t="s">
-        <v>7326</v>
+        <v>7318</v>
       </c>
       <c r="B3811" t="s">
-        <v>7327</v>
+        <v>7319</v>
       </c>
     </row>
     <row r="3812" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3812" t="s">
-        <v>7328</v>
+        <v>7320</v>
       </c>
       <c r="B3812" t="s">
-        <v>7329</v>
+        <v>7321</v>
       </c>
     </row>
     <row r="3813" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3813" t="s">
-        <v>7330</v>
+        <v>7322</v>
       </c>
       <c r="B3813" t="s">
-        <v>7331</v>
+        <v>7323</v>
       </c>
     </row>
     <row r="3814" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3814" t="s">
-        <v>7332</v>
+        <v>7324</v>
       </c>
       <c r="B3814" t="s">
-        <v>7333</v>
+        <v>7325</v>
       </c>
     </row>
     <row r="3815" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3815" t="s">
-        <v>7334</v>
+        <v>7326</v>
       </c>
       <c r="B3815" t="s">
-        <v>7335</v>
+        <v>7327</v>
       </c>
     </row>
     <row r="3816" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3816" t="s">
-        <v>7336</v>
+        <v>7328</v>
       </c>
       <c r="B3816" t="s">
-        <v>7337</v>
+        <v>7329</v>
       </c>
     </row>
     <row r="3817" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3817" t="s">
-        <v>7338</v>
+        <v>7330</v>
       </c>
       <c r="B3817" t="s">
-        <v>7339</v>
+        <v>7331</v>
       </c>
     </row>
     <row r="3818" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3818" t="s">
-        <v>7340</v>
+        <v>7332</v>
       </c>
       <c r="B3818" t="s">
-        <v>7341</v>
+        <v>7333</v>
       </c>
     </row>
     <row r="3819" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3819" t="s">
-        <v>7342</v>
+        <v>7334</v>
       </c>
       <c r="B3819" t="s">
-        <v>7343</v>
+        <v>7335</v>
       </c>
     </row>
     <row r="3820" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3820" t="s">
-        <v>7344</v>
+        <v>7336</v>
       </c>
       <c r="B3820" t="s">
-        <v>7345</v>
+        <v>7337</v>
       </c>
     </row>
     <row r="3821" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3821" t="s">
-        <v>7346</v>
+        <v>7338</v>
       </c>
       <c r="B3821" t="s">
-        <v>7347</v>
+        <v>7339</v>
       </c>
     </row>
     <row r="3822" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3822" t="s">
-        <v>7348</v>
+        <v>7340</v>
       </c>
       <c r="B3822" t="s">
-        <v>7349</v>
+        <v>7341</v>
       </c>
     </row>
     <row r="3823" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3823" t="s">
-        <v>7350</v>
+        <v>7342</v>
       </c>
       <c r="B3823" t="s">
-        <v>7351</v>
+        <v>7343</v>
       </c>
     </row>
     <row r="3824" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3824" t="s">
-        <v>7352</v>
+        <v>7344</v>
       </c>
       <c r="B3824" t="s">
-        <v>7353</v>
+        <v>7345</v>
       </c>
     </row>
     <row r="3825" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3825" t="s">
-        <v>7354</v>
+        <v>7346</v>
       </c>
       <c r="B3825" t="s">
-        <v>7355</v>
+        <v>7347</v>
       </c>
     </row>
     <row r="3826" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3826" t="s">
-        <v>7356</v>
+        <v>7348</v>
       </c>
       <c r="B3826" t="s">
-        <v>7357</v>
+        <v>7349</v>
       </c>
     </row>
     <row r="3827" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3827" t="s">
-        <v>7358</v>
+        <v>7350</v>
       </c>
       <c r="B3827" t="s">
-        <v>7359</v>
+        <v>7351</v>
       </c>
     </row>
     <row r="3828" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3828" t="s">
-        <v>7360</v>
+        <v>7352</v>
       </c>
       <c r="B3828" t="s">
-        <v>7361</v>
+        <v>7353</v>
       </c>
     </row>
     <row r="3829" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3829" t="s">
-        <v>7362</v>
+        <v>7354</v>
       </c>
       <c r="B3829" t="s">
-        <v>7363</v>
+        <v>7355</v>
       </c>
     </row>
     <row r="3830" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3830" t="s">
-        <v>7364</v>
+        <v>7356</v>
       </c>
       <c r="B3830" t="s">
-        <v>7365</v>
+        <v>7357</v>
       </c>
     </row>
     <row r="3831" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3831" t="s">
-        <v>7366</v>
+        <v>7358</v>
       </c>
       <c r="B3831" t="s">
-        <v>7367</v>
+        <v>7359</v>
       </c>
     </row>
     <row r="3832" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3832" t="s">
-        <v>7368</v>
+        <v>7360</v>
       </c>
       <c r="B3832" t="s">
-        <v>7369</v>
+        <v>7361</v>
       </c>
     </row>
     <row r="3833" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3833" t="s">
-        <v>7370</v>
+        <v>7362</v>
       </c>
       <c r="B3833" t="s">
-        <v>7371</v>
+        <v>7363</v>
       </c>
     </row>
     <row r="3834" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3834" t="s">
-        <v>7372</v>
+        <v>7364</v>
       </c>
       <c r="B3834" t="s">
-        <v>7373</v>
+        <v>7365</v>
       </c>
     </row>
     <row r="3835" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3835" t="s">
-        <v>7374</v>
+        <v>7366</v>
       </c>
       <c r="B3835" t="s">
-        <v>7375</v>
+        <v>7367</v>
       </c>
     </row>
     <row r="3836" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3836" t="s">
-        <v>7376</v>
+        <v>7368</v>
       </c>
       <c r="B3836" t="s">
-        <v>7377</v>
+        <v>7369</v>
       </c>
     </row>
     <row r="3837" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3837" t="s">
-        <v>7378</v>
+        <v>7370</v>
       </c>
       <c r="B3837" t="s">
-        <v>7379</v>
+        <v>7371</v>
       </c>
     </row>
     <row r="3838" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3838" t="s">
-        <v>7380</v>
+        <v>7372</v>
       </c>
       <c r="B3838" t="s">
-        <v>7381</v>
+        <v>7373</v>
       </c>
     </row>
     <row r="3839" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3839" t="s">
-        <v>7382</v>
+        <v>7374</v>
       </c>
       <c r="B3839" t="s">
-        <v>7383</v>
+        <v>7375</v>
       </c>
     </row>
     <row r="3840" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3840" t="s">
-        <v>7384</v>
+        <v>7376</v>
       </c>
       <c r="B3840" t="s">
-        <v>7385</v>
+        <v>7377</v>
       </c>
     </row>
     <row r="3841" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3841" t="s">
-        <v>7386</v>
+        <v>7378</v>
       </c>
       <c r="B3841" t="s">
-        <v>7387</v>
+        <v>7379</v>
       </c>
     </row>
     <row r="3842" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3842" t="s">
-        <v>7388</v>
+        <v>7380</v>
       </c>
       <c r="B3842" t="s">
-        <v>7389</v>
+        <v>7381</v>
       </c>
     </row>
     <row r="3843" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3843" t="s">
-        <v>7390</v>
+        <v>7382</v>
       </c>
       <c r="B3843" t="s">
-        <v>7391</v>
+        <v>7383</v>
       </c>
     </row>
     <row r="3844" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3844" t="s">
-        <v>7392</v>
+        <v>7384</v>
       </c>
       <c r="B3844" t="s">
-        <v>7393</v>
+        <v>7385</v>
       </c>
     </row>
     <row r="3845" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3845" t="s">
-        <v>7394</v>
+        <v>7386</v>
       </c>
       <c r="B3845" t="s">
-        <v>7395</v>
+        <v>7387</v>
       </c>
     </row>
     <row r="3846" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3846" t="s">
-        <v>7396</v>
+        <v>7388</v>
       </c>
       <c r="B3846" t="s">
-        <v>7397</v>
+        <v>7389</v>
       </c>
     </row>
     <row r="3847" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3847" t="s">
-        <v>7398</v>
+        <v>7390</v>
       </c>
       <c r="B3847" t="s">
-        <v>7399</v>
+        <v>7391</v>
       </c>
     </row>
     <row r="3848" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3848" t="s">
-        <v>7400</v>
+        <v>7392</v>
       </c>
       <c r="B3848" t="s">
-        <v>7401</v>
+        <v>7393</v>
       </c>
     </row>
     <row r="3849" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3849" t="s">
-        <v>7402</v>
+        <v>7394</v>
       </c>
       <c r="B3849" t="s">
-        <v>7403</v>
+        <v>7395</v>
       </c>
     </row>
     <row r="3850" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3850" t="s">
-        <v>7404</v>
+        <v>7396</v>
       </c>
       <c r="B3850" t="s">
-        <v>7405</v>
+        <v>7397</v>
       </c>
     </row>
     <row r="3851" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3851" t="s">
-        <v>7406</v>
+        <v>7398</v>
       </c>
       <c r="B3851" t="s">
-        <v>7407</v>
+        <v>7399</v>
       </c>
     </row>
     <row r="3852" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3852" t="s">
-        <v>7408</v>
+        <v>7400</v>
       </c>
       <c r="B3852" t="s">
-        <v>7409</v>
+        <v>7401</v>
       </c>
     </row>
     <row r="3853" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3853" t="s">
-        <v>7410</v>
+        <v>7402</v>
       </c>
       <c r="B3853" t="s">
-        <v>7411</v>
+        <v>7403</v>
       </c>
     </row>
     <row r="3854" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3854" t="s">
-        <v>7412</v>
+        <v>7404</v>
       </c>
       <c r="B3854" t="s">
-        <v>7413</v>
+        <v>7405</v>
       </c>
     </row>
     <row r="3855" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3855" t="s">
-        <v>7414</v>
+        <v>7406</v>
       </c>
       <c r="B3855" t="s">
-        <v>7415</v>
+        <v>7407</v>
       </c>
     </row>
     <row r="3856" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3856" t="s">
-        <v>7416</v>
+        <v>7408</v>
       </c>
       <c r="B3856" t="s">
-        <v>7417</v>
+        <v>7409</v>
       </c>
     </row>
     <row r="3857" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3857" t="s">
-        <v>7418</v>
+        <v>7410</v>
       </c>
       <c r="B3857" t="s">
-        <v>7419</v>
+        <v>7411</v>
       </c>
     </row>
     <row r="3858" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3858" t="s">
-        <v>7420</v>
+        <v>7412</v>
       </c>
       <c r="B3858" t="s">
-        <v>7421</v>
+        <v>7413</v>
       </c>
     </row>
     <row r="3859" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3859" t="s">
-        <v>7422</v>
+        <v>7414</v>
       </c>
       <c r="B3859" t="s">
-        <v>7423</v>
+        <v>7415</v>
       </c>
     </row>
     <row r="3860" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3860" t="s">
-        <v>7424</v>
+        <v>7416</v>
       </c>
       <c r="B3860" t="s">
-        <v>7425</v>
+        <v>7417</v>
       </c>
     </row>
     <row r="3861" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3861" t="s">
-        <v>7426</v>
+        <v>7418</v>
       </c>
       <c r="B3861" t="s">
-        <v>7427</v>
+        <v>7419</v>
       </c>
     </row>
     <row r="3862" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3862" t="s">
-        <v>7428</v>
+        <v>7420</v>
       </c>
       <c r="B3862" t="s">
-        <v>7429</v>
+        <v>7421</v>
       </c>
     </row>
     <row r="3863" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3863" t="s">
-        <v>7430</v>
+        <v>7422</v>
       </c>
       <c r="B3863" t="s">
-        <v>7431</v>
+        <v>7423</v>
       </c>
     </row>
     <row r="3864" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3864" t="s">
-        <v>7432</v>
+        <v>7424</v>
       </c>
       <c r="B3864" t="s">
-        <v>7433</v>
+        <v>7425</v>
       </c>
     </row>
     <row r="3865" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3865" t="s">
-        <v>7434</v>
+        <v>7426</v>
       </c>
       <c r="B3865" t="s">
-        <v>7435</v>
+        <v>7427</v>
       </c>
     </row>
     <row r="3866" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3866" t="s">
-        <v>7436</v>
+        <v>7428</v>
       </c>
       <c r="B3866" t="s">
-        <v>7437</v>
+        <v>7429</v>
       </c>
     </row>
     <row r="3867" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3867" t="s">
-        <v>7438</v>
+        <v>7430</v>
       </c>
       <c r="B3867" t="s">
-        <v>7439</v>
+        <v>7431</v>
       </c>
     </row>
     <row r="3868" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3868" t="s">
-        <v>7440</v>
+        <v>7432</v>
       </c>
       <c r="B3868" t="s">
-        <v>7441</v>
+        <v>7433</v>
       </c>
     </row>
     <row r="3869" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3869" t="s">
-        <v>7442</v>
+        <v>7434</v>
       </c>
       <c r="B3869" t="s">
-        <v>7443</v>
+        <v>7435</v>
       </c>
     </row>
     <row r="3870" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3870" t="s">
-        <v>7444</v>
+        <v>7436</v>
       </c>
       <c r="B3870" t="s">
-        <v>7445</v>
+        <v>7437</v>
       </c>
     </row>
     <row r="3871" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3871" t="s">
-        <v>7446</v>
+        <v>7438</v>
       </c>
       <c r="B3871" t="s">
-        <v>7447</v>
+        <v>7439</v>
       </c>
     </row>
     <row r="3872" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3872" t="s">
-        <v>7448</v>
+        <v>7440</v>
       </c>
       <c r="B3872" t="s">
-        <v>7449</v>
+        <v>7441</v>
       </c>
     </row>
     <row r="3873" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3873" t="s">
-        <v>7450</v>
+        <v>7442</v>
       </c>
       <c r="B3873" t="s">
-        <v>7451</v>
+        <v>7443</v>
       </c>
     </row>
     <row r="3874" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3874" t="s">
-        <v>7452</v>
+        <v>7444</v>
       </c>
       <c r="B3874" t="s">
-        <v>7453</v>
+        <v>7445</v>
       </c>
     </row>
     <row r="3875" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3875" t="s">
-        <v>7454</v>
+        <v>7446</v>
       </c>
       <c r="B3875" t="s">
-        <v>7455</v>
+        <v>7447</v>
       </c>
     </row>
     <row r="3876" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3876" t="s">
-        <v>7456</v>
+        <v>7448</v>
       </c>
       <c r="B3876" t="s">
-        <v>7457</v>
+        <v>7449</v>
       </c>
     </row>
     <row r="3877" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3877" t="s">
-        <v>7458</v>
+        <v>7450</v>
       </c>
       <c r="B3877" t="s">
-        <v>7459</v>
+        <v>7451</v>
       </c>
     </row>
     <row r="3878" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3878" t="s">
-        <v>7460</v>
+        <v>7452</v>
       </c>
       <c r="B3878" t="s">
-        <v>7461</v>
+        <v>7453</v>
       </c>
     </row>
     <row r="3879" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3879" t="s">
-        <v>7462</v>
+        <v>7454</v>
       </c>
       <c r="B3879" t="s">
-        <v>7463</v>
+        <v>7455</v>
       </c>
     </row>
     <row r="3880" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3880" t="s">
-        <v>7464</v>
+        <v>7456</v>
       </c>
       <c r="B3880" t="s">
-        <v>7465</v>
+        <v>7457</v>
       </c>
     </row>
     <row r="3881" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3881" t="s">
-        <v>7466</v>
+        <v>7458</v>
       </c>
       <c r="B3881" t="s">
-        <v>7467</v>
+        <v>7459</v>
       </c>
     </row>
     <row r="3882" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3882" t="s">
-        <v>7468</v>
+        <v>7460</v>
       </c>
       <c r="B3882" t="s">
-        <v>7469</v>
+        <v>7461</v>
       </c>
     </row>
     <row r="3883" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3883" t="s">
-        <v>7470</v>
+        <v>7462</v>
       </c>
       <c r="B3883" t="s">
-        <v>7471</v>
+        <v>7463</v>
       </c>
     </row>
     <row r="3884" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3884" t="s">
-        <v>7472</v>
+        <v>7464</v>
       </c>
       <c r="B3884" t="s">
-        <v>7473</v>
+        <v>7465</v>
       </c>
     </row>
     <row r="3885" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3885" t="s">
-        <v>7474</v>
+        <v>7466</v>
       </c>
       <c r="B3885" t="s">
-        <v>7475</v>
+        <v>7467</v>
       </c>
     </row>
     <row r="3886" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3886" t="s">
-        <v>7476</v>
+        <v>7468</v>
       </c>
       <c r="B3886" t="s">
-        <v>7477</v>
+        <v>7469</v>
       </c>
     </row>
     <row r="3887" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3887" t="s">
-        <v>7478</v>
+        <v>7470</v>
       </c>
       <c r="B3887" t="s">
-        <v>7479</v>
+        <v>7471</v>
       </c>
     </row>
     <row r="3888" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3888" t="s">
-        <v>7480</v>
+        <v>7472</v>
       </c>
       <c r="B3888" t="s">
-        <v>7481</v>
+        <v>7473</v>
       </c>
     </row>
     <row r="3889" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3889" t="s">
-        <v>7482</v>
+        <v>7474</v>
       </c>
       <c r="B3889" t="s">
-        <v>7483</v>
+        <v>7475</v>
       </c>
     </row>
     <row r="3890" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3890" t="s">
-        <v>7484</v>
+        <v>7476</v>
       </c>
       <c r="B3890" t="s">
-        <v>7485</v>
+        <v>7477</v>
       </c>
     </row>
     <row r="3891" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3891" t="s">
-        <v>7486</v>
+        <v>7478</v>
       </c>
       <c r="B3891" t="s">
-        <v>7487</v>
+        <v>7479</v>
       </c>
     </row>
     <row r="3892" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3892" t="s">
-        <v>7488</v>
+        <v>7480</v>
       </c>
       <c r="B3892" t="s">
-        <v>7489</v>
+        <v>7481</v>
       </c>
     </row>
     <row r="3893" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3893" t="s">
-        <v>7490</v>
+        <v>7482</v>
       </c>
       <c r="B3893" t="s">
-        <v>7491</v>
+        <v>7483</v>
       </c>
     </row>
     <row r="3894" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3894" t="s">
-        <v>7492</v>
+        <v>7484</v>
       </c>
       <c r="B3894" t="s">
-        <v>7493</v>
+        <v>7485</v>
       </c>
     </row>
     <row r="3895" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3895" t="s">
-        <v>7494</v>
+        <v>7486</v>
       </c>
       <c r="B3895" t="s">
-        <v>7495</v>
+        <v>7487</v>
       </c>
     </row>
     <row r="3896" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3896" t="s">
-        <v>7496</v>
+        <v>7488</v>
       </c>
       <c r="B3896" t="s">
-        <v>7497</v>
+        <v>7489</v>
       </c>
     </row>
     <row r="3897" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3897" t="s">
-        <v>7498</v>
+        <v>7490</v>
       </c>
       <c r="B3897" t="s">
-        <v>7499</v>
+        <v>7491</v>
       </c>
     </row>
     <row r="3898" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3898" t="s">
-        <v>7500</v>
+        <v>7492</v>
       </c>
       <c r="B3898" t="s">
-        <v>7501</v>
+        <v>7493</v>
       </c>
     </row>
     <row r="3899" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3899" t="s">
-        <v>7502</v>
+        <v>7494</v>
       </c>
       <c r="B3899" t="s">
-        <v>7503</v>
+        <v>7495</v>
       </c>
     </row>
     <row r="3900" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3900" t="s">
-        <v>7504</v>
+        <v>7496</v>
       </c>
       <c r="B3900" t="s">
-        <v>7505</v>
+        <v>7497</v>
       </c>
     </row>
     <row r="3901" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3901" t="s">
-        <v>7506</v>
+        <v>7498</v>
       </c>
       <c r="B3901" t="s">
-        <v>7507</v>
+        <v>7499</v>
       </c>
     </row>
     <row r="3902" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3902" t="s">
-        <v>7508</v>
+        <v>7500</v>
       </c>
       <c r="B3902" t="s">
-        <v>7509</v>
+        <v>7501</v>
       </c>
     </row>
     <row r="3903" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3903" t="s">
-        <v>7510</v>
+        <v>7502</v>
       </c>
       <c r="B3903" t="s">
-        <v>7511</v>
+        <v>7503</v>
       </c>
     </row>
     <row r="3904" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3904" t="s">
-        <v>7512</v>
+        <v>7504</v>
       </c>
       <c r="B3904" t="s">
-        <v>7513</v>
+        <v>7505</v>
       </c>
     </row>
     <row r="3905" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3905" t="s">
-        <v>7514</v>
+        <v>7506</v>
       </c>
       <c r="B3905" t="s">
-        <v>7515</v>
+        <v>7507</v>
       </c>
     </row>
     <row r="3906" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3906" t="s">
-        <v>7516</v>
+        <v>7508</v>
       </c>
       <c r="B3906" t="s">
-        <v>7517</v>
+        <v>7509</v>
       </c>
     </row>
     <row r="3907" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3907" t="s">
-        <v>7518</v>
+        <v>7510</v>
       </c>
       <c r="B3907" t="s">
-        <v>7519</v>
+        <v>7511</v>
       </c>
     </row>
     <row r="3908" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3908" t="s">
-        <v>7520</v>
+        <v>7512</v>
       </c>
       <c r="B3908" t="s">
-        <v>7521</v>
+        <v>7513</v>
       </c>
     </row>
     <row r="3909" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3909" t="s">
-        <v>7522</v>
+        <v>7514</v>
       </c>
       <c r="B3909" t="s">
-        <v>7523</v>
+        <v>7515</v>
       </c>
     </row>
     <row r="3910" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3910" t="s">
-        <v>7524</v>
+        <v>7516</v>
       </c>
       <c r="B3910" t="s">
-        <v>7525</v>
+        <v>7517</v>
       </c>
     </row>
     <row r="3911" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3911" t="s">
-        <v>7526</v>
+        <v>7518</v>
       </c>
       <c r="B3911" t="s">
-        <v>7527</v>
+        <v>7519</v>
       </c>
     </row>
     <row r="3912" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3912" t="s">
-        <v>7528</v>
+        <v>7520</v>
       </c>
       <c r="B3912" t="s">
-        <v>7529</v>
+        <v>7521</v>
       </c>
     </row>
     <row r="3913" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3913" t="s">
-        <v>7530</v>
+        <v>7522</v>
       </c>
       <c r="B3913" t="s">
-        <v>7531</v>
+        <v>7523</v>
       </c>
     </row>
     <row r="3914" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3914" t="s">
-        <v>7532</v>
+        <v>7524</v>
       </c>
       <c r="B3914" t="s">
-        <v>7533</v>
+        <v>7525</v>
       </c>
     </row>
     <row r="3915" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3915" t="s">
-        <v>7534</v>
+        <v>7526</v>
       </c>
       <c r="B3915" t="s">
-        <v>7535</v>
+        <v>7527</v>
       </c>
     </row>
     <row r="3916" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3916" t="s">
-        <v>7536</v>
+        <v>7528</v>
       </c>
       <c r="B3916" t="s">
-        <v>7537</v>
+        <v>7529</v>
       </c>
     </row>
     <row r="3917" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3917" t="s">
-        <v>7538</v>
+        <v>7530</v>
       </c>
       <c r="B3917" t="s">
-        <v>7539</v>
+        <v>7531</v>
       </c>
     </row>
     <row r="3918" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3918" t="s">
-        <v>7540</v>
+        <v>7532</v>
       </c>
       <c r="B3918" t="s">
-        <v>7541</v>
+        <v>7533</v>
       </c>
     </row>
     <row r="3919" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3919" t="s">
-        <v>7542</v>
+        <v>7534</v>
       </c>
       <c r="B3919" t="s">
-        <v>7543</v>
+        <v>7535</v>
       </c>
     </row>
     <row r="3920" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3920" t="s">
-        <v>7544</v>
+        <v>7536</v>
       </c>
       <c r="B3920" t="s">
-        <v>7545</v>
+        <v>7537</v>
       </c>
     </row>
     <row r="3921" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3921" t="s">
-        <v>7546</v>
+        <v>7538</v>
       </c>
       <c r="B3921" t="s">
-        <v>7547</v>
+        <v>7539</v>
       </c>
     </row>
     <row r="3922" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3922" t="s">
-        <v>7548</v>
+        <v>7540</v>
       </c>
       <c r="B3922" t="s">
-        <v>7549</v>
+        <v>7541</v>
       </c>
     </row>
     <row r="3923" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3923" t="s">
-        <v>7550</v>
+        <v>7542</v>
       </c>
       <c r="B3923" t="s">
-        <v>7551</v>
+        <v>7543</v>
       </c>
     </row>
     <row r="3924" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3924" t="s">
-        <v>7552</v>
+        <v>7544</v>
       </c>
       <c r="B3924" t="s">
-        <v>7553</v>
+        <v>7545</v>
       </c>
     </row>
     <row r="3925" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3925" t="s">
-        <v>7554</v>
+        <v>7546</v>
       </c>
       <c r="B3925" t="s">
-        <v>7555</v>
+        <v>7547</v>
       </c>
     </row>
     <row r="3926" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3926" t="s">
-        <v>7556</v>
+        <v>7548</v>
       </c>
       <c r="B3926" t="s">
-        <v>7557</v>
+        <v>7549</v>
       </c>
     </row>
     <row r="3927" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3927" t="s">
-        <v>7558</v>
+        <v>7550</v>
       </c>
       <c r="B3927" t="s">
-        <v>7559</v>
+        <v>7551</v>
       </c>
     </row>
     <row r="3928" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3928" t="s">
-        <v>7560</v>
+        <v>7552</v>
       </c>
       <c r="B3928" t="s">
-        <v>7561</v>
+        <v>7553</v>
       </c>
     </row>
     <row r="3929" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3929" t="s">
-        <v>7562</v>
+        <v>7554</v>
       </c>
       <c r="B3929" t="s">
-        <v>7563</v>
+        <v>7555</v>
       </c>
     </row>
     <row r="3930" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3930" t="s">
-        <v>7564</v>
+        <v>7556</v>
       </c>
       <c r="B3930" t="s">
-        <v>7565</v>
+        <v>7557</v>
       </c>
     </row>
     <row r="3931" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3931" t="s">
-        <v>7566</v>
+        <v>7558</v>
       </c>
       <c r="B3931" t="s">
-        <v>7567</v>
+        <v>7559</v>
       </c>
     </row>
     <row r="3932" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3932" t="s">
-        <v>7568</v>
+        <v>7560</v>
       </c>
       <c r="B3932" t="s">
-        <v>7569</v>
+        <v>7561</v>
       </c>
     </row>
     <row r="3933" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3933" t="s">
-        <v>7570</v>
+        <v>7562</v>
       </c>
       <c r="B3933" t="s">
-        <v>7571</v>
+        <v>7563</v>
       </c>
     </row>
     <row r="3934" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3934" t="s">
-        <v>7572</v>
+        <v>7564</v>
       </c>
       <c r="B3934" t="s">
-        <v>7573</v>
+        <v>7565</v>
       </c>
     </row>
     <row r="3935" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3935" t="s">
-        <v>7574</v>
+        <v>7566</v>
       </c>
       <c r="B3935" t="s">
-        <v>7575</v>
+        <v>7567</v>
       </c>
     </row>
     <row r="3936" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3936" t="s">
-        <v>7576</v>
+        <v>7568</v>
       </c>
       <c r="B3936" t="s">
-        <v>7577</v>
+        <v>7569</v>
       </c>
     </row>
     <row r="3937" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3937" t="s">
-        <v>7578</v>
+        <v>7570</v>
       </c>
       <c r="B3937" t="s">
-        <v>7579</v>
+        <v>7571</v>
       </c>
     </row>
     <row r="3938" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3938" t="s">
-        <v>7580</v>
+        <v>7572</v>
       </c>
       <c r="B3938" t="s">
-        <v>7581</v>
+        <v>7573</v>
       </c>
     </row>
     <row r="3939" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3939" t="s">
-        <v>7582</v>
+        <v>7574</v>
       </c>
       <c r="B3939" t="s">
-        <v>7583</v>
+        <v>7575</v>
       </c>
     </row>
     <row r="3940" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3940" t="s">
-        <v>7584</v>
+        <v>7576</v>
       </c>
       <c r="B3940" t="s">
-        <v>7585</v>
+        <v>7577</v>
       </c>
     </row>
     <row r="3941" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3941" t="s">
-        <v>7586</v>
+        <v>7578</v>
       </c>
       <c r="B3941" t="s">
-        <v>7587</v>
+        <v>7579</v>
       </c>
     </row>
     <row r="3942" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3942" t="s">
-        <v>7588</v>
+        <v>7580</v>
       </c>
       <c r="B3942" t="s">
-        <v>7589</v>
+        <v>7581</v>
       </c>
     </row>
     <row r="3943" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3943" t="s">
-        <v>7590</v>
+        <v>7582</v>
       </c>
       <c r="B3943" t="s">
-        <v>7591</v>
+        <v>7583</v>
       </c>
     </row>
     <row r="3944" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3944" t="s">
-        <v>7592</v>
+        <v>7584</v>
       </c>
       <c r="B3944" t="s">
-        <v>7593</v>
+        <v>7585</v>
       </c>
     </row>
     <row r="3945" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3945" t="s">
-        <v>7594</v>
+        <v>7586</v>
       </c>
       <c r="B3945" t="s">
-        <v>7595</v>
+        <v>7587</v>
       </c>
     </row>
     <row r="3946" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3946" t="s">
-        <v>7596</v>
+        <v>7588</v>
       </c>
       <c r="B3946" t="s">
-        <v>7597</v>
+        <v>7589</v>
       </c>
     </row>
     <row r="3947" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3947" t="s">
-        <v>7598</v>
+        <v>7590</v>
       </c>
       <c r="B3947" t="s">
-        <v>7599</v>
+        <v>7591</v>
       </c>
     </row>
     <row r="3948" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3948" t="s">
-        <v>7600</v>
+        <v>7592</v>
       </c>
       <c r="B3948" t="s">
-        <v>7601</v>
+        <v>7593</v>
       </c>
     </row>
     <row r="3949" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3949" t="s">
-        <v>7602</v>
+        <v>7594</v>
       </c>
       <c r="B3949" t="s">
-        <v>7603</v>
+        <v>7595</v>
       </c>
     </row>
     <row r="3950" spans="1:2" x14ac:dyDescent="0.25">
@@ -58868,7 +58868,7 @@
         <v>154</v>
       </c>
       <c r="B3950" t="s">
-        <v>7604</v>
+        <v>7596</v>
       </c>
     </row>
     <row r="3951" spans="1:2" x14ac:dyDescent="0.25">
@@ -58876,7 +58876,7 @@
         <v>156</v>
       </c>
       <c r="B3951" t="s">
-        <v>7605</v>
+        <v>7597</v>
       </c>
     </row>
     <row r="3952" spans="1:2" x14ac:dyDescent="0.25">
@@ -58884,7 +58884,7 @@
         <v>158</v>
       </c>
       <c r="B3952" t="s">
-        <v>7606</v>
+        <v>7598</v>
       </c>
     </row>
     <row r="3953" spans="1:2" x14ac:dyDescent="0.25">
@@ -58892,2343 +58892,2343 @@
         <v>160</v>
       </c>
       <c r="B3953" t="s">
-        <v>7607</v>
+        <v>7599</v>
       </c>
     </row>
     <row r="3954" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3954" t="s">
-        <v>7608</v>
+        <v>7600</v>
       </c>
       <c r="B3954" t="s">
-        <v>7609</v>
+        <v>7601</v>
       </c>
     </row>
     <row r="3955" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3955" t="s">
-        <v>7610</v>
+        <v>7602</v>
       </c>
       <c r="B3955" t="s">
-        <v>7611</v>
+        <v>7603</v>
       </c>
     </row>
     <row r="3956" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3956" t="s">
-        <v>7612</v>
+        <v>7604</v>
       </c>
       <c r="B3956" t="s">
-        <v>7613</v>
+        <v>7605</v>
       </c>
     </row>
     <row r="3957" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3957" t="s">
-        <v>7614</v>
+        <v>7606</v>
       </c>
       <c r="B3957" t="s">
-        <v>7615</v>
+        <v>7607</v>
       </c>
     </row>
     <row r="3958" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3958" t="s">
-        <v>7616</v>
+        <v>7608</v>
       </c>
       <c r="B3958" t="s">
-        <v>7617</v>
+        <v>7609</v>
       </c>
     </row>
     <row r="3959" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3959" t="s">
-        <v>7618</v>
+        <v>7610</v>
       </c>
       <c r="B3959" t="s">
-        <v>7619</v>
+        <v>7611</v>
       </c>
     </row>
     <row r="3960" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3960" t="s">
-        <v>7620</v>
+        <v>7612</v>
       </c>
       <c r="B3960" t="s">
-        <v>7621</v>
+        <v>7613</v>
       </c>
     </row>
     <row r="3961" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3961" t="s">
-        <v>7622</v>
+        <v>7614</v>
       </c>
       <c r="B3961" t="s">
-        <v>7623</v>
+        <v>7615</v>
       </c>
     </row>
     <row r="3962" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3962" t="s">
-        <v>7624</v>
+        <v>7616</v>
       </c>
       <c r="B3962" t="s">
-        <v>7625</v>
+        <v>7617</v>
       </c>
     </row>
     <row r="3963" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3963" t="s">
-        <v>7626</v>
+        <v>7618</v>
       </c>
       <c r="B3963" t="s">
-        <v>7627</v>
+        <v>7619</v>
       </c>
     </row>
     <row r="3964" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3964" t="s">
-        <v>7628</v>
+        <v>7620</v>
       </c>
       <c r="B3964" t="s">
-        <v>7629</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="3965" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3965" t="s">
-        <v>7630</v>
+        <v>7622</v>
       </c>
       <c r="B3965" t="s">
-        <v>7631</v>
+        <v>7623</v>
       </c>
     </row>
     <row r="3966" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3966" t="s">
-        <v>7632</v>
+        <v>7624</v>
       </c>
       <c r="B3966" t="s">
-        <v>7633</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="3967" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3967" t="s">
-        <v>7634</v>
+        <v>7626</v>
       </c>
       <c r="B3967" t="s">
-        <v>7635</v>
+        <v>7627</v>
       </c>
     </row>
     <row r="3968" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3968" t="s">
-        <v>7636</v>
+        <v>7628</v>
       </c>
       <c r="B3968" t="s">
-        <v>7637</v>
+        <v>7629</v>
       </c>
     </row>
     <row r="3969" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3969" t="s">
-        <v>7638</v>
+        <v>7630</v>
       </c>
       <c r="B3969" t="s">
-        <v>7639</v>
+        <v>7631</v>
       </c>
     </row>
     <row r="3970" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3970" t="s">
-        <v>7640</v>
+        <v>7632</v>
       </c>
       <c r="B3970" t="s">
-        <v>7641</v>
+        <v>7633</v>
       </c>
     </row>
     <row r="3971" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3971" t="s">
-        <v>7642</v>
+        <v>7634</v>
       </c>
       <c r="B3971" t="s">
-        <v>7643</v>
+        <v>7635</v>
       </c>
     </row>
     <row r="3972" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3972" t="s">
-        <v>7644</v>
+        <v>7636</v>
       </c>
       <c r="B3972" t="s">
-        <v>7645</v>
+        <v>7637</v>
       </c>
     </row>
     <row r="3973" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3973" t="s">
-        <v>7646</v>
+        <v>7638</v>
       </c>
       <c r="B3973" t="s">
-        <v>7647</v>
+        <v>7639</v>
       </c>
     </row>
     <row r="3974" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3974" t="s">
-        <v>7648</v>
+        <v>7640</v>
       </c>
       <c r="B3974" t="s">
-        <v>7649</v>
+        <v>7641</v>
       </c>
     </row>
     <row r="3975" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3975" t="s">
-        <v>7650</v>
+        <v>7642</v>
       </c>
       <c r="B3975" t="s">
-        <v>7651</v>
+        <v>7643</v>
       </c>
     </row>
     <row r="3976" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3976" t="s">
-        <v>7652</v>
+        <v>7644</v>
       </c>
       <c r="B3976" t="s">
-        <v>7653</v>
+        <v>7645</v>
       </c>
     </row>
     <row r="3977" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3977" t="s">
-        <v>7654</v>
+        <v>7646</v>
       </c>
       <c r="B3977" t="s">
-        <v>7655</v>
+        <v>7647</v>
       </c>
     </row>
     <row r="3978" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3978" t="s">
-        <v>7656</v>
+        <v>7648</v>
       </c>
       <c r="B3978" t="s">
-        <v>7657</v>
+        <v>7649</v>
       </c>
     </row>
     <row r="3979" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3979" t="s">
-        <v>7658</v>
+        <v>7650</v>
       </c>
       <c r="B3979" t="s">
-        <v>7659</v>
+        <v>7651</v>
       </c>
     </row>
     <row r="3980" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3980" t="s">
-        <v>7660</v>
+        <v>7652</v>
       </c>
       <c r="B3980" t="s">
-        <v>7661</v>
+        <v>7653</v>
       </c>
     </row>
     <row r="3981" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3981" t="s">
-        <v>7662</v>
+        <v>7654</v>
       </c>
       <c r="B3981" t="s">
-        <v>7663</v>
+        <v>7655</v>
       </c>
     </row>
     <row r="3982" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3982" t="s">
-        <v>7664</v>
+        <v>7656</v>
       </c>
       <c r="B3982" t="s">
-        <v>7665</v>
+        <v>7657</v>
       </c>
     </row>
     <row r="3983" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3983" t="s">
-        <v>7666</v>
+        <v>7658</v>
       </c>
       <c r="B3983" t="s">
-        <v>7667</v>
+        <v>7659</v>
       </c>
     </row>
     <row r="3984" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3984" t="s">
-        <v>7668</v>
+        <v>7660</v>
       </c>
       <c r="B3984" t="s">
-        <v>7669</v>
+        <v>7661</v>
       </c>
     </row>
     <row r="3985" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3985" t="s">
-        <v>7670</v>
+        <v>7662</v>
       </c>
       <c r="B3985" t="s">
-        <v>7671</v>
+        <v>7663</v>
       </c>
     </row>
     <row r="3986" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3986" t="s">
-        <v>7672</v>
+        <v>7664</v>
       </c>
       <c r="B3986" t="s">
-        <v>7673</v>
+        <v>7665</v>
       </c>
     </row>
     <row r="3987" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3987" t="s">
-        <v>7674</v>
+        <v>7666</v>
       </c>
       <c r="B3987" t="s">
-        <v>7675</v>
+        <v>7667</v>
       </c>
     </row>
     <row r="3988" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3988" t="s">
-        <v>7676</v>
+        <v>7668</v>
       </c>
       <c r="B3988" t="s">
-        <v>7677</v>
+        <v>7669</v>
       </c>
     </row>
     <row r="3989" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3989" t="s">
-        <v>7678</v>
+        <v>7670</v>
       </c>
       <c r="B3989" t="s">
-        <v>7679</v>
+        <v>7671</v>
       </c>
     </row>
     <row r="3990" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3990" t="s">
-        <v>7680</v>
+        <v>7672</v>
       </c>
       <c r="B3990" t="s">
-        <v>7681</v>
+        <v>7673</v>
       </c>
     </row>
     <row r="3991" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3991" t="s">
-        <v>7682</v>
+        <v>7674</v>
       </c>
       <c r="B3991" t="s">
-        <v>7683</v>
+        <v>7675</v>
       </c>
     </row>
     <row r="3992" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3992" t="s">
-        <v>7684</v>
+        <v>7676</v>
       </c>
       <c r="B3992" t="s">
-        <v>7685</v>
+        <v>7677</v>
       </c>
     </row>
     <row r="3993" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3993" t="s">
-        <v>7686</v>
+        <v>7678</v>
       </c>
       <c r="B3993" t="s">
-        <v>7687</v>
+        <v>7679</v>
       </c>
     </row>
     <row r="3994" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3994" t="s">
-        <v>7688</v>
+        <v>7680</v>
       </c>
       <c r="B3994" t="s">
-        <v>7689</v>
+        <v>7681</v>
       </c>
     </row>
     <row r="3995" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3995" t="s">
-        <v>7690</v>
+        <v>7682</v>
       </c>
       <c r="B3995" t="s">
-        <v>7691</v>
+        <v>7683</v>
       </c>
     </row>
     <row r="3996" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3996" t="s">
-        <v>7692</v>
+        <v>7684</v>
       </c>
       <c r="B3996" t="s">
-        <v>7693</v>
+        <v>7685</v>
       </c>
     </row>
     <row r="3997" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3997" t="s">
-        <v>7694</v>
+        <v>7686</v>
       </c>
       <c r="B3997" t="s">
-        <v>7695</v>
+        <v>7687</v>
       </c>
     </row>
     <row r="3998" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3998" t="s">
-        <v>7696</v>
+        <v>7688</v>
       </c>
       <c r="B3998" t="s">
-        <v>7697</v>
+        <v>7689</v>
       </c>
     </row>
     <row r="3999" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3999" t="s">
-        <v>7698</v>
+        <v>7690</v>
       </c>
       <c r="B3999" t="s">
-        <v>7699</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="4000" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4000" t="s">
-        <v>7700</v>
+        <v>7692</v>
       </c>
       <c r="B4000" t="s">
-        <v>7701</v>
+        <v>7693</v>
       </c>
     </row>
     <row r="4001" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4001" t="s">
-        <v>7702</v>
+        <v>7694</v>
       </c>
       <c r="B4001" t="s">
-        <v>7703</v>
+        <v>7695</v>
       </c>
     </row>
     <row r="4002" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4002" t="s">
-        <v>7704</v>
+        <v>7696</v>
       </c>
       <c r="B4002" t="s">
-        <v>7705</v>
+        <v>7697</v>
       </c>
     </row>
     <row r="4003" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4003" t="s">
-        <v>7706</v>
+        <v>7698</v>
       </c>
       <c r="B4003" t="s">
-        <v>7707</v>
+        <v>7699</v>
       </c>
     </row>
     <row r="4004" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4004" t="s">
-        <v>7708</v>
+        <v>7700</v>
       </c>
       <c r="B4004" t="s">
-        <v>7709</v>
+        <v>7701</v>
       </c>
     </row>
     <row r="4005" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4005" t="s">
-        <v>7710</v>
+        <v>7702</v>
       </c>
       <c r="B4005" t="s">
-        <v>7711</v>
+        <v>7703</v>
       </c>
     </row>
     <row r="4006" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4006" t="s">
-        <v>7712</v>
+        <v>7704</v>
       </c>
       <c r="B4006" t="s">
-        <v>7713</v>
+        <v>7705</v>
       </c>
     </row>
     <row r="4007" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4007" t="s">
-        <v>7714</v>
+        <v>7706</v>
       </c>
       <c r="B4007" t="s">
-        <v>7715</v>
+        <v>7707</v>
       </c>
     </row>
     <row r="4008" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4008" t="s">
-        <v>7716</v>
+        <v>7708</v>
       </c>
       <c r="B4008" t="s">
-        <v>7717</v>
+        <v>7709</v>
       </c>
     </row>
     <row r="4009" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4009" t="s">
-        <v>7718</v>
+        <v>7710</v>
       </c>
       <c r="B4009" t="s">
-        <v>7719</v>
+        <v>7711</v>
       </c>
     </row>
     <row r="4010" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4010" t="s">
-        <v>7720</v>
+        <v>7712</v>
       </c>
       <c r="B4010" t="s">
-        <v>7721</v>
+        <v>7713</v>
       </c>
     </row>
     <row r="4011" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4011" t="s">
-        <v>7722</v>
+        <v>7714</v>
       </c>
       <c r="B4011" t="s">
-        <v>7723</v>
+        <v>7715</v>
       </c>
     </row>
     <row r="4012" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4012" t="s">
-        <v>7724</v>
+        <v>7716</v>
       </c>
       <c r="B4012" t="s">
-        <v>7725</v>
+        <v>7717</v>
       </c>
     </row>
     <row r="4013" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4013" t="s">
-        <v>7726</v>
+        <v>7718</v>
       </c>
       <c r="B4013" t="s">
-        <v>7727</v>
+        <v>7719</v>
       </c>
     </row>
     <row r="4014" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4014" t="s">
-        <v>7728</v>
+        <v>7720</v>
       </c>
       <c r="B4014" t="s">
-        <v>7729</v>
+        <v>7721</v>
       </c>
     </row>
     <row r="4015" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4015" t="s">
-        <v>7730</v>
+        <v>7722</v>
       </c>
       <c r="B4015" t="s">
-        <v>7731</v>
+        <v>7723</v>
       </c>
     </row>
     <row r="4016" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4016" t="s">
-        <v>7732</v>
+        <v>7724</v>
       </c>
       <c r="B4016" t="s">
-        <v>7733</v>
+        <v>7725</v>
       </c>
     </row>
     <row r="4017" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4017" t="s">
-        <v>7734</v>
+        <v>7726</v>
       </c>
       <c r="B4017" t="s">
-        <v>7735</v>
+        <v>7727</v>
       </c>
     </row>
     <row r="4018" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4018" t="s">
-        <v>7736</v>
+        <v>7728</v>
       </c>
       <c r="B4018" t="s">
-        <v>7737</v>
+        <v>7729</v>
       </c>
     </row>
     <row r="4019" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4019" t="s">
-        <v>7738</v>
+        <v>7730</v>
       </c>
       <c r="B4019" t="s">
-        <v>7739</v>
+        <v>7731</v>
       </c>
     </row>
     <row r="4020" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4020" t="s">
-        <v>7740</v>
+        <v>7732</v>
       </c>
       <c r="B4020" t="s">
-        <v>7741</v>
+        <v>7733</v>
       </c>
     </row>
     <row r="4021" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4021" t="s">
-        <v>7742</v>
+        <v>7734</v>
       </c>
       <c r="B4021" t="s">
-        <v>7743</v>
+        <v>7735</v>
       </c>
     </row>
     <row r="4022" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4022" t="s">
-        <v>7744</v>
+        <v>7736</v>
       </c>
       <c r="B4022" t="s">
-        <v>7745</v>
+        <v>7737</v>
       </c>
     </row>
     <row r="4023" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4023" t="s">
-        <v>7746</v>
+        <v>7738</v>
       </c>
       <c r="B4023" t="s">
-        <v>7747</v>
+        <v>7739</v>
       </c>
     </row>
     <row r="4024" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4024" t="s">
-        <v>7748</v>
+        <v>7740</v>
       </c>
       <c r="B4024" t="s">
-        <v>7749</v>
+        <v>7741</v>
       </c>
     </row>
     <row r="4025" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4025" t="s">
-        <v>7750</v>
+        <v>7742</v>
       </c>
       <c r="B4025" t="s">
-        <v>7751</v>
+        <v>7743</v>
       </c>
     </row>
     <row r="4026" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4026" t="s">
-        <v>7752</v>
+        <v>7744</v>
       </c>
       <c r="B4026" t="s">
-        <v>7753</v>
+        <v>7745</v>
       </c>
     </row>
     <row r="4027" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4027" t="s">
-        <v>7754</v>
+        <v>7746</v>
       </c>
       <c r="B4027" t="s">
-        <v>7755</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="4028" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4028" t="s">
-        <v>7756</v>
+        <v>7748</v>
       </c>
       <c r="B4028" t="s">
-        <v>7757</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="4029" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4029" t="s">
-        <v>7758</v>
+        <v>7750</v>
       </c>
       <c r="B4029" t="s">
-        <v>7759</v>
+        <v>7751</v>
       </c>
     </row>
     <row r="4030" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4030" t="s">
-        <v>7760</v>
+        <v>7752</v>
       </c>
       <c r="B4030" t="s">
-        <v>7761</v>
+        <v>7753</v>
       </c>
     </row>
     <row r="4031" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4031" t="s">
-        <v>7762</v>
+        <v>7754</v>
       </c>
       <c r="B4031" t="s">
-        <v>7763</v>
+        <v>7755</v>
       </c>
     </row>
     <row r="4032" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4032" t="s">
-        <v>7764</v>
+        <v>7756</v>
       </c>
       <c r="B4032" t="s">
-        <v>7765</v>
+        <v>7757</v>
       </c>
     </row>
     <row r="4033" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4033" t="s">
-        <v>7766</v>
+        <v>7758</v>
       </c>
       <c r="B4033" t="s">
-        <v>7767</v>
+        <v>7759</v>
       </c>
     </row>
     <row r="4034" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4034" t="s">
-        <v>7768</v>
+        <v>7760</v>
       </c>
       <c r="B4034" t="s">
-        <v>7769</v>
+        <v>7761</v>
       </c>
     </row>
     <row r="4035" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4035" t="s">
-        <v>7770</v>
+        <v>7762</v>
       </c>
       <c r="B4035" t="s">
-        <v>7771</v>
+        <v>7763</v>
       </c>
     </row>
     <row r="4036" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4036" t="s">
-        <v>7772</v>
+        <v>7764</v>
       </c>
       <c r="B4036" t="s">
-        <v>7773</v>
+        <v>7765</v>
       </c>
     </row>
     <row r="4037" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4037" t="s">
-        <v>7774</v>
+        <v>7766</v>
       </c>
       <c r="B4037" t="s">
-        <v>7775</v>
+        <v>7767</v>
       </c>
     </row>
     <row r="4038" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4038" t="s">
-        <v>7776</v>
+        <v>7768</v>
       </c>
       <c r="B4038" t="s">
-        <v>7777</v>
+        <v>7769</v>
       </c>
     </row>
     <row r="4039" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4039" t="s">
-        <v>7778</v>
+        <v>7770</v>
       </c>
       <c r="B4039" t="s">
-        <v>7779</v>
+        <v>7771</v>
       </c>
     </row>
     <row r="4040" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4040" t="s">
-        <v>7780</v>
+        <v>7772</v>
       </c>
       <c r="B4040" t="s">
-        <v>7781</v>
+        <v>7773</v>
       </c>
     </row>
     <row r="4041" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4041" t="s">
-        <v>7782</v>
+        <v>7774</v>
       </c>
       <c r="B4041" t="s">
-        <v>7783</v>
+        <v>7775</v>
       </c>
     </row>
     <row r="4042" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4042" t="s">
-        <v>7784</v>
+        <v>7776</v>
       </c>
       <c r="B4042" t="s">
-        <v>7785</v>
+        <v>7777</v>
       </c>
     </row>
     <row r="4043" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4043" t="s">
-        <v>7786</v>
+        <v>7778</v>
       </c>
       <c r="B4043" t="s">
-        <v>7787</v>
+        <v>7779</v>
       </c>
     </row>
     <row r="4044" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4044" t="s">
-        <v>7788</v>
+        <v>7780</v>
       </c>
       <c r="B4044" t="s">
-        <v>7789</v>
+        <v>7781</v>
       </c>
     </row>
     <row r="4045" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4045" t="s">
-        <v>7790</v>
+        <v>7782</v>
       </c>
       <c r="B4045" t="s">
-        <v>7791</v>
+        <v>7783</v>
       </c>
     </row>
     <row r="4046" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4046" t="s">
-        <v>7792</v>
+        <v>7784</v>
       </c>
       <c r="B4046" t="s">
-        <v>7793</v>
+        <v>7785</v>
       </c>
     </row>
     <row r="4047" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4047" t="s">
-        <v>7794</v>
+        <v>7786</v>
       </c>
       <c r="B4047" t="s">
-        <v>7795</v>
+        <v>7787</v>
       </c>
     </row>
     <row r="4048" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4048" t="s">
-        <v>7796</v>
+        <v>7788</v>
       </c>
       <c r="B4048" t="s">
-        <v>7797</v>
+        <v>7789</v>
       </c>
     </row>
     <row r="4049" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4049" t="s">
-        <v>7798</v>
+        <v>7790</v>
       </c>
       <c r="B4049" t="s">
-        <v>7799</v>
+        <v>7791</v>
       </c>
     </row>
     <row r="4050" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4050" t="s">
-        <v>7800</v>
+        <v>7792</v>
       </c>
       <c r="B4050" t="s">
-        <v>7801</v>
+        <v>7793</v>
       </c>
     </row>
     <row r="4051" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4051" t="s">
-        <v>7802</v>
+        <v>7794</v>
       </c>
       <c r="B4051" t="s">
-        <v>7803</v>
+        <v>7795</v>
       </c>
     </row>
     <row r="4052" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4052" t="s">
-        <v>7804</v>
+        <v>7796</v>
       </c>
       <c r="B4052" t="s">
-        <v>7805</v>
+        <v>7797</v>
       </c>
     </row>
     <row r="4053" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4053" t="s">
-        <v>7806</v>
+        <v>7798</v>
       </c>
       <c r="B4053" t="s">
-        <v>7807</v>
+        <v>7799</v>
       </c>
     </row>
     <row r="4054" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4054" t="s">
-        <v>7808</v>
+        <v>7800</v>
       </c>
       <c r="B4054" t="s">
-        <v>7809</v>
+        <v>7801</v>
       </c>
     </row>
     <row r="4055" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4055" t="s">
-        <v>7810</v>
+        <v>7802</v>
       </c>
       <c r="B4055" t="s">
-        <v>7811</v>
+        <v>7803</v>
       </c>
     </row>
     <row r="4056" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4056" t="s">
-        <v>7812</v>
+        <v>7804</v>
       </c>
       <c r="B4056" t="s">
-        <v>7813</v>
+        <v>7805</v>
       </c>
     </row>
     <row r="4057" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4057" t="s">
-        <v>7814</v>
+        <v>7806</v>
       </c>
       <c r="B4057" t="s">
-        <v>7815</v>
+        <v>7807</v>
       </c>
     </row>
     <row r="4058" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4058" t="s">
-        <v>7816</v>
+        <v>7808</v>
       </c>
       <c r="B4058" t="s">
-        <v>7817</v>
+        <v>7809</v>
       </c>
     </row>
     <row r="4059" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4059" t="s">
-        <v>7818</v>
+        <v>7810</v>
       </c>
       <c r="B4059" t="s">
-        <v>7819</v>
+        <v>7811</v>
       </c>
     </row>
     <row r="4060" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4060" t="s">
-        <v>7820</v>
+        <v>7812</v>
       </c>
       <c r="B4060" t="s">
-        <v>7821</v>
+        <v>7813</v>
       </c>
     </row>
     <row r="4061" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4061" t="s">
-        <v>7822</v>
+        <v>7814</v>
       </c>
       <c r="B4061" t="s">
-        <v>7823</v>
+        <v>7815</v>
       </c>
     </row>
     <row r="4062" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4062" t="s">
-        <v>7824</v>
+        <v>7816</v>
       </c>
       <c r="B4062" t="s">
-        <v>7825</v>
+        <v>7817</v>
       </c>
     </row>
     <row r="4063" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4063" t="s">
-        <v>7826</v>
+        <v>7818</v>
       </c>
       <c r="B4063" t="s">
-        <v>7827</v>
+        <v>7819</v>
       </c>
     </row>
     <row r="4064" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4064" t="s">
-        <v>7828</v>
+        <v>7820</v>
       </c>
       <c r="B4064" t="s">
-        <v>7829</v>
+        <v>7821</v>
       </c>
     </row>
     <row r="4065" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4065" t="s">
-        <v>7830</v>
+        <v>7822</v>
       </c>
       <c r="B4065" t="s">
-        <v>7831</v>
+        <v>7823</v>
       </c>
     </row>
     <row r="4066" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4066" t="s">
-        <v>7832</v>
+        <v>7824</v>
       </c>
       <c r="B4066" t="s">
-        <v>7833</v>
+        <v>7825</v>
       </c>
     </row>
     <row r="4067" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4067" t="s">
-        <v>7834</v>
+        <v>7826</v>
       </c>
       <c r="B4067" t="s">
-        <v>7835</v>
+        <v>7827</v>
       </c>
     </row>
     <row r="4068" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4068" t="s">
-        <v>7836</v>
+        <v>7828</v>
       </c>
       <c r="B4068" t="s">
-        <v>7837</v>
+        <v>7829</v>
       </c>
     </row>
     <row r="4069" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4069" t="s">
-        <v>7838</v>
+        <v>7830</v>
       </c>
       <c r="B4069" t="s">
-        <v>7839</v>
+        <v>7831</v>
       </c>
     </row>
     <row r="4070" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4070" t="s">
-        <v>7840</v>
+        <v>7832</v>
       </c>
       <c r="B4070" t="s">
-        <v>7841</v>
+        <v>7833</v>
       </c>
     </row>
     <row r="4071" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4071" t="s">
-        <v>7842</v>
+        <v>7834</v>
       </c>
       <c r="B4071" t="s">
-        <v>7843</v>
+        <v>7835</v>
       </c>
     </row>
     <row r="4072" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4072" t="s">
-        <v>7844</v>
+        <v>7836</v>
       </c>
       <c r="B4072" t="s">
-        <v>7845</v>
+        <v>7837</v>
       </c>
     </row>
     <row r="4073" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4073" t="s">
-        <v>7846</v>
+        <v>7838</v>
       </c>
       <c r="B4073" t="s">
-        <v>7847</v>
+        <v>7839</v>
       </c>
     </row>
     <row r="4074" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4074" t="s">
-        <v>7848</v>
+        <v>7840</v>
       </c>
       <c r="B4074" t="s">
-        <v>7849</v>
+        <v>7841</v>
       </c>
     </row>
     <row r="4075" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4075" t="s">
-        <v>7850</v>
+        <v>7842</v>
       </c>
       <c r="B4075" t="s">
-        <v>7851</v>
+        <v>7843</v>
       </c>
     </row>
     <row r="4076" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4076" t="s">
-        <v>7852</v>
+        <v>7844</v>
       </c>
       <c r="B4076" t="s">
-        <v>7853</v>
+        <v>7845</v>
       </c>
     </row>
     <row r="4077" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4077" t="s">
-        <v>7854</v>
+        <v>7846</v>
       </c>
       <c r="B4077" t="s">
-        <v>7855</v>
+        <v>7847</v>
       </c>
     </row>
     <row r="4078" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4078" t="s">
-        <v>7856</v>
+        <v>7848</v>
       </c>
       <c r="B4078" t="s">
-        <v>7857</v>
+        <v>7849</v>
       </c>
     </row>
     <row r="4079" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4079" t="s">
-        <v>7858</v>
+        <v>7850</v>
       </c>
       <c r="B4079" t="s">
-        <v>7859</v>
+        <v>7851</v>
       </c>
     </row>
     <row r="4080" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4080" t="s">
-        <v>7860</v>
+        <v>7852</v>
       </c>
       <c r="B4080" t="s">
-        <v>7861</v>
+        <v>7853</v>
       </c>
     </row>
     <row r="4081" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4081" t="s">
-        <v>7862</v>
+        <v>7854</v>
       </c>
       <c r="B4081" t="s">
-        <v>7863</v>
+        <v>7855</v>
       </c>
     </row>
     <row r="4082" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4082" t="s">
-        <v>7864</v>
+        <v>7856</v>
       </c>
       <c r="B4082" t="s">
-        <v>7865</v>
+        <v>7857</v>
       </c>
     </row>
     <row r="4083" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4083" t="s">
-        <v>7866</v>
+        <v>7858</v>
       </c>
       <c r="B4083" t="s">
-        <v>7867</v>
+        <v>7859</v>
       </c>
     </row>
     <row r="4084" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4084" t="s">
-        <v>7868</v>
+        <v>7860</v>
       </c>
       <c r="B4084" t="s">
-        <v>7869</v>
+        <v>7861</v>
       </c>
     </row>
     <row r="4085" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4085" t="s">
-        <v>7870</v>
+        <v>7862</v>
       </c>
       <c r="B4085" t="s">
-        <v>7871</v>
+        <v>7863</v>
       </c>
     </row>
     <row r="4086" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4086" t="s">
-        <v>7872</v>
+        <v>7864</v>
       </c>
       <c r="B4086" t="s">
-        <v>7873</v>
+        <v>7865</v>
       </c>
     </row>
     <row r="4087" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4087" t="s">
-        <v>7874</v>
+        <v>7866</v>
       </c>
       <c r="B4087" t="s">
-        <v>7875</v>
+        <v>7867</v>
       </c>
     </row>
     <row r="4088" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4088" t="s">
-        <v>7876</v>
+        <v>7868</v>
       </c>
       <c r="B4088" t="s">
-        <v>7877</v>
+        <v>7869</v>
       </c>
     </row>
     <row r="4089" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4089" t="s">
-        <v>7878</v>
+        <v>7870</v>
       </c>
       <c r="B4089" t="s">
-        <v>7879</v>
+        <v>7871</v>
       </c>
     </row>
     <row r="4090" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4090" t="s">
-        <v>7880</v>
+        <v>7872</v>
       </c>
       <c r="B4090" t="s">
-        <v>7881</v>
+        <v>7873</v>
       </c>
     </row>
     <row r="4091" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4091" t="s">
-        <v>7882</v>
+        <v>7874</v>
       </c>
       <c r="B4091" t="s">
-        <v>7883</v>
+        <v>7875</v>
       </c>
     </row>
     <row r="4092" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4092" t="s">
-        <v>7884</v>
+        <v>7876</v>
       </c>
       <c r="B4092" t="s">
-        <v>7885</v>
+        <v>7877</v>
       </c>
     </row>
     <row r="4093" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4093" t="s">
-        <v>7886</v>
+        <v>7878</v>
       </c>
       <c r="B4093" t="s">
-        <v>7887</v>
+        <v>7879</v>
       </c>
     </row>
     <row r="4094" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4094" t="s">
-        <v>7888</v>
+        <v>7880</v>
       </c>
       <c r="B4094" t="s">
-        <v>7889</v>
+        <v>7881</v>
       </c>
     </row>
     <row r="4095" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4095" t="s">
-        <v>7890</v>
+        <v>7882</v>
       </c>
       <c r="B4095" t="s">
-        <v>7891</v>
+        <v>7883</v>
       </c>
     </row>
     <row r="4096" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4096" t="s">
-        <v>7892</v>
+        <v>7884</v>
       </c>
       <c r="B4096" t="s">
-        <v>7893</v>
+        <v>7885</v>
       </c>
     </row>
     <row r="4097" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4097" t="s">
-        <v>7894</v>
+        <v>7886</v>
       </c>
       <c r="B4097" t="s">
-        <v>7895</v>
+        <v>7887</v>
       </c>
     </row>
     <row r="4098" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4098" t="s">
-        <v>7896</v>
+        <v>7888</v>
       </c>
       <c r="B4098" t="s">
-        <v>7897</v>
+        <v>7889</v>
       </c>
     </row>
     <row r="4099" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4099" t="s">
-        <v>7898</v>
+        <v>7890</v>
       </c>
       <c r="B4099" t="s">
-        <v>7899</v>
+        <v>7891</v>
       </c>
     </row>
     <row r="4100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4100" t="s">
-        <v>7900</v>
+        <v>7892</v>
       </c>
       <c r="B4100" t="s">
-        <v>7901</v>
+        <v>7893</v>
       </c>
     </row>
     <row r="4101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4101" t="s">
-        <v>7902</v>
+        <v>7894</v>
       </c>
       <c r="B4101" t="s">
-        <v>7903</v>
+        <v>7895</v>
       </c>
     </row>
     <row r="4102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4102" t="s">
-        <v>7904</v>
+        <v>7896</v>
       </c>
       <c r="B4102" t="s">
-        <v>7905</v>
+        <v>7897</v>
       </c>
     </row>
     <row r="4103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4103" t="s">
-        <v>7906</v>
+        <v>7898</v>
       </c>
       <c r="B4103" t="s">
-        <v>7907</v>
+        <v>7899</v>
       </c>
     </row>
     <row r="4104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4104" t="s">
-        <v>7908</v>
+        <v>7900</v>
       </c>
       <c r="B4104" t="s">
-        <v>7909</v>
+        <v>7901</v>
       </c>
     </row>
     <row r="4105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4105" t="s">
-        <v>7910</v>
+        <v>7902</v>
       </c>
       <c r="B4105" t="s">
-        <v>7911</v>
+        <v>7903</v>
       </c>
     </row>
     <row r="4106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4106" t="s">
-        <v>7912</v>
+        <v>7904</v>
       </c>
       <c r="B4106" t="s">
-        <v>7913</v>
+        <v>7905</v>
       </c>
     </row>
     <row r="4107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4107" t="s">
-        <v>7914</v>
+        <v>7906</v>
       </c>
       <c r="B4107" t="s">
-        <v>7915</v>
+        <v>7907</v>
       </c>
     </row>
     <row r="4108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4108" t="s">
-        <v>7916</v>
+        <v>7908</v>
       </c>
       <c r="B4108" t="s">
-        <v>7917</v>
+        <v>7909</v>
       </c>
     </row>
     <row r="4109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4109" t="s">
-        <v>7918</v>
+        <v>7910</v>
       </c>
       <c r="B4109" t="s">
-        <v>7919</v>
+        <v>7911</v>
       </c>
     </row>
     <row r="4110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4110" t="s">
-        <v>7920</v>
+        <v>7912</v>
       </c>
       <c r="B4110" t="s">
-        <v>7921</v>
+        <v>7913</v>
       </c>
     </row>
     <row r="4111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4111" t="s">
-        <v>7922</v>
+        <v>7914</v>
       </c>
       <c r="B4111" t="s">
-        <v>7923</v>
+        <v>7915</v>
       </c>
     </row>
     <row r="4112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4112" t="s">
-        <v>7924</v>
+        <v>7916</v>
       </c>
       <c r="B4112" t="s">
-        <v>7925</v>
+        <v>7917</v>
       </c>
     </row>
     <row r="4113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4113" t="s">
-        <v>7926</v>
+        <v>7918</v>
       </c>
       <c r="B4113" t="s">
-        <v>7927</v>
+        <v>7919</v>
       </c>
     </row>
     <row r="4114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4114" t="s">
-        <v>7928</v>
+        <v>7920</v>
       </c>
       <c r="B4114" t="s">
-        <v>7929</v>
+        <v>7921</v>
       </c>
     </row>
     <row r="4115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4115" t="s">
-        <v>7930</v>
+        <v>7922</v>
       </c>
       <c r="B4115" t="s">
-        <v>7931</v>
+        <v>7923</v>
       </c>
     </row>
     <row r="4116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4116" t="s">
-        <v>7932</v>
+        <v>7924</v>
       </c>
       <c r="B4116" t="s">
-        <v>7933</v>
+        <v>7925</v>
       </c>
     </row>
     <row r="4117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4117" t="s">
-        <v>7934</v>
+        <v>7926</v>
       </c>
       <c r="B4117" t="s">
-        <v>7935</v>
+        <v>7927</v>
       </c>
     </row>
     <row r="4118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4118" t="s">
-        <v>7936</v>
+        <v>7928</v>
       </c>
       <c r="B4118" t="s">
-        <v>7937</v>
+        <v>7929</v>
       </c>
     </row>
     <row r="4119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4119" t="s">
-        <v>7938</v>
+        <v>7930</v>
       </c>
       <c r="B4119" t="s">
-        <v>7939</v>
+        <v>7931</v>
       </c>
     </row>
     <row r="4120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4120" t="s">
-        <v>7940</v>
+        <v>7932</v>
       </c>
       <c r="B4120" t="s">
-        <v>7941</v>
+        <v>7933</v>
       </c>
     </row>
     <row r="4121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4121" t="s">
-        <v>7942</v>
+        <v>7934</v>
       </c>
       <c r="B4121" t="s">
-        <v>7943</v>
+        <v>7935</v>
       </c>
     </row>
     <row r="4122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4122" t="s">
-        <v>7944</v>
+        <v>7936</v>
       </c>
       <c r="B4122" t="s">
-        <v>7945</v>
+        <v>7937</v>
       </c>
     </row>
     <row r="4123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4123" t="s">
-        <v>7946</v>
+        <v>7938</v>
       </c>
       <c r="B4123" t="s">
-        <v>7947</v>
+        <v>7939</v>
       </c>
     </row>
     <row r="4124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4124" t="s">
-        <v>7948</v>
+        <v>7940</v>
       </c>
       <c r="B4124" t="s">
-        <v>7949</v>
+        <v>7941</v>
       </c>
     </row>
     <row r="4125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4125" t="s">
-        <v>7950</v>
+        <v>7942</v>
       </c>
       <c r="B4125" t="s">
-        <v>7951</v>
+        <v>7943</v>
       </c>
     </row>
     <row r="4126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4126" t="s">
-        <v>7952</v>
+        <v>7944</v>
       </c>
       <c r="B4126" t="s">
-        <v>7953</v>
+        <v>7945</v>
       </c>
     </row>
     <row r="4127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4127" t="s">
-        <v>7954</v>
+        <v>7946</v>
       </c>
       <c r="B4127" t="s">
-        <v>7955</v>
+        <v>7947</v>
       </c>
     </row>
     <row r="4128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4128" t="s">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="B4128" t="s">
-        <v>7957</v>
+        <v>7949</v>
       </c>
     </row>
     <row r="4129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4129" t="s">
-        <v>7958</v>
+        <v>7950</v>
       </c>
       <c r="B4129" t="s">
-        <v>7959</v>
+        <v>7951</v>
       </c>
     </row>
     <row r="4130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4130" t="s">
-        <v>7960</v>
+        <v>7952</v>
       </c>
       <c r="B4130" t="s">
-        <v>7961</v>
+        <v>7953</v>
       </c>
     </row>
     <row r="4131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4131" t="s">
-        <v>7962</v>
+        <v>7954</v>
       </c>
       <c r="B4131" t="s">
-        <v>7963</v>
+        <v>7955</v>
       </c>
     </row>
     <row r="4132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4132" t="s">
-        <v>7964</v>
+        <v>7956</v>
       </c>
       <c r="B4132" t="s">
-        <v>7965</v>
+        <v>7957</v>
       </c>
     </row>
     <row r="4133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4133" t="s">
-        <v>7966</v>
+        <v>7958</v>
       </c>
       <c r="B4133" t="s">
-        <v>7967</v>
+        <v>7959</v>
       </c>
     </row>
     <row r="4134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4134" t="s">
-        <v>7968</v>
+        <v>7960</v>
       </c>
       <c r="B4134" t="s">
-        <v>7969</v>
+        <v>7961</v>
       </c>
     </row>
     <row r="4135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4135" t="s">
-        <v>7970</v>
+        <v>7962</v>
       </c>
       <c r="B4135" t="s">
-        <v>7971</v>
+        <v>7963</v>
       </c>
     </row>
     <row r="4136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4136" t="s">
-        <v>7972</v>
+        <v>7964</v>
       </c>
       <c r="B4136" t="s">
-        <v>7973</v>
+        <v>7965</v>
       </c>
     </row>
     <row r="4137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4137" t="s">
-        <v>7974</v>
+        <v>7966</v>
       </c>
       <c r="B4137" t="s">
-        <v>7975</v>
+        <v>7967</v>
       </c>
     </row>
     <row r="4138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4138" t="s">
-        <v>7976</v>
+        <v>7968</v>
       </c>
       <c r="B4138" t="s">
-        <v>7977</v>
+        <v>7969</v>
       </c>
     </row>
     <row r="4139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4139" t="s">
-        <v>7978</v>
+        <v>7970</v>
       </c>
       <c r="B4139" t="s">
-        <v>7979</v>
+        <v>7971</v>
       </c>
     </row>
     <row r="4140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4140" t="s">
-        <v>7980</v>
+        <v>7972</v>
       </c>
       <c r="B4140" t="s">
-        <v>7981</v>
+        <v>7973</v>
       </c>
     </row>
     <row r="4141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4141" t="s">
-        <v>7982</v>
+        <v>7974</v>
       </c>
       <c r="B4141" t="s">
-        <v>7983</v>
+        <v>7975</v>
       </c>
     </row>
     <row r="4142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4142" t="s">
-        <v>7984</v>
+        <v>7976</v>
       </c>
       <c r="B4142" t="s">
-        <v>7985</v>
+        <v>7977</v>
       </c>
     </row>
     <row r="4143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4143" t="s">
-        <v>7986</v>
+        <v>7978</v>
       </c>
       <c r="B4143" t="s">
-        <v>7987</v>
+        <v>7979</v>
       </c>
     </row>
     <row r="4144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4144" t="s">
-        <v>7988</v>
+        <v>7980</v>
       </c>
       <c r="B4144" t="s">
-        <v>7989</v>
+        <v>7981</v>
       </c>
     </row>
     <row r="4145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4145" t="s">
-        <v>7990</v>
+        <v>7982</v>
       </c>
       <c r="B4145" t="s">
-        <v>7991</v>
+        <v>7983</v>
       </c>
     </row>
     <row r="4146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4146" t="s">
-        <v>7992</v>
+        <v>7984</v>
       </c>
       <c r="B4146" t="s">
-        <v>7993</v>
+        <v>7985</v>
       </c>
     </row>
     <row r="4147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4147" t="s">
-        <v>7994</v>
+        <v>7986</v>
       </c>
       <c r="B4147" t="s">
-        <v>7995</v>
+        <v>7987</v>
       </c>
     </row>
     <row r="4148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4148" t="s">
-        <v>7996</v>
+        <v>7988</v>
       </c>
       <c r="B4148" t="s">
-        <v>7997</v>
+        <v>7989</v>
       </c>
     </row>
     <row r="4149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4149" t="s">
-        <v>7998</v>
+        <v>7990</v>
       </c>
       <c r="B4149" t="s">
-        <v>7999</v>
+        <v>7991</v>
       </c>
     </row>
     <row r="4150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4150" t="s">
-        <v>8000</v>
+        <v>7992</v>
       </c>
       <c r="B4150" t="s">
-        <v>8001</v>
+        <v>7993</v>
       </c>
     </row>
     <row r="4151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4151" t="s">
-        <v>8002</v>
+        <v>7994</v>
       </c>
       <c r="B4151" t="s">
-        <v>8003</v>
+        <v>7995</v>
       </c>
     </row>
     <row r="4152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4152" t="s">
-        <v>8004</v>
+        <v>7996</v>
       </c>
       <c r="B4152" t="s">
-        <v>8005</v>
+        <v>7997</v>
       </c>
     </row>
     <row r="4153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4153" t="s">
-        <v>8006</v>
+        <v>7998</v>
       </c>
       <c r="B4153" t="s">
-        <v>8007</v>
+        <v>7999</v>
       </c>
     </row>
     <row r="4154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4154" t="s">
-        <v>8008</v>
+        <v>8000</v>
       </c>
       <c r="B4154" t="s">
-        <v>8009</v>
+        <v>8001</v>
       </c>
     </row>
     <row r="4155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4155" t="s">
-        <v>8010</v>
+        <v>8002</v>
       </c>
       <c r="B4155" t="s">
-        <v>8011</v>
+        <v>8003</v>
       </c>
     </row>
     <row r="4156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4156" t="s">
-        <v>8012</v>
+        <v>8004</v>
       </c>
       <c r="B4156" t="s">
-        <v>8013</v>
+        <v>8005</v>
       </c>
     </row>
     <row r="4157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4157" t="s">
-        <v>8014</v>
+        <v>8006</v>
       </c>
       <c r="B4157" t="s">
-        <v>8015</v>
+        <v>8007</v>
       </c>
     </row>
     <row r="4158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4158" t="s">
-        <v>8016</v>
+        <v>8008</v>
       </c>
       <c r="B4158" t="s">
-        <v>8017</v>
+        <v>8009</v>
       </c>
     </row>
     <row r="4159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4159" t="s">
-        <v>8018</v>
+        <v>8010</v>
       </c>
       <c r="B4159" t="s">
-        <v>8019</v>
+        <v>8011</v>
       </c>
     </row>
     <row r="4160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4160" t="s">
-        <v>8020</v>
+        <v>8012</v>
       </c>
       <c r="B4160" t="s">
-        <v>8021</v>
+        <v>8013</v>
       </c>
     </row>
     <row r="4161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4161" t="s">
-        <v>8022</v>
+        <v>8014</v>
       </c>
       <c r="B4161" t="s">
-        <v>8023</v>
+        <v>8015</v>
       </c>
     </row>
     <row r="4162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4162" t="s">
-        <v>8024</v>
+        <v>8016</v>
       </c>
       <c r="B4162" t="s">
-        <v>8025</v>
+        <v>8017</v>
       </c>
     </row>
     <row r="4163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4163" t="s">
-        <v>8026</v>
+        <v>8018</v>
       </c>
       <c r="B4163" t="s">
-        <v>8027</v>
+        <v>8019</v>
       </c>
     </row>
     <row r="4164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4164" t="s">
-        <v>8028</v>
+        <v>8020</v>
       </c>
       <c r="B4164" t="s">
-        <v>8029</v>
+        <v>8021</v>
       </c>
     </row>
     <row r="4165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4165" t="s">
-        <v>8030</v>
+        <v>8022</v>
       </c>
       <c r="B4165" t="s">
-        <v>8031</v>
+        <v>8023</v>
       </c>
     </row>
     <row r="4166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4166" t="s">
-        <v>8032</v>
+        <v>8024</v>
       </c>
       <c r="B4166" t="s">
-        <v>8033</v>
+        <v>8025</v>
       </c>
     </row>
     <row r="4167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4167" t="s">
-        <v>8034</v>
+        <v>8026</v>
       </c>
       <c r="B4167" t="s">
-        <v>8035</v>
+        <v>8027</v>
       </c>
     </row>
     <row r="4168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4168" t="s">
-        <v>8036</v>
+        <v>8028</v>
       </c>
       <c r="B4168" t="s">
-        <v>8037</v>
+        <v>8029</v>
       </c>
     </row>
     <row r="4169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4169" t="s">
-        <v>8038</v>
+        <v>8030</v>
       </c>
       <c r="B4169" t="s">
-        <v>8039</v>
+        <v>8031</v>
       </c>
     </row>
     <row r="4170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4170" t="s">
-        <v>8040</v>
+        <v>8032</v>
       </c>
       <c r="B4170" t="s">
-        <v>8041</v>
+        <v>8033</v>
       </c>
     </row>
     <row r="4171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4171" t="s">
-        <v>8042</v>
+        <v>8034</v>
       </c>
       <c r="B4171" t="s">
-        <v>8043</v>
+        <v>8035</v>
       </c>
     </row>
     <row r="4172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4172" t="s">
-        <v>8044</v>
+        <v>8036</v>
       </c>
       <c r="B4172" t="s">
-        <v>8045</v>
+        <v>8037</v>
       </c>
     </row>
     <row r="4173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4173" t="s">
-        <v>8046</v>
+        <v>8038</v>
       </c>
       <c r="B4173" t="s">
-        <v>8047</v>
+        <v>8039</v>
       </c>
     </row>
     <row r="4174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4174" t="s">
-        <v>8048</v>
+        <v>8040</v>
       </c>
       <c r="B4174" t="s">
-        <v>8049</v>
+        <v>8041</v>
       </c>
     </row>
     <row r="4175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4175" t="s">
-        <v>8050</v>
+        <v>8042</v>
       </c>
       <c r="B4175" t="s">
-        <v>8051</v>
+        <v>8043</v>
       </c>
     </row>
     <row r="4176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4176" t="s">
-        <v>8052</v>
+        <v>8044</v>
       </c>
       <c r="B4176" t="s">
-        <v>8053</v>
+        <v>8045</v>
       </c>
     </row>
     <row r="4177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4177" t="s">
-        <v>8054</v>
+        <v>8046</v>
       </c>
       <c r="B4177" t="s">
-        <v>8055</v>
+        <v>8047</v>
       </c>
     </row>
     <row r="4178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4178" t="s">
-        <v>8056</v>
+        <v>8048</v>
       </c>
       <c r="B4178" t="s">
-        <v>8057</v>
+        <v>8049</v>
       </c>
     </row>
     <row r="4179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4179" t="s">
-        <v>8058</v>
+        <v>8050</v>
       </c>
       <c r="B4179" t="s">
-        <v>8059</v>
+        <v>8051</v>
       </c>
     </row>
     <row r="4180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4180" t="s">
-        <v>8060</v>
+        <v>8052</v>
       </c>
       <c r="B4180" t="s">
-        <v>8061</v>
+        <v>8053</v>
       </c>
     </row>
     <row r="4181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4181" t="s">
-        <v>8062</v>
+        <v>8054</v>
       </c>
       <c r="B4181" t="s">
-        <v>8063</v>
+        <v>8055</v>
       </c>
     </row>
     <row r="4182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4182" t="s">
-        <v>8064</v>
+        <v>8056</v>
       </c>
       <c r="B4182" t="s">
-        <v>8065</v>
+        <v>8057</v>
       </c>
     </row>
     <row r="4183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4183" t="s">
-        <v>8066</v>
+        <v>8058</v>
       </c>
       <c r="B4183" t="s">
-        <v>8067</v>
+        <v>8059</v>
       </c>
     </row>
     <row r="4184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4184" t="s">
-        <v>8068</v>
+        <v>8060</v>
       </c>
       <c r="B4184" t="s">
-        <v>8069</v>
+        <v>8061</v>
       </c>
     </row>
     <row r="4185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4185" t="s">
-        <v>8070</v>
+        <v>8062</v>
       </c>
       <c r="B4185" t="s">
-        <v>8071</v>
+        <v>8063</v>
       </c>
     </row>
     <row r="4186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4186" t="s">
-        <v>8072</v>
+        <v>8064</v>
       </c>
       <c r="B4186" t="s">
-        <v>8073</v>
+        <v>8065</v>
       </c>
     </row>
     <row r="4187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4187" t="s">
-        <v>8074</v>
+        <v>8066</v>
       </c>
       <c r="B4187" t="s">
-        <v>8075</v>
+        <v>8067</v>
       </c>
     </row>
     <row r="4188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4188" t="s">
-        <v>8076</v>
+        <v>8068</v>
       </c>
       <c r="B4188" t="s">
-        <v>8077</v>
+        <v>8069</v>
       </c>
     </row>
     <row r="4189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4189" t="s">
-        <v>8078</v>
+        <v>8070</v>
       </c>
       <c r="B4189" t="s">
-        <v>8079</v>
+        <v>8071</v>
       </c>
     </row>
     <row r="4190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4190" t="s">
-        <v>8080</v>
+        <v>8072</v>
       </c>
       <c r="B4190" t="s">
-        <v>8081</v>
+        <v>8073</v>
       </c>
     </row>
     <row r="4191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4191" t="s">
-        <v>8082</v>
+        <v>8074</v>
       </c>
       <c r="B4191" t="s">
-        <v>8083</v>
+        <v>8075</v>
       </c>
     </row>
     <row r="4192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4192" t="s">
-        <v>8084</v>
+        <v>8076</v>
       </c>
       <c r="B4192" t="s">
-        <v>8085</v>
+        <v>8077</v>
       </c>
     </row>
     <row r="4193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4193" t="s">
-        <v>8086</v>
+        <v>8078</v>
       </c>
       <c r="B4193" t="s">
-        <v>8087</v>
+        <v>8079</v>
       </c>
     </row>
     <row r="4194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4194" t="s">
-        <v>8088</v>
+        <v>8080</v>
       </c>
       <c r="B4194" t="s">
-        <v>8089</v>
+        <v>8081</v>
       </c>
     </row>
     <row r="4195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4195" t="s">
-        <v>8090</v>
+        <v>8082</v>
       </c>
       <c r="B4195" t="s">
-        <v>8091</v>
+        <v>8083</v>
       </c>
     </row>
     <row r="4196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4196" t="s">
-        <v>8092</v>
+        <v>8084</v>
       </c>
       <c r="B4196" t="s">
-        <v>8093</v>
+        <v>8085</v>
       </c>
     </row>
     <row r="4197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4197" t="s">
-        <v>8094</v>
+        <v>8086</v>
       </c>
       <c r="B4197" t="s">
-        <v>8095</v>
+        <v>8087</v>
       </c>
     </row>
     <row r="4198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4198" t="s">
-        <v>8096</v>
+        <v>8088</v>
       </c>
       <c r="B4198" t="s">
-        <v>8097</v>
+        <v>8089</v>
       </c>
     </row>
     <row r="4199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4199" t="s">
-        <v>8098</v>
+        <v>8090</v>
       </c>
       <c r="B4199" t="s">
-        <v>8099</v>
+        <v>8091</v>
       </c>
     </row>
     <row r="4200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4200" t="s">
-        <v>8100</v>
+        <v>8092</v>
       </c>
       <c r="B4200" t="s">
-        <v>8101</v>
+        <v>8093</v>
       </c>
     </row>
     <row r="4201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4201" t="s">
-        <v>8102</v>
+        <v>8094</v>
       </c>
       <c r="B4201" t="s">
-        <v>8103</v>
+        <v>8095</v>
       </c>
     </row>
     <row r="4202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4202" t="s">
-        <v>8104</v>
+        <v>8096</v>
       </c>
       <c r="B4202" t="s">
-        <v>8105</v>
+        <v>8097</v>
       </c>
     </row>
     <row r="4203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4203" t="s">
-        <v>8106</v>
+        <v>8098</v>
       </c>
       <c r="B4203" t="s">
-        <v>8107</v>
+        <v>8099</v>
       </c>
     </row>
     <row r="4204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4204" t="s">
-        <v>8108</v>
+        <v>8100</v>
       </c>
       <c r="B4204" t="s">
-        <v>8109</v>
+        <v>8101</v>
       </c>
     </row>
     <row r="4205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4205" t="s">
-        <v>8110</v>
+        <v>8102</v>
       </c>
       <c r="B4205" t="s">
-        <v>8111</v>
+        <v>8103</v>
       </c>
     </row>
     <row r="4206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4206" t="s">
-        <v>8112</v>
+        <v>8104</v>
       </c>
       <c r="B4206" t="s">
-        <v>8113</v>
+        <v>8105</v>
       </c>
     </row>
     <row r="4207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4207" t="s">
-        <v>8114</v>
+        <v>8106</v>
       </c>
       <c r="B4207" t="s">
-        <v>8115</v>
+        <v>8107</v>
       </c>
     </row>
     <row r="4208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4208" t="s">
-        <v>8116</v>
+        <v>8108</v>
       </c>
       <c r="B4208" t="s">
-        <v>8117</v>
+        <v>8109</v>
       </c>
     </row>
     <row r="4209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4209" t="s">
-        <v>8118</v>
+        <v>8110</v>
       </c>
       <c r="B4209" t="s">
-        <v>8119</v>
+        <v>8111</v>
       </c>
     </row>
     <row r="4210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4210" t="s">
-        <v>8120</v>
+        <v>8112</v>
       </c>
       <c r="B4210" t="s">
-        <v>8121</v>
+        <v>8113</v>
       </c>
     </row>
     <row r="4211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4211" t="s">
-        <v>8122</v>
+        <v>8114</v>
       </c>
       <c r="B4211" t="s">
-        <v>8123</v>
+        <v>8115</v>
       </c>
     </row>
     <row r="4212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4212" t="s">
-        <v>8124</v>
+        <v>8116</v>
       </c>
       <c r="B4212" t="s">
-        <v>8125</v>
+        <v>8117</v>
       </c>
     </row>
     <row r="4213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4213" t="s">
-        <v>8126</v>
+        <v>8118</v>
       </c>
       <c r="B4213" t="s">
-        <v>8127</v>
+        <v>8119</v>
       </c>
     </row>
     <row r="4214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4214" t="s">
-        <v>8128</v>
+        <v>8120</v>
       </c>
       <c r="B4214" t="s">
-        <v>8129</v>
+        <v>8121</v>
       </c>
     </row>
     <row r="4215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4215" t="s">
-        <v>8130</v>
+        <v>8122</v>
       </c>
       <c r="B4215" t="s">
-        <v>8131</v>
+        <v>8123</v>
       </c>
     </row>
     <row r="4216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4216" t="s">
-        <v>8132</v>
+        <v>8124</v>
       </c>
       <c r="B4216" t="s">
-        <v>8133</v>
+        <v>8125</v>
       </c>
     </row>
     <row r="4217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4217" t="s">
-        <v>8134</v>
+        <v>8126</v>
       </c>
       <c r="B4217" t="s">
-        <v>8135</v>
+        <v>8127</v>
       </c>
     </row>
     <row r="4218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4218" t="s">
-        <v>8136</v>
+        <v>8128</v>
       </c>
       <c r="B4218" t="s">
-        <v>8137</v>
+        <v>8129</v>
       </c>
     </row>
     <row r="4219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4219" t="s">
-        <v>8138</v>
+        <v>8130</v>
       </c>
       <c r="B4219" t="s">
-        <v>8139</v>
+        <v>8131</v>
       </c>
     </row>
     <row r="4220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4220" t="s">
-        <v>8140</v>
+        <v>8132</v>
       </c>
       <c r="B4220" t="s">
-        <v>8141</v>
+        <v>8133</v>
       </c>
     </row>
     <row r="4221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4221" t="s">
-        <v>8142</v>
+        <v>8134</v>
       </c>
       <c r="B4221" t="s">
-        <v>8143</v>
+        <v>8135</v>
       </c>
     </row>
     <row r="4222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4222" t="s">
-        <v>8144</v>
+        <v>8136</v>
       </c>
       <c r="B4222" t="s">
-        <v>8145</v>
+        <v>8137</v>
       </c>
     </row>
     <row r="4223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4223" t="s">
-        <v>8146</v>
+        <v>8138</v>
       </c>
       <c r="B4223" t="s">
-        <v>8147</v>
+        <v>8139</v>
       </c>
     </row>
     <row r="4224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4224" t="s">
-        <v>8148</v>
+        <v>8140</v>
       </c>
       <c r="B4224" t="s">
-        <v>8149</v>
+        <v>8141</v>
       </c>
     </row>
     <row r="4225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4225" t="s">
-        <v>8150</v>
+        <v>8142</v>
       </c>
       <c r="B4225" t="s">
-        <v>8151</v>
+        <v>8143</v>
       </c>
     </row>
     <row r="4226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4226" t="s">
-        <v>8152</v>
+        <v>8144</v>
       </c>
       <c r="B4226" t="s">
-        <v>8153</v>
+        <v>8145</v>
       </c>
     </row>
     <row r="4227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4227" t="s">
-        <v>8154</v>
+        <v>8146</v>
       </c>
       <c r="B4227" t="s">
-        <v>8155</v>
+        <v>8147</v>
       </c>
     </row>
     <row r="4228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4228" t="s">
-        <v>8156</v>
+        <v>8148</v>
       </c>
       <c r="B4228" t="s">
-        <v>8157</v>
+        <v>8149</v>
       </c>
     </row>
     <row r="4229" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4229" t="s">
-        <v>8158</v>
+        <v>8150</v>
       </c>
       <c r="B4229" t="s">
-        <v>8159</v>
+        <v>8151</v>
       </c>
     </row>
     <row r="4230" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4230" t="s">
-        <v>8160</v>
+        <v>8152</v>
       </c>
       <c r="B4230" t="s">
-        <v>8161</v>
+        <v>8153</v>
       </c>
     </row>
     <row r="4231" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4231" t="s">
-        <v>8162</v>
+        <v>8154</v>
       </c>
       <c r="B4231" t="s">
-        <v>8163</v>
+        <v>8155</v>
       </c>
     </row>
     <row r="4232" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4232" t="s">
-        <v>8164</v>
+        <v>8156</v>
       </c>
       <c r="B4232" t="s">
-        <v>8165</v>
+        <v>8157</v>
       </c>
     </row>
     <row r="4233" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4233" t="s">
-        <v>8166</v>
+        <v>8158</v>
       </c>
       <c r="B4233" t="s">
-        <v>8167</v>
+        <v>8159</v>
       </c>
     </row>
     <row r="4234" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4234" t="s">
-        <v>8168</v>
+        <v>8160</v>
       </c>
       <c r="B4234" t="s">
-        <v>8169</v>
+        <v>8161</v>
       </c>
     </row>
     <row r="4235" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4235" t="s">
-        <v>8170</v>
+        <v>8162</v>
       </c>
       <c r="B4235" t="s">
-        <v>8171</v>
+        <v>8163</v>
       </c>
     </row>
     <row r="4236" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4236" t="s">
-        <v>8172</v>
+        <v>8164</v>
       </c>
       <c r="B4236" t="s">
-        <v>8173</v>
+        <v>8165</v>
       </c>
     </row>
     <row r="4237" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4237" t="s">
-        <v>8174</v>
+        <v>8166</v>
       </c>
       <c r="B4237" t="s">
-        <v>8175</v>
+        <v>8167</v>
       </c>
     </row>
     <row r="4238" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4238" t="s">
-        <v>8176</v>
+        <v>8168</v>
       </c>
       <c r="B4238" t="s">
-        <v>8177</v>
+        <v>8169</v>
       </c>
     </row>
     <row r="4239" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4239" t="s">
-        <v>8178</v>
+        <v>8170</v>
       </c>
       <c r="B4239" t="s">
-        <v>8179</v>
+        <v>8171</v>
       </c>
     </row>
     <row r="4240" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4240" t="s">
-        <v>8180</v>
+        <v>8172</v>
       </c>
       <c r="B4240" t="s">
-        <v>8181</v>
+        <v>8173</v>
       </c>
     </row>
     <row r="4241" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4241" t="s">
-        <v>8182</v>
+        <v>8174</v>
       </c>
       <c r="B4241" t="s">
-        <v>8183</v>
+        <v>8175</v>
       </c>
     </row>
     <row r="4242" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4242" t="s">
-        <v>8184</v>
+        <v>8176</v>
       </c>
       <c r="B4242" t="s">
-        <v>8185</v>
+        <v>8177</v>
       </c>
     </row>
     <row r="4243" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4243" t="s">
-        <v>8186</v>
+        <v>8178</v>
       </c>
       <c r="B4243" t="s">
-        <v>8187</v>
+        <v>8179</v>
       </c>
     </row>
     <row r="4244" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4244" t="s">
-        <v>8188</v>
+        <v>8180</v>
       </c>
       <c r="B4244" t="s">
-        <v>8189</v>
+        <v>8181</v>
       </c>
     </row>
     <row r="4245" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4245" t="s">
-        <v>8190</v>
+        <v>8182</v>
       </c>
       <c r="B4245" t="s">
-        <v>8191</v>
+        <v>8183</v>
       </c>
     </row>
     <row r="4246" spans="1:2" x14ac:dyDescent="0.25">
@@ -61236,7 +61236,7 @@
         <v>154</v>
       </c>
       <c r="B4246" t="s">
-        <v>8192</v>
+        <v>8184</v>
       </c>
     </row>
     <row r="4247" spans="1:2" x14ac:dyDescent="0.25">
@@ -61244,7 +61244,7 @@
         <v>156</v>
       </c>
       <c r="B4247" t="s">
-        <v>8193</v>
+        <v>8185</v>
       </c>
     </row>
     <row r="4248" spans="1:2" x14ac:dyDescent="0.25">
@@ -61252,7 +61252,7 @@
         <v>158</v>
       </c>
       <c r="B4248" t="s">
-        <v>8194</v>
+        <v>8186</v>
       </c>
     </row>
     <row r="4249" spans="1:2" x14ac:dyDescent="0.25">
@@ -61260,359 +61260,359 @@
         <v>160</v>
       </c>
       <c r="B4249" t="s">
-        <v>8195</v>
+        <v>8187</v>
       </c>
     </row>
     <row r="4250" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4250" t="s">
-        <v>8196</v>
+        <v>8188</v>
       </c>
       <c r="B4250" t="s">
-        <v>8197</v>
+        <v>8189</v>
       </c>
     </row>
     <row r="4251" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4251" t="s">
-        <v>8198</v>
+        <v>8190</v>
       </c>
       <c r="B4251" t="s">
-        <v>8199</v>
+        <v>8191</v>
       </c>
     </row>
     <row r="4252" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4252" t="s">
-        <v>8200</v>
+        <v>8192</v>
       </c>
       <c r="B4252" t="s">
-        <v>8201</v>
+        <v>8193</v>
       </c>
     </row>
     <row r="4253" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4253" t="s">
-        <v>8202</v>
+        <v>8194</v>
       </c>
       <c r="B4253" t="s">
-        <v>8203</v>
+        <v>8195</v>
       </c>
     </row>
     <row r="4254" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4254" t="s">
-        <v>8204</v>
+        <v>8196</v>
       </c>
       <c r="B4254" t="s">
-        <v>8205</v>
+        <v>8197</v>
       </c>
     </row>
     <row r="4255" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4255" t="s">
-        <v>8206</v>
+        <v>8198</v>
       </c>
       <c r="B4255" t="s">
-        <v>8207</v>
+        <v>8199</v>
       </c>
     </row>
     <row r="4256" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4256" t="s">
-        <v>8208</v>
+        <v>8200</v>
       </c>
       <c r="B4256" t="s">
-        <v>8209</v>
+        <v>8201</v>
       </c>
     </row>
     <row r="4257" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4257" t="s">
-        <v>8210</v>
+        <v>8202</v>
       </c>
       <c r="B4257" t="s">
-        <v>8211</v>
+        <v>8203</v>
       </c>
     </row>
     <row r="4258" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4258" t="s">
-        <v>8212</v>
+        <v>8204</v>
       </c>
       <c r="B4258" t="s">
-        <v>8213</v>
+        <v>8205</v>
       </c>
     </row>
     <row r="4259" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4259" t="s">
-        <v>8214</v>
+        <v>8206</v>
       </c>
       <c r="B4259" t="s">
-        <v>8215</v>
+        <v>8207</v>
       </c>
     </row>
     <row r="4260" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4260" t="s">
-        <v>8216</v>
+        <v>8208</v>
       </c>
       <c r="B4260" t="s">
-        <v>8217</v>
+        <v>8209</v>
       </c>
     </row>
     <row r="4261" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4261" t="s">
-        <v>8218</v>
+        <v>8210</v>
       </c>
       <c r="B4261" t="s">
-        <v>8219</v>
+        <v>8211</v>
       </c>
     </row>
     <row r="4262" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4262" t="s">
-        <v>8220</v>
+        <v>8212</v>
       </c>
       <c r="B4262" t="s">
-        <v>8221</v>
+        <v>8213</v>
       </c>
     </row>
     <row r="4263" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4263" t="s">
-        <v>8222</v>
+        <v>8214</v>
       </c>
       <c r="B4263" t="s">
-        <v>8223</v>
+        <v>8215</v>
       </c>
     </row>
     <row r="4264" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4264" t="s">
-        <v>8224</v>
+        <v>8216</v>
       </c>
       <c r="B4264" t="s">
-        <v>8225</v>
+        <v>8217</v>
       </c>
     </row>
     <row r="4265" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4265" t="s">
-        <v>8226</v>
+        <v>8218</v>
       </c>
       <c r="B4265" t="s">
-        <v>8227</v>
+        <v>8219</v>
       </c>
     </row>
     <row r="4266" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4266" t="s">
-        <v>8228</v>
+        <v>8220</v>
       </c>
       <c r="B4266" t="s">
-        <v>8229</v>
+        <v>8221</v>
       </c>
     </row>
     <row r="4267" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4267" t="s">
-        <v>8230</v>
+        <v>8222</v>
       </c>
       <c r="B4267" t="s">
-        <v>8231</v>
+        <v>8223</v>
       </c>
     </row>
     <row r="4268" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4268" t="s">
-        <v>8232</v>
+        <v>8224</v>
       </c>
       <c r="B4268" t="s">
-        <v>8233</v>
+        <v>8225</v>
       </c>
     </row>
     <row r="4269" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4269" t="s">
-        <v>8234</v>
+        <v>8226</v>
       </c>
       <c r="B4269" t="s">
-        <v>8235</v>
+        <v>8227</v>
       </c>
     </row>
     <row r="4270" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4270" t="s">
-        <v>8788</v>
+        <v>8780</v>
       </c>
       <c r="B4270" t="s">
-        <v>8792</v>
+        <v>8784</v>
       </c>
     </row>
     <row r="4271" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4271" t="s">
-        <v>8789</v>
+        <v>8781</v>
       </c>
       <c r="B4271" t="s">
-        <v>8792</v>
+        <v>8784</v>
       </c>
     </row>
     <row r="4272" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4272" t="s">
-        <v>8790</v>
+        <v>8782</v>
       </c>
       <c r="B4272" t="s">
-        <v>8792</v>
+        <v>8784</v>
       </c>
     </row>
     <row r="4273" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4273" t="s">
-        <v>8791</v>
+        <v>8783</v>
       </c>
       <c r="B4273" t="s">
-        <v>8792</v>
+        <v>8784</v>
       </c>
     </row>
     <row r="4274" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4274" t="s">
-        <v>8236</v>
+        <v>8228</v>
       </c>
       <c r="B4274" t="s">
-        <v>8237</v>
+        <v>8229</v>
       </c>
     </row>
     <row r="4275" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4275" t="s">
-        <v>8238</v>
+        <v>8230</v>
       </c>
       <c r="B4275" t="s">
-        <v>8239</v>
+        <v>8231</v>
       </c>
     </row>
     <row r="4276" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4276" t="s">
-        <v>8240</v>
+        <v>8232</v>
       </c>
       <c r="B4276" t="s">
-        <v>8241</v>
+        <v>8233</v>
       </c>
     </row>
     <row r="4277" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4277" t="s">
-        <v>8242</v>
+        <v>8234</v>
       </c>
       <c r="B4277" t="s">
-        <v>8243</v>
+        <v>8235</v>
       </c>
     </row>
     <row r="4278" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4278" t="s">
-        <v>8244</v>
+        <v>8236</v>
       </c>
       <c r="B4278" t="s">
-        <v>8245</v>
+        <v>8237</v>
       </c>
     </row>
     <row r="4279" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4279" t="s">
-        <v>8246</v>
+        <v>8238</v>
       </c>
       <c r="B4279" t="s">
-        <v>8247</v>
+        <v>8239</v>
       </c>
     </row>
     <row r="4280" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4280" t="s">
-        <v>8248</v>
+        <v>8240</v>
       </c>
       <c r="B4280" t="s">
-        <v>8249</v>
+        <v>8241</v>
       </c>
     </row>
     <row r="4281" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4281" t="s">
-        <v>8250</v>
+        <v>8242</v>
       </c>
       <c r="B4281" t="s">
-        <v>8251</v>
+        <v>8243</v>
       </c>
     </row>
     <row r="4282" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4282" t="s">
-        <v>8252</v>
+        <v>8244</v>
       </c>
       <c r="B4282" t="s">
-        <v>8253</v>
+        <v>8245</v>
       </c>
     </row>
     <row r="4283" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4283" t="s">
-        <v>8254</v>
+        <v>8246</v>
       </c>
       <c r="B4283" t="s">
-        <v>8255</v>
+        <v>8247</v>
       </c>
     </row>
     <row r="4284" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4284" t="s">
-        <v>8256</v>
+        <v>8248</v>
       </c>
       <c r="B4284" t="s">
-        <v>8257</v>
+        <v>8249</v>
       </c>
     </row>
     <row r="4285" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4285" t="s">
-        <v>8258</v>
+        <v>8250</v>
       </c>
       <c r="B4285" t="s">
-        <v>8259</v>
+        <v>8251</v>
       </c>
     </row>
     <row r="4286" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4286" t="s">
-        <v>8260</v>
+        <v>8252</v>
       </c>
       <c r="B4286" t="s">
-        <v>8261</v>
+        <v>8253</v>
       </c>
     </row>
     <row r="4287" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4287" t="s">
-        <v>8262</v>
+        <v>8254</v>
       </c>
       <c r="B4287" t="s">
-        <v>8263</v>
+        <v>8255</v>
       </c>
     </row>
     <row r="4288" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4288" t="s">
-        <v>8264</v>
+        <v>8256</v>
       </c>
       <c r="B4288" t="s">
-        <v>8265</v>
+        <v>8257</v>
       </c>
     </row>
     <row r="4289" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4289" t="s">
-        <v>8266</v>
+        <v>8258</v>
       </c>
       <c r="B4289" t="s">
-        <v>8267</v>
+        <v>8259</v>
       </c>
     </row>
     <row r="4290" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4290" t="s">
-        <v>8268</v>
+        <v>8260</v>
       </c>
       <c r="B4290" t="s">
-        <v>8269</v>
+        <v>8261</v>
       </c>
     </row>
     <row r="4291" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4291" t="s">
-        <v>8270</v>
+        <v>8262</v>
       </c>
       <c r="B4291" t="s">
-        <v>8271</v>
+        <v>8263</v>
       </c>
     </row>
     <row r="4292" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4292" t="s">
-        <v>8272</v>
+        <v>8264</v>
       </c>
       <c r="B4292" t="s">
-        <v>8273</v>
+        <v>8265</v>
       </c>
     </row>
     <row r="4293" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4293" t="s">
-        <v>8274</v>
+        <v>8266</v>
       </c>
       <c r="B4293" t="s">
-        <v>8275</v>
+        <v>8267</v>
       </c>
     </row>
     <row r="4294" spans="1:2" x14ac:dyDescent="0.25">
@@ -61620,7 +61620,7 @@
         <v>#N/A</v>
       </c>
       <c r="B4294" t="s">
-        <v>8276</v>
+        <v>8268</v>
       </c>
     </row>
     <row r="4295" spans="1:2" x14ac:dyDescent="0.25">
@@ -61628,7 +61628,7 @@
         <v>#N/A</v>
       </c>
       <c r="B4295" t="s">
-        <v>8277</v>
+        <v>8269</v>
       </c>
     </row>
     <row r="4296" spans="1:2" x14ac:dyDescent="0.25">
@@ -61636,7 +61636,7 @@
         <v>#N/A</v>
       </c>
       <c r="B4296" t="s">
-        <v>8278</v>
+        <v>8270</v>
       </c>
     </row>
     <row r="4297" spans="1:2" x14ac:dyDescent="0.25">
@@ -61644,7 +61644,7 @@
         <v>#N/A</v>
       </c>
       <c r="B4297" t="s">
-        <v>8279</v>
+        <v>8271</v>
       </c>
     </row>
     <row r="4298" spans="1:2" x14ac:dyDescent="0.25">
@@ -61652,7 +61652,7 @@
         <v>#N/A</v>
       </c>
       <c r="B4298" t="s">
-        <v>8280</v>
+        <v>8272</v>
       </c>
     </row>
     <row r="4299" spans="1:2" x14ac:dyDescent="0.25">
@@ -61660,7 +61660,7 @@
         <v>#N/A</v>
       </c>
       <c r="B4299" t="s">
-        <v>8281</v>
+        <v>8273</v>
       </c>
     </row>
     <row r="4300" spans="1:2" x14ac:dyDescent="0.25">
@@ -61668,7 +61668,7 @@
         <v>#N/A</v>
       </c>
       <c r="B4300" t="s">
-        <v>8282</v>
+        <v>8274</v>
       </c>
     </row>
     <row r="4301" spans="1:2" x14ac:dyDescent="0.25">
@@ -61676,7 +61676,7 @@
         <v>#N/A</v>
       </c>
       <c r="B4301" t="s">
-        <v>8283</v>
+        <v>8275</v>
       </c>
     </row>
     <row r="4302" spans="1:2" x14ac:dyDescent="0.25">
@@ -61684,7 +61684,7 @@
         <v>154</v>
       </c>
       <c r="B4302" t="s">
-        <v>8284</v>
+        <v>8276</v>
       </c>
     </row>
     <row r="4303" spans="1:2" x14ac:dyDescent="0.25">
@@ -61692,7 +61692,7 @@
         <v>156</v>
       </c>
       <c r="B4303" t="s">
-        <v>8285</v>
+        <v>8277</v>
       </c>
     </row>
     <row r="4304" spans="1:2" x14ac:dyDescent="0.25">
@@ -61700,7 +61700,7 @@
         <v>158</v>
       </c>
       <c r="B4304" t="s">
-        <v>8286</v>
+        <v>8278</v>
       </c>
     </row>
     <row r="4305" spans="1:2" x14ac:dyDescent="0.25">
@@ -61708,7 +61708,7 @@
         <v>160</v>
       </c>
       <c r="B4305" t="s">
-        <v>8287</v>
+        <v>8279</v>
       </c>
     </row>
     <row r="4306" spans="1:2" x14ac:dyDescent="0.25">
@@ -61716,7 +61716,7 @@
         <v>154</v>
       </c>
       <c r="B4306" t="s">
-        <v>8288</v>
+        <v>8280</v>
       </c>
     </row>
     <row r="4307" spans="1:2" x14ac:dyDescent="0.25">
@@ -61724,7 +61724,7 @@
         <v>156</v>
       </c>
       <c r="B4307" t="s">
-        <v>8289</v>
+        <v>8281</v>
       </c>
     </row>
     <row r="4308" spans="1:2" x14ac:dyDescent="0.25">
@@ -61732,7 +61732,7 @@
         <v>158</v>
       </c>
       <c r="B4308" t="s">
-        <v>8290</v>
+        <v>8282</v>
       </c>
     </row>
     <row r="4309" spans="1:2" x14ac:dyDescent="0.25">
@@ -61740,7 +61740,7 @@
         <v>160</v>
       </c>
       <c r="B4309" t="s">
-        <v>8291</v>
+        <v>8283</v>
       </c>
     </row>
     <row r="4310" spans="1:2" x14ac:dyDescent="0.25">
@@ -61748,7 +61748,7 @@
         <v>154</v>
       </c>
       <c r="B4310" t="s">
-        <v>8292</v>
+        <v>8284</v>
       </c>
     </row>
     <row r="4311" spans="1:2" x14ac:dyDescent="0.25">
@@ -61756,7 +61756,7 @@
         <v>156</v>
       </c>
       <c r="B4311" t="s">
-        <v>8293</v>
+        <v>8285</v>
       </c>
     </row>
     <row r="4312" spans="1:2" x14ac:dyDescent="0.25">
@@ -61764,7 +61764,7 @@
         <v>158</v>
       </c>
       <c r="B4312" t="s">
-        <v>8294</v>
+        <v>8286</v>
       </c>
     </row>
     <row r="4313" spans="1:2" x14ac:dyDescent="0.25">
@@ -61772,7 +61772,7 @@
         <v>160</v>
       </c>
       <c r="B4313" t="s">
-        <v>8295</v>
+        <v>8287</v>
       </c>
     </row>
     <row r="4314" spans="1:2" x14ac:dyDescent="0.25">
@@ -61780,7 +61780,7 @@
         <v>154</v>
       </c>
       <c r="B4314" t="s">
-        <v>8296</v>
+        <v>8288</v>
       </c>
     </row>
     <row r="4315" spans="1:2" x14ac:dyDescent="0.25">
@@ -61788,7 +61788,7 @@
         <v>156</v>
       </c>
       <c r="B4315" t="s">
-        <v>8297</v>
+        <v>8289</v>
       </c>
     </row>
     <row r="4316" spans="1:2" x14ac:dyDescent="0.25">
@@ -61796,7 +61796,7 @@
         <v>158</v>
       </c>
       <c r="B4316" t="s">
-        <v>8298</v>
+        <v>8290</v>
       </c>
     </row>
     <row r="4317" spans="1:2" x14ac:dyDescent="0.25">
@@ -61804,7 +61804,7 @@
         <v>160</v>
       </c>
       <c r="B4317" t="s">
-        <v>8299</v>
+        <v>8291</v>
       </c>
     </row>
     <row r="4318" spans="1:2" x14ac:dyDescent="0.25">
@@ -61812,7 +61812,7 @@
         <v>154</v>
       </c>
       <c r="B4318" t="s">
-        <v>8300</v>
+        <v>8292</v>
       </c>
     </row>
     <row r="4319" spans="1:2" x14ac:dyDescent="0.25">
@@ -61820,7 +61820,7 @@
         <v>156</v>
       </c>
       <c r="B4319" t="s">
-        <v>8301</v>
+        <v>8293</v>
       </c>
     </row>
     <row r="4320" spans="1:2" x14ac:dyDescent="0.25">
@@ -61828,7 +61828,7 @@
         <v>158</v>
       </c>
       <c r="B4320" t="s">
-        <v>8302</v>
+        <v>8294</v>
       </c>
     </row>
     <row r="4321" spans="1:2" x14ac:dyDescent="0.25">
@@ -61836,7 +61836,7 @@
         <v>160</v>
       </c>
       <c r="B4321" t="s">
-        <v>8303</v>
+        <v>8295</v>
       </c>
     </row>
     <row r="4322" spans="1:2" x14ac:dyDescent="0.25">
@@ -61844,7 +61844,7 @@
         <v>154</v>
       </c>
       <c r="B4322" t="s">
-        <v>8304</v>
+        <v>8296</v>
       </c>
     </row>
     <row r="4323" spans="1:2" x14ac:dyDescent="0.25">
@@ -61852,7 +61852,7 @@
         <v>156</v>
       </c>
       <c r="B4323" t="s">
-        <v>8305</v>
+        <v>8297</v>
       </c>
     </row>
     <row r="4324" spans="1:2" x14ac:dyDescent="0.25">
@@ -61860,7 +61860,7 @@
         <v>158</v>
       </c>
       <c r="B4324" t="s">
-        <v>8306</v>
+        <v>8298</v>
       </c>
     </row>
     <row r="4325" spans="1:2" x14ac:dyDescent="0.25">
@@ -61868,1383 +61868,1383 @@
         <v>160</v>
       </c>
       <c r="B4325" t="s">
-        <v>8307</v>
+        <v>8299</v>
       </c>
     </row>
     <row r="4326" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4326" t="s">
-        <v>8308</v>
+        <v>8300</v>
       </c>
       <c r="B4326" t="s">
-        <v>8309</v>
+        <v>8301</v>
       </c>
     </row>
     <row r="4327" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4327" t="s">
-        <v>8310</v>
+        <v>8302</v>
       </c>
       <c r="B4327" t="s">
-        <v>8311</v>
+        <v>8303</v>
       </c>
     </row>
     <row r="4328" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4328" t="s">
-        <v>8312</v>
+        <v>8304</v>
       </c>
       <c r="B4328" t="s">
-        <v>8313</v>
+        <v>8305</v>
       </c>
     </row>
     <row r="4329" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4329" t="s">
-        <v>8314</v>
+        <v>8306</v>
       </c>
       <c r="B4329" t="s">
-        <v>8315</v>
+        <v>8307</v>
       </c>
     </row>
     <row r="4330" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4330" t="s">
-        <v>8316</v>
+        <v>8308</v>
       </c>
       <c r="B4330" t="s">
-        <v>8317</v>
+        <v>8309</v>
       </c>
     </row>
     <row r="4331" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4331" t="s">
-        <v>8318</v>
+        <v>8310</v>
       </c>
       <c r="B4331" t="s">
-        <v>8319</v>
+        <v>8311</v>
       </c>
     </row>
     <row r="4332" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4332" t="s">
-        <v>8320</v>
+        <v>8312</v>
       </c>
       <c r="B4332" t="s">
-        <v>8321</v>
+        <v>8313</v>
       </c>
     </row>
     <row r="4333" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4333" t="s">
-        <v>8322</v>
+        <v>8314</v>
       </c>
       <c r="B4333" t="s">
-        <v>8323</v>
+        <v>8315</v>
       </c>
     </row>
     <row r="4334" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4334" t="s">
-        <v>8324</v>
+        <v>8316</v>
       </c>
       <c r="B4334" t="s">
-        <v>8325</v>
+        <v>8317</v>
       </c>
     </row>
     <row r="4335" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4335" t="s">
-        <v>8326</v>
+        <v>8318</v>
       </c>
       <c r="B4335" t="s">
-        <v>8327</v>
+        <v>8319</v>
       </c>
     </row>
     <row r="4336" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4336" t="s">
-        <v>8328</v>
+        <v>8320</v>
       </c>
       <c r="B4336" t="s">
-        <v>8329</v>
+        <v>8321</v>
       </c>
     </row>
     <row r="4337" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4337" t="s">
-        <v>8330</v>
+        <v>8322</v>
       </c>
       <c r="B4337" t="s">
-        <v>8331</v>
+        <v>8323</v>
       </c>
     </row>
     <row r="4338" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4338" t="s">
-        <v>8332</v>
+        <v>8324</v>
       </c>
       <c r="B4338" t="s">
-        <v>8333</v>
+        <v>8325</v>
       </c>
     </row>
     <row r="4339" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4339" t="s">
-        <v>8334</v>
+        <v>8326</v>
       </c>
       <c r="B4339" t="s">
-        <v>8335</v>
+        <v>8327</v>
       </c>
     </row>
     <row r="4340" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4340" t="s">
-        <v>8336</v>
+        <v>8328</v>
       </c>
       <c r="B4340" t="s">
-        <v>8337</v>
+        <v>8329</v>
       </c>
     </row>
     <row r="4341" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4341" t="s">
-        <v>8338</v>
+        <v>8330</v>
       </c>
       <c r="B4341" t="s">
-        <v>8339</v>
+        <v>8331</v>
       </c>
     </row>
     <row r="4342" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4342" t="s">
-        <v>8340</v>
+        <v>8332</v>
       </c>
       <c r="B4342" t="s">
-        <v>8341</v>
+        <v>8333</v>
       </c>
     </row>
     <row r="4343" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4343" t="s">
-        <v>8342</v>
+        <v>8334</v>
       </c>
       <c r="B4343" t="s">
-        <v>8343</v>
+        <v>8335</v>
       </c>
     </row>
     <row r="4344" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4344" t="s">
-        <v>8344</v>
+        <v>8336</v>
       </c>
       <c r="B4344" t="s">
-        <v>8345</v>
+        <v>8337</v>
       </c>
     </row>
     <row r="4345" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4345" t="s">
-        <v>8346</v>
+        <v>8338</v>
       </c>
       <c r="B4345" t="s">
-        <v>8347</v>
+        <v>8339</v>
       </c>
     </row>
     <row r="4346" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4346" t="s">
-        <v>8348</v>
+        <v>8340</v>
       </c>
       <c r="B4346" t="s">
-        <v>8349</v>
+        <v>8341</v>
       </c>
     </row>
     <row r="4347" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4347" t="s">
-        <v>8350</v>
+        <v>8342</v>
       </c>
       <c r="B4347" t="s">
-        <v>8351</v>
+        <v>8343</v>
       </c>
     </row>
     <row r="4348" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4348" t="s">
-        <v>8352</v>
+        <v>8344</v>
       </c>
       <c r="B4348" t="s">
-        <v>8353</v>
+        <v>8345</v>
       </c>
     </row>
     <row r="4349" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4349" t="s">
-        <v>8354</v>
+        <v>8346</v>
       </c>
       <c r="B4349" t="s">
-        <v>8355</v>
+        <v>8347</v>
       </c>
     </row>
     <row r="4350" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4350" t="s">
-        <v>8356</v>
+        <v>8348</v>
       </c>
       <c r="B4350" t="s">
-        <v>8357</v>
+        <v>8349</v>
       </c>
     </row>
     <row r="4351" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4351" t="s">
-        <v>8358</v>
+        <v>8350</v>
       </c>
       <c r="B4351" t="s">
-        <v>8359</v>
+        <v>8351</v>
       </c>
     </row>
     <row r="4352" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4352" t="s">
-        <v>8360</v>
+        <v>8352</v>
       </c>
       <c r="B4352" t="s">
-        <v>8361</v>
+        <v>8353</v>
       </c>
     </row>
     <row r="4353" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4353" t="s">
-        <v>8362</v>
+        <v>8354</v>
       </c>
       <c r="B4353" t="s">
-        <v>8363</v>
+        <v>8355</v>
       </c>
     </row>
     <row r="4354" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4354" t="s">
-        <v>8364</v>
+        <v>8356</v>
       </c>
       <c r="B4354" t="s">
-        <v>8365</v>
+        <v>8357</v>
       </c>
     </row>
     <row r="4355" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4355" t="s">
-        <v>8366</v>
+        <v>8358</v>
       </c>
       <c r="B4355" t="s">
-        <v>8367</v>
+        <v>8359</v>
       </c>
     </row>
     <row r="4356" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4356" t="s">
-        <v>8368</v>
+        <v>8360</v>
       </c>
       <c r="B4356" t="s">
-        <v>8369</v>
+        <v>8361</v>
       </c>
     </row>
     <row r="4357" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4357" t="s">
-        <v>8370</v>
+        <v>8362</v>
       </c>
       <c r="B4357" t="s">
-        <v>8371</v>
+        <v>8363</v>
       </c>
     </row>
     <row r="4358" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4358" t="s">
-        <v>8372</v>
+        <v>8364</v>
       </c>
       <c r="B4358" t="s">
-        <v>8373</v>
+        <v>8365</v>
       </c>
     </row>
     <row r="4359" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4359" t="s">
-        <v>8374</v>
+        <v>8366</v>
       </c>
       <c r="B4359" t="s">
-        <v>8375</v>
+        <v>8367</v>
       </c>
     </row>
     <row r="4360" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4360" t="s">
-        <v>8376</v>
+        <v>8368</v>
       </c>
       <c r="B4360" t="s">
-        <v>8377</v>
+        <v>8369</v>
       </c>
     </row>
     <row r="4361" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4361" t="s">
-        <v>8378</v>
+        <v>8370</v>
       </c>
       <c r="B4361" t="s">
-        <v>8379</v>
+        <v>8371</v>
       </c>
     </row>
     <row r="4362" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4362" t="s">
-        <v>8380</v>
+        <v>8372</v>
       </c>
       <c r="B4362" t="s">
-        <v>8381</v>
+        <v>8373</v>
       </c>
     </row>
     <row r="4363" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4363" t="s">
-        <v>8382</v>
+        <v>8374</v>
       </c>
       <c r="B4363" t="s">
-        <v>8383</v>
+        <v>8375</v>
       </c>
     </row>
     <row r="4364" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4364" t="s">
-        <v>8384</v>
+        <v>8376</v>
       </c>
       <c r="B4364" t="s">
-        <v>8385</v>
+        <v>8377</v>
       </c>
     </row>
     <row r="4365" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4365" t="s">
-        <v>8386</v>
+        <v>8378</v>
       </c>
       <c r="B4365" t="s">
-        <v>8387</v>
+        <v>8379</v>
       </c>
     </row>
     <row r="4366" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4366" t="s">
-        <v>8388</v>
+        <v>8380</v>
       </c>
       <c r="B4366" t="s">
-        <v>8389</v>
+        <v>8381</v>
       </c>
     </row>
     <row r="4367" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4367" t="s">
-        <v>8390</v>
+        <v>8382</v>
       </c>
       <c r="B4367" t="s">
-        <v>8391</v>
+        <v>8383</v>
       </c>
     </row>
     <row r="4368" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4368" t="s">
-        <v>8392</v>
+        <v>8384</v>
       </c>
       <c r="B4368" t="s">
-        <v>8393</v>
+        <v>8385</v>
       </c>
     </row>
     <row r="4369" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4369" t="s">
-        <v>8394</v>
+        <v>8386</v>
       </c>
       <c r="B4369" t="s">
-        <v>8395</v>
+        <v>8387</v>
       </c>
     </row>
     <row r="4370" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4370" t="s">
-        <v>8396</v>
+        <v>8388</v>
       </c>
       <c r="B4370" t="s">
-        <v>8397</v>
+        <v>8389</v>
       </c>
     </row>
     <row r="4371" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4371" t="s">
-        <v>8398</v>
+        <v>8390</v>
       </c>
       <c r="B4371" t="s">
-        <v>8399</v>
+        <v>8391</v>
       </c>
     </row>
     <row r="4372" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4372" t="s">
-        <v>8400</v>
+        <v>8392</v>
       </c>
       <c r="B4372" t="s">
-        <v>8401</v>
+        <v>8393</v>
       </c>
     </row>
     <row r="4373" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4373" t="s">
-        <v>8402</v>
+        <v>8394</v>
       </c>
       <c r="B4373" t="s">
-        <v>8403</v>
+        <v>8395</v>
       </c>
     </row>
     <row r="4374" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4374" t="s">
-        <v>8404</v>
+        <v>8396</v>
       </c>
       <c r="B4374" t="s">
-        <v>8405</v>
+        <v>8397</v>
       </c>
     </row>
     <row r="4375" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4375" t="s">
-        <v>8406</v>
+        <v>8398</v>
       </c>
       <c r="B4375" t="s">
-        <v>8407</v>
+        <v>8399</v>
       </c>
     </row>
     <row r="4376" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4376" t="s">
-        <v>8408</v>
+        <v>8400</v>
       </c>
       <c r="B4376" t="s">
-        <v>8409</v>
+        <v>8401</v>
       </c>
     </row>
     <row r="4377" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4377" t="s">
-        <v>8410</v>
+        <v>8402</v>
       </c>
       <c r="B4377" t="s">
-        <v>8411</v>
+        <v>8403</v>
       </c>
     </row>
     <row r="4378" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4378" t="s">
-        <v>8412</v>
+        <v>8404</v>
       </c>
       <c r="B4378" t="s">
-        <v>8413</v>
+        <v>8405</v>
       </c>
     </row>
     <row r="4379" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4379" t="s">
-        <v>8414</v>
+        <v>8406</v>
       </c>
       <c r="B4379" t="s">
-        <v>8415</v>
+        <v>8407</v>
       </c>
     </row>
     <row r="4380" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4380" t="s">
-        <v>8416</v>
+        <v>8408</v>
       </c>
       <c r="B4380" t="s">
-        <v>8417</v>
+        <v>8409</v>
       </c>
     </row>
     <row r="4381" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4381" t="s">
-        <v>8418</v>
+        <v>8410</v>
       </c>
       <c r="B4381" t="s">
-        <v>8419</v>
+        <v>8411</v>
       </c>
     </row>
     <row r="4382" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4382" t="s">
-        <v>8420</v>
+        <v>8412</v>
       </c>
       <c r="B4382" t="s">
-        <v>8421</v>
+        <v>8413</v>
       </c>
     </row>
     <row r="4383" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4383" t="s">
-        <v>8422</v>
+        <v>8414</v>
       </c>
       <c r="B4383" t="s">
-        <v>8423</v>
+        <v>8415</v>
       </c>
     </row>
     <row r="4384" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4384" t="s">
-        <v>8424</v>
+        <v>8416</v>
       </c>
       <c r="B4384" t="s">
-        <v>8425</v>
+        <v>8417</v>
       </c>
     </row>
     <row r="4385" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4385" t="s">
-        <v>8426</v>
+        <v>8418</v>
       </c>
       <c r="B4385" t="s">
-        <v>8427</v>
+        <v>8419</v>
       </c>
     </row>
     <row r="4386" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4386" t="s">
-        <v>8428</v>
+        <v>8420</v>
       </c>
       <c r="B4386" t="s">
-        <v>8429</v>
+        <v>8421</v>
       </c>
     </row>
     <row r="4387" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4387" t="s">
-        <v>8430</v>
+        <v>8422</v>
       </c>
       <c r="B4387" t="s">
-        <v>8431</v>
+        <v>8423</v>
       </c>
     </row>
     <row r="4388" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4388" t="s">
-        <v>8432</v>
+        <v>8424</v>
       </c>
       <c r="B4388" t="s">
-        <v>8433</v>
+        <v>8425</v>
       </c>
     </row>
     <row r="4389" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4389" t="s">
-        <v>8434</v>
+        <v>8426</v>
       </c>
       <c r="B4389" t="s">
-        <v>8435</v>
+        <v>8427</v>
       </c>
     </row>
     <row r="4390" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4390" t="s">
-        <v>8436</v>
+        <v>8428</v>
       </c>
       <c r="B4390" t="s">
-        <v>8437</v>
+        <v>8429</v>
       </c>
     </row>
     <row r="4391" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4391" t="s">
-        <v>8438</v>
+        <v>8430</v>
       </c>
       <c r="B4391" t="s">
-        <v>8439</v>
+        <v>8431</v>
       </c>
     </row>
     <row r="4392" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4392" t="s">
-        <v>8440</v>
+        <v>8432</v>
       </c>
       <c r="B4392" t="s">
-        <v>8441</v>
+        <v>8433</v>
       </c>
     </row>
     <row r="4393" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4393" t="s">
-        <v>8442</v>
+        <v>8434</v>
       </c>
       <c r="B4393" t="s">
-        <v>8443</v>
+        <v>8435</v>
       </c>
     </row>
     <row r="4394" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4394" t="s">
-        <v>8444</v>
+        <v>8436</v>
       </c>
       <c r="B4394" t="s">
-        <v>8445</v>
+        <v>8437</v>
       </c>
     </row>
     <row r="4395" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4395" t="s">
-        <v>8446</v>
+        <v>8438</v>
       </c>
       <c r="B4395" t="s">
-        <v>8447</v>
+        <v>8439</v>
       </c>
     </row>
     <row r="4396" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4396" t="s">
-        <v>8448</v>
+        <v>8440</v>
       </c>
       <c r="B4396" t="s">
-        <v>8449</v>
+        <v>8441</v>
       </c>
     </row>
     <row r="4397" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4397" t="s">
-        <v>8450</v>
+        <v>8442</v>
       </c>
       <c r="B4397" t="s">
-        <v>8451</v>
+        <v>8443</v>
       </c>
     </row>
     <row r="4398" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4398" t="s">
-        <v>8452</v>
+        <v>8444</v>
       </c>
       <c r="B4398" t="s">
-        <v>8453</v>
+        <v>8445</v>
       </c>
     </row>
     <row r="4399" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4399" t="s">
-        <v>8454</v>
+        <v>8446</v>
       </c>
       <c r="B4399" t="s">
-        <v>8455</v>
+        <v>8447</v>
       </c>
     </row>
     <row r="4400" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4400" t="s">
-        <v>8456</v>
+        <v>8448</v>
       </c>
       <c r="B4400" t="s">
-        <v>8457</v>
+        <v>8449</v>
       </c>
     </row>
     <row r="4401" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4401" t="s">
-        <v>8458</v>
+        <v>8450</v>
       </c>
       <c r="B4401" t="s">
-        <v>8459</v>
+        <v>8451</v>
       </c>
     </row>
     <row r="4402" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4402" t="s">
-        <v>8460</v>
+        <v>8452</v>
       </c>
       <c r="B4402" t="s">
-        <v>8309</v>
+        <v>8301</v>
       </c>
     </row>
     <row r="4403" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4403" t="s">
-        <v>8461</v>
+        <v>8453</v>
       </c>
       <c r="B4403" t="s">
-        <v>8311</v>
+        <v>8303</v>
       </c>
     </row>
     <row r="4404" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4404" t="s">
-        <v>8462</v>
+        <v>8454</v>
       </c>
       <c r="B4404" t="s">
-        <v>8313</v>
+        <v>8305</v>
       </c>
     </row>
     <row r="4405" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4405" t="s">
-        <v>8463</v>
+        <v>8455</v>
       </c>
       <c r="B4405" t="s">
-        <v>8315</v>
+        <v>8307</v>
       </c>
     </row>
     <row r="4406" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4406" t="s">
-        <v>8464</v>
+        <v>8456</v>
       </c>
       <c r="B4406" t="s">
-        <v>8465</v>
+        <v>8457</v>
       </c>
     </row>
     <row r="4407" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4407" t="s">
-        <v>8466</v>
+        <v>8458</v>
       </c>
       <c r="B4407" t="s">
-        <v>8467</v>
+        <v>8459</v>
       </c>
     </row>
     <row r="4408" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4408" t="s">
-        <v>8468</v>
+        <v>8460</v>
       </c>
       <c r="B4408" t="s">
-        <v>8469</v>
+        <v>8461</v>
       </c>
     </row>
     <row r="4409" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4409" t="s">
-        <v>8470</v>
+        <v>8462</v>
       </c>
       <c r="B4409" t="s">
-        <v>8471</v>
+        <v>8463</v>
       </c>
     </row>
     <row r="4410" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4410" t="s">
-        <v>8472</v>
+        <v>8464</v>
       </c>
       <c r="B4410" t="s">
-        <v>8473</v>
+        <v>8465</v>
       </c>
     </row>
     <row r="4411" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4411" t="s">
-        <v>8474</v>
+        <v>8466</v>
       </c>
       <c r="B4411" t="s">
-        <v>8475</v>
+        <v>8467</v>
       </c>
     </row>
     <row r="4412" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4412" t="s">
-        <v>8476</v>
+        <v>8468</v>
       </c>
       <c r="B4412" t="s">
-        <v>8477</v>
+        <v>8469</v>
       </c>
     </row>
     <row r="4413" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4413" t="s">
-        <v>8478</v>
+        <v>8470</v>
       </c>
       <c r="B4413" t="s">
-        <v>8479</v>
+        <v>8471</v>
       </c>
     </row>
     <row r="4414" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4414" t="s">
-        <v>8480</v>
+        <v>8472</v>
       </c>
       <c r="B4414" t="s">
-        <v>8481</v>
+        <v>8473</v>
       </c>
     </row>
     <row r="4415" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4415" t="s">
-        <v>8482</v>
+        <v>8474</v>
       </c>
       <c r="B4415" t="s">
-        <v>8483</v>
+        <v>8475</v>
       </c>
     </row>
     <row r="4416" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4416" t="s">
-        <v>8484</v>
+        <v>8476</v>
       </c>
       <c r="B4416" t="s">
-        <v>8485</v>
+        <v>8477</v>
       </c>
     </row>
     <row r="4417" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4417" t="s">
-        <v>8486</v>
+        <v>8478</v>
       </c>
       <c r="B4417" t="s">
-        <v>8487</v>
+        <v>8479</v>
       </c>
     </row>
     <row r="4418" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4418" t="s">
-        <v>8488</v>
+        <v>8480</v>
       </c>
       <c r="B4418" t="s">
-        <v>8489</v>
+        <v>8481</v>
       </c>
     </row>
     <row r="4419" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4419" t="s">
-        <v>8490</v>
+        <v>8482</v>
       </c>
       <c r="B4419" t="s">
-        <v>8491</v>
+        <v>8483</v>
       </c>
     </row>
     <row r="4420" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4420" t="s">
-        <v>8492</v>
+        <v>8484</v>
       </c>
       <c r="B4420" t="s">
-        <v>8493</v>
+        <v>8485</v>
       </c>
     </row>
     <row r="4421" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4421" t="s">
-        <v>8494</v>
+        <v>8486</v>
       </c>
       <c r="B4421" t="s">
-        <v>8495</v>
+        <v>8487</v>
       </c>
     </row>
     <row r="4422" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4422" t="s">
-        <v>8496</v>
+        <v>8488</v>
       </c>
       <c r="B4422" t="s">
-        <v>8497</v>
+        <v>8489</v>
       </c>
     </row>
     <row r="4423" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4423" t="s">
-        <v>8498</v>
+        <v>8490</v>
       </c>
       <c r="B4423" t="s">
-        <v>8499</v>
+        <v>8491</v>
       </c>
     </row>
     <row r="4424" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4424" t="s">
-        <v>8500</v>
+        <v>8492</v>
       </c>
       <c r="B4424" t="s">
-        <v>8501</v>
+        <v>8493</v>
       </c>
     </row>
     <row r="4425" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4425" t="s">
-        <v>8502</v>
+        <v>8494</v>
       </c>
       <c r="B4425" t="s">
-        <v>8503</v>
+        <v>8495</v>
       </c>
     </row>
     <row r="4426" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4426" t="s">
-        <v>8504</v>
+        <v>8496</v>
       </c>
       <c r="B4426" t="s">
-        <v>8505</v>
+        <v>8497</v>
       </c>
     </row>
     <row r="4427" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4427" t="s">
-        <v>8506</v>
+        <v>8498</v>
       </c>
       <c r="B4427" t="s">
-        <v>8507</v>
+        <v>8499</v>
       </c>
     </row>
     <row r="4428" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4428" t="s">
-        <v>8508</v>
+        <v>8500</v>
       </c>
       <c r="B4428" t="s">
-        <v>8509</v>
+        <v>8501</v>
       </c>
     </row>
     <row r="4429" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4429" t="s">
-        <v>8510</v>
+        <v>8502</v>
       </c>
       <c r="B4429" t="s">
-        <v>8511</v>
+        <v>8503</v>
       </c>
     </row>
     <row r="4430" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4430" t="s">
-        <v>8512</v>
+        <v>8504</v>
       </c>
       <c r="B4430" t="s">
-        <v>8513</v>
+        <v>8505</v>
       </c>
     </row>
     <row r="4431" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4431" t="s">
-        <v>8514</v>
+        <v>8506</v>
       </c>
       <c r="B4431" t="s">
-        <v>8515</v>
+        <v>8507</v>
       </c>
     </row>
     <row r="4432" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4432" t="s">
-        <v>8516</v>
+        <v>8508</v>
       </c>
       <c r="B4432" t="s">
-        <v>8517</v>
+        <v>8509</v>
       </c>
     </row>
     <row r="4433" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4433" t="s">
-        <v>8518</v>
+        <v>8510</v>
       </c>
       <c r="B4433" t="s">
-        <v>8519</v>
+        <v>8511</v>
       </c>
     </row>
     <row r="4434" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4434" t="s">
-        <v>8520</v>
+        <v>8512</v>
       </c>
       <c r="B4434" t="s">
-        <v>8521</v>
+        <v>8513</v>
       </c>
     </row>
     <row r="4435" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4435" t="s">
-        <v>8522</v>
+        <v>8514</v>
       </c>
       <c r="B4435" t="s">
-        <v>8523</v>
+        <v>8515</v>
       </c>
     </row>
     <row r="4436" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4436" t="s">
-        <v>8524</v>
+        <v>8516</v>
       </c>
       <c r="B4436" t="s">
-        <v>8525</v>
+        <v>8517</v>
       </c>
     </row>
     <row r="4437" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4437" t="s">
-        <v>8526</v>
+        <v>8518</v>
       </c>
       <c r="B4437" t="s">
-        <v>8527</v>
+        <v>8519</v>
       </c>
     </row>
     <row r="4438" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4438" t="s">
-        <v>8528</v>
+        <v>8520</v>
       </c>
       <c r="B4438" t="s">
-        <v>8529</v>
+        <v>8521</v>
       </c>
     </row>
     <row r="4439" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4439" t="s">
-        <v>8530</v>
+        <v>8522</v>
       </c>
       <c r="B4439" t="s">
-        <v>8531</v>
+        <v>8523</v>
       </c>
     </row>
     <row r="4440" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4440" t="s">
-        <v>8532</v>
+        <v>8524</v>
       </c>
       <c r="B4440" t="s">
-        <v>8533</v>
+        <v>8525</v>
       </c>
     </row>
     <row r="4441" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4441" t="s">
-        <v>8534</v>
+        <v>8526</v>
       </c>
       <c r="B4441" t="s">
-        <v>8535</v>
+        <v>8527</v>
       </c>
     </row>
     <row r="4442" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4442" t="s">
-        <v>8536</v>
+        <v>8528</v>
       </c>
       <c r="B4442" t="s">
-        <v>8537</v>
+        <v>8529</v>
       </c>
     </row>
     <row r="4443" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4443" t="s">
-        <v>8538</v>
+        <v>8530</v>
       </c>
       <c r="B4443" t="s">
-        <v>8539</v>
+        <v>8531</v>
       </c>
     </row>
     <row r="4444" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4444" t="s">
-        <v>8540</v>
+        <v>8532</v>
       </c>
       <c r="B4444" t="s">
-        <v>8541</v>
+        <v>8533</v>
       </c>
     </row>
     <row r="4445" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4445" t="s">
-        <v>8542</v>
+        <v>8534</v>
       </c>
       <c r="B4445" t="s">
-        <v>8543</v>
+        <v>8535</v>
       </c>
     </row>
     <row r="4446" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4446" t="s">
-        <v>8544</v>
+        <v>8536</v>
       </c>
       <c r="B4446" t="s">
-        <v>8545</v>
+        <v>8537</v>
       </c>
     </row>
     <row r="4447" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4447" t="s">
-        <v>8546</v>
+        <v>8538</v>
       </c>
       <c r="B4447" t="s">
-        <v>8547</v>
+        <v>8539</v>
       </c>
     </row>
     <row r="4448" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4448" t="s">
-        <v>8548</v>
+        <v>8540</v>
       </c>
       <c r="B4448" t="s">
-        <v>8549</v>
+        <v>8541</v>
       </c>
     </row>
     <row r="4449" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4449" t="s">
-        <v>8550</v>
+        <v>8542</v>
       </c>
       <c r="B4449" t="s">
-        <v>8551</v>
+        <v>8543</v>
       </c>
     </row>
     <row r="4450" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4450" t="s">
-        <v>8552</v>
+        <v>8544</v>
       </c>
       <c r="B4450" t="s">
-        <v>8553</v>
+        <v>8545</v>
       </c>
     </row>
     <row r="4451" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4451" t="s">
-        <v>8554</v>
+        <v>8546</v>
       </c>
       <c r="B4451" t="s">
-        <v>8555</v>
+        <v>8547</v>
       </c>
     </row>
     <row r="4452" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4452" t="s">
-        <v>8556</v>
+        <v>8548</v>
       </c>
       <c r="B4452" t="s">
-        <v>8557</v>
+        <v>8549</v>
       </c>
     </row>
     <row r="4453" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4453" t="s">
-        <v>8558</v>
+        <v>8550</v>
       </c>
       <c r="B4453" t="s">
-        <v>8559</v>
+        <v>8551</v>
       </c>
     </row>
     <row r="4454" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4454" t="s">
-        <v>8560</v>
+        <v>8552</v>
       </c>
       <c r="B4454" t="s">
-        <v>8561</v>
+        <v>8553</v>
       </c>
     </row>
     <row r="4455" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4455" t="s">
-        <v>8562</v>
+        <v>8554</v>
       </c>
       <c r="B4455" t="s">
-        <v>8563</v>
+        <v>8555</v>
       </c>
     </row>
     <row r="4456" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4456" t="s">
-        <v>8564</v>
+        <v>8556</v>
       </c>
       <c r="B4456" t="s">
-        <v>8565</v>
+        <v>8557</v>
       </c>
     </row>
     <row r="4457" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4457" t="s">
-        <v>8566</v>
+        <v>8558</v>
       </c>
       <c r="B4457" t="s">
-        <v>8567</v>
+        <v>8559</v>
       </c>
     </row>
     <row r="4458" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4458" t="s">
-        <v>8568</v>
+        <v>8560</v>
       </c>
       <c r="B4458" t="s">
-        <v>8569</v>
+        <v>8561</v>
       </c>
     </row>
     <row r="4459" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4459" t="s">
-        <v>8570</v>
+        <v>8562</v>
       </c>
       <c r="B4459" t="s">
-        <v>8571</v>
+        <v>8563</v>
       </c>
     </row>
     <row r="4460" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4460" t="s">
-        <v>8572</v>
+        <v>8564</v>
       </c>
       <c r="B4460" t="s">
-        <v>8573</v>
+        <v>8565</v>
       </c>
     </row>
     <row r="4461" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4461" t="s">
-        <v>8574</v>
+        <v>8566</v>
       </c>
       <c r="B4461" t="s">
-        <v>8575</v>
+        <v>8567</v>
       </c>
     </row>
     <row r="4462" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4462" t="s">
-        <v>8576</v>
+        <v>8568</v>
       </c>
       <c r="B4462" t="s">
-        <v>8577</v>
+        <v>8569</v>
       </c>
     </row>
     <row r="4463" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4463" t="s">
-        <v>8578</v>
+        <v>8570</v>
       </c>
       <c r="B4463" t="s">
-        <v>8579</v>
+        <v>8571</v>
       </c>
     </row>
     <row r="4464" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4464" t="s">
-        <v>8580</v>
+        <v>8572</v>
       </c>
       <c r="B4464" t="s">
-        <v>8581</v>
+        <v>8573</v>
       </c>
     </row>
     <row r="4465" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4465" t="s">
-        <v>8582</v>
+        <v>8574</v>
       </c>
       <c r="B4465" t="s">
-        <v>8583</v>
+        <v>8575</v>
       </c>
     </row>
     <row r="4466" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4466" t="s">
-        <v>8584</v>
+        <v>8576</v>
       </c>
       <c r="B4466" t="s">
-        <v>8585</v>
+        <v>8577</v>
       </c>
     </row>
     <row r="4467" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4467" t="s">
-        <v>8586</v>
+        <v>8578</v>
       </c>
       <c r="B4467" t="s">
-        <v>8587</v>
+        <v>8579</v>
       </c>
     </row>
     <row r="4468" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4468" t="s">
-        <v>8588</v>
+        <v>8580</v>
       </c>
       <c r="B4468" t="s">
-        <v>8589</v>
+        <v>8581</v>
       </c>
     </row>
     <row r="4469" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4469" t="s">
-        <v>8590</v>
+        <v>8582</v>
       </c>
       <c r="B4469" t="s">
-        <v>8591</v>
+        <v>8583</v>
       </c>
     </row>
     <row r="4470" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4470" t="s">
-        <v>8592</v>
+        <v>8584</v>
       </c>
       <c r="B4470" t="s">
-        <v>8593</v>
+        <v>8585</v>
       </c>
     </row>
     <row r="4471" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4471" t="s">
-        <v>8594</v>
+        <v>8586</v>
       </c>
       <c r="B4471" t="s">
-        <v>8595</v>
+        <v>8587</v>
       </c>
     </row>
     <row r="4472" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4472" t="s">
-        <v>8596</v>
+        <v>8588</v>
       </c>
       <c r="B4472" t="s">
-        <v>8597</v>
+        <v>8589</v>
       </c>
     </row>
     <row r="4473" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4473" t="s">
-        <v>8598</v>
+        <v>8590</v>
       </c>
       <c r="B4473" t="s">
-        <v>8599</v>
+        <v>8591</v>
       </c>
     </row>
     <row r="4474" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4474" t="s">
-        <v>8600</v>
+        <v>8592</v>
       </c>
       <c r="B4474" t="s">
-        <v>8601</v>
+        <v>8593</v>
       </c>
     </row>
     <row r="4475" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4475" t="s">
-        <v>8602</v>
+        <v>8594</v>
       </c>
       <c r="B4475" t="s">
-        <v>8603</v>
+        <v>8595</v>
       </c>
     </row>
     <row r="4476" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4476" t="s">
-        <v>8604</v>
+        <v>8596</v>
       </c>
       <c r="B4476" t="s">
-        <v>8605</v>
+        <v>8597</v>
       </c>
     </row>
     <row r="4477" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4477" t="s">
-        <v>8606</v>
+        <v>8598</v>
       </c>
       <c r="B4477" t="s">
-        <v>8607</v>
+        <v>8599</v>
       </c>
     </row>
     <row r="4478" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4478" t="s">
-        <v>8608</v>
+        <v>8600</v>
       </c>
       <c r="B4478" t="s">
-        <v>8609</v>
+        <v>8601</v>
       </c>
     </row>
     <row r="4479" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4479" t="s">
-        <v>8610</v>
+        <v>8602</v>
       </c>
       <c r="B4479" t="s">
-        <v>8611</v>
+        <v>8603</v>
       </c>
     </row>
     <row r="4480" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4480" t="s">
-        <v>8612</v>
+        <v>8604</v>
       </c>
       <c r="B4480" t="s">
-        <v>8613</v>
+        <v>8605</v>
       </c>
     </row>
     <row r="4481" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4481" t="s">
-        <v>8614</v>
+        <v>8606</v>
       </c>
       <c r="B4481" t="s">
-        <v>8615</v>
+        <v>8607</v>
       </c>
     </row>
     <row r="4482" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4482" t="s">
-        <v>8616</v>
+        <v>8608</v>
       </c>
       <c r="B4482" t="s">
-        <v>8617</v>
+        <v>8609</v>
       </c>
     </row>
     <row r="4483" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4483" t="s">
-        <v>8618</v>
+        <v>8610</v>
       </c>
       <c r="B4483" t="s">
-        <v>8619</v>
+        <v>8611</v>
       </c>
     </row>
     <row r="4484" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4484" t="s">
-        <v>8620</v>
+        <v>8612</v>
       </c>
       <c r="B4484" t="s">
-        <v>8621</v>
+        <v>8613</v>
       </c>
     </row>
     <row r="4485" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4485" t="s">
-        <v>8622</v>
+        <v>8614</v>
       </c>
       <c r="B4485" t="s">
-        <v>8623</v>
+        <v>8615</v>
       </c>
     </row>
     <row r="4486" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4486" t="s">
-        <v>8624</v>
+        <v>8616</v>
       </c>
       <c r="B4486" t="s">
-        <v>8625</v>
+        <v>8617</v>
       </c>
     </row>
     <row r="4487" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4487" t="s">
-        <v>8626</v>
+        <v>8618</v>
       </c>
       <c r="B4487" t="s">
-        <v>8627</v>
+        <v>8619</v>
       </c>
     </row>
     <row r="4488" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4488" t="s">
-        <v>8628</v>
+        <v>8620</v>
       </c>
       <c r="B4488" t="s">
-        <v>8629</v>
+        <v>8621</v>
       </c>
     </row>
     <row r="4489" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4489" t="s">
-        <v>8630</v>
+        <v>8622</v>
       </c>
       <c r="B4489" t="s">
-        <v>8631</v>
+        <v>8623</v>
       </c>
     </row>
     <row r="4490" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4490" t="s">
-        <v>8632</v>
+        <v>8624</v>
       </c>
       <c r="B4490" t="s">
-        <v>8633</v>
+        <v>8625</v>
       </c>
     </row>
     <row r="4491" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4491" t="s">
-        <v>8634</v>
+        <v>8626</v>
       </c>
       <c r="B4491" t="s">
-        <v>8635</v>
+        <v>8627</v>
       </c>
     </row>
     <row r="4492" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4492" t="s">
-        <v>8636</v>
+        <v>8628</v>
       </c>
       <c r="B4492" t="s">
-        <v>8637</v>
+        <v>8629</v>
       </c>
     </row>
     <row r="4493" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4493" t="s">
-        <v>8638</v>
+        <v>8630</v>
       </c>
       <c r="B4493" t="s">
-        <v>8639</v>
+        <v>8631</v>
       </c>
     </row>
     <row r="4494" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4494" t="s">
-        <v>8640</v>
+        <v>8632</v>
       </c>
       <c r="B4494" t="s">
-        <v>8641</v>
+        <v>8633</v>
       </c>
     </row>
     <row r="4495" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4495" t="s">
-        <v>8642</v>
+        <v>8634</v>
       </c>
       <c r="B4495" t="s">
-        <v>8643</v>
+        <v>8635</v>
       </c>
     </row>
     <row r="4496" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4496" t="s">
-        <v>8644</v>
+        <v>8636</v>
       </c>
       <c r="B4496" t="s">
-        <v>8645</v>
+        <v>8637</v>
       </c>
     </row>
     <row r="4497" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4497" t="s">
-        <v>8646</v>
+        <v>8638</v>
       </c>
       <c r="B4497" t="s">
-        <v>8647</v>
+        <v>8639</v>
       </c>
     </row>
     <row r="4498" spans="1:2" x14ac:dyDescent="0.25">
@@ -63252,7 +63252,7 @@
         <v>5404</v>
       </c>
       <c r="B4498" t="s">
-        <v>8648</v>
+        <v>8640</v>
       </c>
     </row>
     <row r="4499" spans="1:2" x14ac:dyDescent="0.25">
@@ -63260,7 +63260,7 @@
         <v>5406</v>
       </c>
       <c r="B4499" t="s">
-        <v>8649</v>
+        <v>8641</v>
       </c>
     </row>
     <row r="4500" spans="1:2" x14ac:dyDescent="0.25">
@@ -63268,7 +63268,7 @@
         <v>5408</v>
       </c>
       <c r="B4500" t="s">
-        <v>8650</v>
+        <v>8642</v>
       </c>
     </row>
     <row r="4501" spans="1:2" x14ac:dyDescent="0.25">
@@ -63276,556 +63276,556 @@
         <v>5410</v>
       </c>
       <c r="B4501" t="s">
-        <v>8651</v>
+        <v>8643</v>
       </c>
     </row>
     <row r="4502" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4502" t="s">
-        <v>8652</v>
+        <v>8644</v>
       </c>
       <c r="B4502" t="s">
-        <v>8653</v>
+        <v>8645</v>
       </c>
     </row>
     <row r="4503" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4503" t="s">
-        <v>8654</v>
+        <v>8646</v>
       </c>
       <c r="B4503" t="s">
-        <v>8655</v>
+        <v>8647</v>
       </c>
     </row>
     <row r="4504" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4504" t="s">
-        <v>8656</v>
+        <v>8648</v>
       </c>
       <c r="B4504" t="s">
-        <v>8657</v>
+        <v>8649</v>
       </c>
     </row>
     <row r="4505" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4505" t="s">
-        <v>8658</v>
+        <v>8650</v>
       </c>
       <c r="B4505" t="s">
-        <v>8659</v>
+        <v>8651</v>
       </c>
     </row>
     <row r="4506" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4506" t="s">
-        <v>8660</v>
+        <v>8652</v>
       </c>
       <c r="B4506" t="s">
-        <v>8661</v>
+        <v>8653</v>
       </c>
     </row>
     <row r="4507" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4507" t="s">
-        <v>8662</v>
+        <v>8654</v>
       </c>
       <c r="B4507" t="s">
-        <v>8663</v>
+        <v>8655</v>
       </c>
     </row>
     <row r="4508" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4508" t="s">
-        <v>8664</v>
+        <v>8656</v>
       </c>
       <c r="B4508" t="s">
-        <v>8665</v>
+        <v>8657</v>
       </c>
     </row>
     <row r="4509" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4509" t="s">
-        <v>8666</v>
+        <v>8658</v>
       </c>
       <c r="B4509" t="s">
-        <v>8667</v>
+        <v>8659</v>
       </c>
     </row>
     <row r="4510" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4510" t="s">
-        <v>8668</v>
+        <v>8660</v>
       </c>
       <c r="B4510" t="s">
-        <v>8669</v>
+        <v>8661</v>
       </c>
     </row>
     <row r="4511" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4511" t="s">
-        <v>8670</v>
+        <v>8662</v>
       </c>
       <c r="B4511" t="s">
-        <v>8671</v>
+        <v>8663</v>
       </c>
     </row>
     <row r="4512" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4512" t="s">
-        <v>8672</v>
+        <v>8664</v>
       </c>
       <c r="B4512" t="s">
-        <v>8673</v>
+        <v>8665</v>
       </c>
     </row>
     <row r="4513" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4513" t="s">
-        <v>8674</v>
+        <v>8666</v>
       </c>
       <c r="B4513" t="s">
-        <v>8675</v>
+        <v>8667</v>
       </c>
     </row>
     <row r="4514" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4514" t="s">
-        <v>8676</v>
+        <v>8668</v>
       </c>
       <c r="B4514" t="s">
-        <v>8677</v>
+        <v>8669</v>
       </c>
     </row>
     <row r="4515" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4515" t="s">
-        <v>8678</v>
+        <v>8670</v>
       </c>
       <c r="B4515" t="s">
-        <v>8679</v>
+        <v>8671</v>
       </c>
     </row>
     <row r="4516" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4516" t="s">
-        <v>8680</v>
+        <v>8672</v>
       </c>
       <c r="B4516" t="s">
-        <v>8681</v>
+        <v>8673</v>
       </c>
     </row>
     <row r="4517" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4517" t="s">
-        <v>8682</v>
+        <v>8674</v>
       </c>
       <c r="B4517" t="s">
-        <v>8683</v>
+        <v>8675</v>
       </c>
     </row>
     <row r="4518" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4518" t="s">
-        <v>8684</v>
+        <v>8676</v>
       </c>
       <c r="B4518" t="s">
-        <v>8685</v>
+        <v>8677</v>
       </c>
     </row>
     <row r="4519" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4519" t="s">
-        <v>8686</v>
+        <v>8678</v>
       </c>
       <c r="B4519" t="s">
-        <v>8687</v>
+        <v>8679</v>
       </c>
     </row>
     <row r="4520" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4520" t="s">
-        <v>8688</v>
+        <v>8680</v>
       </c>
       <c r="B4520" t="s">
-        <v>8689</v>
+        <v>8681</v>
       </c>
     </row>
     <row r="4521" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4521" t="s">
-        <v>8690</v>
+        <v>8682</v>
       </c>
       <c r="B4521" t="s">
-        <v>8691</v>
+        <v>8683</v>
       </c>
     </row>
     <row r="4522" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4522" t="s">
-        <v>8692</v>
+        <v>8684</v>
       </c>
       <c r="B4522" t="s">
-        <v>8693</v>
+        <v>8685</v>
       </c>
     </row>
     <row r="4523" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4523" t="s">
-        <v>8694</v>
+        <v>8686</v>
       </c>
       <c r="B4523" t="s">
-        <v>8695</v>
+        <v>8687</v>
       </c>
     </row>
     <row r="4524" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4524" t="s">
-        <v>8696</v>
+        <v>8688</v>
       </c>
       <c r="B4524" t="s">
-        <v>8697</v>
+        <v>8689</v>
       </c>
     </row>
     <row r="4525" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4525" t="s">
-        <v>8698</v>
+        <v>8690</v>
       </c>
       <c r="B4525" t="s">
-        <v>8699</v>
+        <v>8691</v>
       </c>
     </row>
     <row r="4526" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4526" t="s">
-        <v>8700</v>
+        <v>8692</v>
       </c>
       <c r="B4526" t="s">
-        <v>8701</v>
+        <v>8693</v>
       </c>
     </row>
     <row r="4527" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4527" t="s">
-        <v>8702</v>
+        <v>8694</v>
       </c>
       <c r="B4527" t="s">
-        <v>8703</v>
+        <v>8695</v>
       </c>
     </row>
     <row r="4528" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4528" t="s">
-        <v>8704</v>
+        <v>8696</v>
       </c>
       <c r="B4528" t="s">
-        <v>8705</v>
+        <v>8697</v>
       </c>
     </row>
     <row r="4529" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4529" t="s">
-        <v>8706</v>
+        <v>8698</v>
       </c>
       <c r="B4529" t="s">
-        <v>8707</v>
+        <v>8699</v>
       </c>
     </row>
     <row r="4530" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4530" t="s">
-        <v>8708</v>
+        <v>8700</v>
       </c>
       <c r="B4530" t="s">
-        <v>8709</v>
+        <v>8701</v>
       </c>
     </row>
     <row r="4531" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4531" t="s">
-        <v>8710</v>
+        <v>8702</v>
       </c>
       <c r="B4531" t="s">
-        <v>8711</v>
+        <v>8703</v>
       </c>
     </row>
     <row r="4532" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4532" t="s">
-        <v>8712</v>
+        <v>8704</v>
       </c>
       <c r="B4532" t="s">
-        <v>8713</v>
+        <v>8705</v>
       </c>
     </row>
     <row r="4533" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4533" t="s">
-        <v>8714</v>
+        <v>8706</v>
       </c>
       <c r="B4533" t="s">
-        <v>8715</v>
+        <v>8707</v>
       </c>
     </row>
     <row r="4534" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4534" t="s">
-        <v>8716</v>
+        <v>8708</v>
       </c>
       <c r="B4534" t="s">
-        <v>8717</v>
+        <v>8709</v>
       </c>
     </row>
     <row r="4535" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4535" t="s">
-        <v>8718</v>
+        <v>8710</v>
       </c>
       <c r="B4535" t="s">
-        <v>8719</v>
+        <v>8711</v>
       </c>
     </row>
     <row r="4536" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4536" t="s">
-        <v>8720</v>
+        <v>8712</v>
       </c>
       <c r="B4536" t="s">
-        <v>8721</v>
+        <v>8713</v>
       </c>
     </row>
     <row r="4537" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4537" t="s">
-        <v>8722</v>
+        <v>8714</v>
       </c>
       <c r="B4537" t="s">
-        <v>8723</v>
+        <v>8715</v>
       </c>
     </row>
     <row r="4538" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4538" t="s">
-        <v>8724</v>
+        <v>8716</v>
       </c>
       <c r="B4538" t="s">
-        <v>8725</v>
+        <v>8717</v>
       </c>
     </row>
     <row r="4539" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4539" t="s">
-        <v>8726</v>
+        <v>8718</v>
       </c>
       <c r="B4539" t="s">
-        <v>8727</v>
+        <v>8719</v>
       </c>
     </row>
     <row r="4540" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4540" t="s">
-        <v>8728</v>
+        <v>8720</v>
       </c>
       <c r="B4540" t="s">
-        <v>8729</v>
+        <v>8721</v>
       </c>
     </row>
     <row r="4541" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4541" t="s">
-        <v>8730</v>
+        <v>8722</v>
       </c>
       <c r="B4541" t="s">
-        <v>8731</v>
+        <v>8723</v>
       </c>
     </row>
     <row r="4542" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4542" t="s">
-        <v>8732</v>
+        <v>8724</v>
       </c>
       <c r="B4542" t="s">
-        <v>8733</v>
+        <v>8725</v>
       </c>
     </row>
     <row r="4543" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4543" t="s">
-        <v>8734</v>
+        <v>8726</v>
       </c>
       <c r="B4543" t="s">
-        <v>8735</v>
+        <v>8727</v>
       </c>
     </row>
     <row r="4544" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4544" t="s">
-        <v>8736</v>
+        <v>8728</v>
       </c>
       <c r="B4544" t="s">
-        <v>8737</v>
+        <v>8729</v>
       </c>
     </row>
     <row r="4545" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4545" t="s">
-        <v>8738</v>
+        <v>8730</v>
       </c>
       <c r="B4545" t="s">
-        <v>8739</v>
+        <v>8731</v>
       </c>
     </row>
     <row r="4546" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4546" t="s">
-        <v>8740</v>
+        <v>8732</v>
       </c>
       <c r="B4546" t="s">
-        <v>8741</v>
+        <v>8733</v>
       </c>
     </row>
     <row r="4547" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4547" t="s">
-        <v>8742</v>
+        <v>8734</v>
       </c>
       <c r="B4547" t="s">
-        <v>8743</v>
+        <v>8735</v>
       </c>
     </row>
     <row r="4548" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4548" t="s">
-        <v>8744</v>
+        <v>8736</v>
       </c>
       <c r="B4548" t="s">
-        <v>8745</v>
+        <v>8737</v>
       </c>
     </row>
     <row r="4549" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4549" t="s">
-        <v>8746</v>
+        <v>8738</v>
       </c>
       <c r="B4549" t="s">
-        <v>8747</v>
+        <v>8739</v>
       </c>
     </row>
     <row r="4550" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4550" t="s">
-        <v>8748</v>
+        <v>8740</v>
       </c>
       <c r="B4550" t="s">
-        <v>8749</v>
+        <v>8741</v>
       </c>
     </row>
     <row r="4551" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4551" t="s">
-        <v>8750</v>
+        <v>8742</v>
       </c>
       <c r="B4551" t="s">
-        <v>8751</v>
+        <v>8743</v>
       </c>
     </row>
     <row r="4552" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4552" t="s">
-        <v>8752</v>
+        <v>8744</v>
       </c>
       <c r="B4552" t="s">
-        <v>8753</v>
+        <v>8745</v>
       </c>
     </row>
     <row r="4553" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4553" t="s">
-        <v>8754</v>
+        <v>8746</v>
       </c>
       <c r="B4553" t="s">
-        <v>8755</v>
+        <v>8747</v>
       </c>
     </row>
     <row r="4554" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4554" t="s">
-        <v>8756</v>
+        <v>8748</v>
       </c>
       <c r="B4554" t="s">
-        <v>8757</v>
+        <v>8749</v>
       </c>
     </row>
     <row r="4555" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4555" t="s">
-        <v>8758</v>
+        <v>8750</v>
       </c>
       <c r="B4555" t="s">
-        <v>8759</v>
+        <v>8751</v>
       </c>
     </row>
     <row r="4556" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4556" t="s">
-        <v>8760</v>
+        <v>8752</v>
       </c>
       <c r="B4556" t="s">
-        <v>8761</v>
+        <v>8753</v>
       </c>
     </row>
     <row r="4557" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4557" t="s">
-        <v>8762</v>
+        <v>8754</v>
       </c>
       <c r="B4557" t="s">
-        <v>8763</v>
+        <v>8755</v>
       </c>
     </row>
     <row r="4558" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4558" t="s">
-        <v>8764</v>
+        <v>8756</v>
       </c>
       <c r="B4558" t="s">
-        <v>8765</v>
+        <v>8757</v>
       </c>
     </row>
     <row r="4559" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4559" t="s">
-        <v>8766</v>
+        <v>8758</v>
       </c>
       <c r="B4559" t="s">
-        <v>8767</v>
+        <v>8759</v>
       </c>
     </row>
     <row r="4560" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4560" t="s">
-        <v>8768</v>
+        <v>8760</v>
       </c>
       <c r="B4560" t="s">
-        <v>8769</v>
+        <v>8761</v>
       </c>
     </row>
     <row r="4561" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4561" t="s">
-        <v>8770</v>
+        <v>8762</v>
       </c>
       <c r="B4561" t="s">
-        <v>8771</v>
+        <v>8763</v>
       </c>
     </row>
     <row r="4562" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4562" t="s">
-        <v>8772</v>
+        <v>8764</v>
       </c>
       <c r="B4562" t="s">
-        <v>8773</v>
+        <v>8765</v>
       </c>
     </row>
     <row r="4563" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4563" t="s">
-        <v>8774</v>
+        <v>8766</v>
       </c>
       <c r="B4563" t="s">
-        <v>8775</v>
+        <v>8767</v>
       </c>
     </row>
     <row r="4564" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4564" t="s">
-        <v>8776</v>
+        <v>8768</v>
       </c>
       <c r="B4564" t="s">
-        <v>8777</v>
+        <v>8769</v>
       </c>
     </row>
     <row r="4565" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4565" t="s">
-        <v>8778</v>
+        <v>8770</v>
       </c>
       <c r="B4565" t="s">
-        <v>8779</v>
+        <v>8771</v>
       </c>
     </row>
     <row r="4566" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4566" t="s">
-        <v>8780</v>
+        <v>8772</v>
       </c>
       <c r="B4566" t="s">
-        <v>8781</v>
+        <v>8773</v>
       </c>
     </row>
     <row r="4567" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4567" t="s">
-        <v>8782</v>
+        <v>8774</v>
       </c>
       <c r="B4567" t="s">
-        <v>8783</v>
+        <v>8775</v>
       </c>
     </row>
     <row r="4568" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4568" t="s">
-        <v>8784</v>
+        <v>8776</v>
       </c>
       <c r="B4568" t="s">
-        <v>8785</v>
+        <v>8777</v>
       </c>
     </row>
     <row r="4569" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4569" t="s">
-        <v>8786</v>
+        <v>8778</v>
       </c>
       <c r="B4569" t="s">
-        <v>8787</v>
+        <v>8779</v>
       </c>
     </row>
     <row r="4570" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4570" t="s">
-        <v>8793</v>
+        <v>8785</v>
       </c>
       <c r="B4570" t="s">
         <v>979</v>
@@ -63833,7 +63833,7 @@
     </row>
     <row r="4571" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4571" t="s">
-        <v>8794</v>
+        <v>8786</v>
       </c>
       <c r="B4571" t="s">
         <v>981</v>
@@ -63841,7 +63841,7 @@
     </row>
     <row r="4572" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4572" t="s">
-        <v>8795</v>
+        <v>8787</v>
       </c>
       <c r="B4572" t="s">
         <v>983</v>
@@ -63849,7 +63849,7 @@
     </row>
     <row r="4573" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4573" t="s">
-        <v>8793</v>
+        <v>8785</v>
       </c>
       <c r="B4573" t="s">
         <v>985</v>

--- a/Tabela com codigos operativos.xlsx
+++ b/Tabela com codigos operativos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Engeselt\Documents\GitHub\ASPO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EF6D4C1-9033-4700-9D97-44947FE30D7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD614164-C45D-4977-8947-530E41EA4816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24497,27 +24497,15 @@
     <t>018TR04-EAE</t>
   </si>
   <si>
-    <t>SE TAN TR-04 13.8KV-EAE</t>
-  </si>
-  <si>
     <t>018TR04-EAR</t>
   </si>
   <si>
-    <t>SE TAN TR-04 13.8KV-EAR</t>
-  </si>
-  <si>
     <t>018TR04-ERE</t>
   </si>
   <si>
-    <t>SE TAN TR-04 13.8KV-ERE</t>
-  </si>
-  <si>
     <t>018TR04-ERR</t>
   </si>
   <si>
-    <t>SE TAN TR-04 13.8KV-ERR</t>
-  </si>
-  <si>
     <t>018TR01-EAE</t>
   </si>
   <si>
@@ -24545,27 +24533,15 @@
     <t>018TR03-EAE</t>
   </si>
   <si>
-    <t>SE TAN TR03 34.5KV-EAE</t>
-  </si>
-  <si>
     <t>018TR03-EAR</t>
   </si>
   <si>
-    <t>SE TAN TR03 34.5KV-EAR</t>
-  </si>
-  <si>
     <t>018TR03-ERE</t>
   </si>
   <si>
-    <t>SE TAN TR03 34.5KV-ERE</t>
-  </si>
-  <si>
     <t>018TR03-ERR</t>
   </si>
   <si>
-    <t>SE TAN TR03 34.5KV-ERR</t>
-  </si>
-  <si>
     <t>PCH FAXINAL I-EAE</t>
   </si>
   <si>
@@ -26424,6 +26400,30 @@
   </si>
   <si>
     <t>SE CN PARECIS TR-02 13.8KV-ERR</t>
+  </si>
+  <si>
+    <t>SE TAN TR04 34.5KV-EAE</t>
+  </si>
+  <si>
+    <t>SE TAN TR04 34.5KV-EAR</t>
+  </si>
+  <si>
+    <t>SE TAN TR04 34.5KV-ERE</t>
+  </si>
+  <si>
+    <t>SE TAN TR04 34.5KV-ERR</t>
+  </si>
+  <si>
+    <t>SE TAN TR-03 13.8KV-EAE</t>
+  </si>
+  <si>
+    <t>SE TAN TR-03 13.8KV-EAR</t>
+  </si>
+  <si>
+    <t>SE TAN TR-03 13.8KV-ERE</t>
+  </si>
+  <si>
+    <t>SE TAN TR-03 13.8KV-ERR</t>
   </si>
 </sst>
 </file>
@@ -57332,7 +57332,7 @@
         <v>7220</v>
       </c>
       <c r="B3758" t="s">
-        <v>8788</v>
+        <v>8780</v>
       </c>
     </row>
     <row r="3759" spans="1:2" x14ac:dyDescent="0.25">
@@ -57340,7 +57340,7 @@
         <v>7221</v>
       </c>
       <c r="B3759" t="s">
-        <v>8789</v>
+        <v>8781</v>
       </c>
     </row>
     <row r="3760" spans="1:2" x14ac:dyDescent="0.25">
@@ -57348,7 +57348,7 @@
         <v>7222</v>
       </c>
       <c r="B3760" t="s">
-        <v>8790</v>
+        <v>8782</v>
       </c>
     </row>
     <row r="3761" spans="1:2" x14ac:dyDescent="0.25">
@@ -57356,7 +57356,7 @@
         <v>7223</v>
       </c>
       <c r="B3761" t="s">
-        <v>8791</v>
+        <v>8783</v>
       </c>
     </row>
     <row r="3762" spans="1:2" x14ac:dyDescent="0.25">
@@ -57364,7 +57364,7 @@
         <v>7224</v>
       </c>
       <c r="B3762" t="s">
-        <v>8792</v>
+        <v>8784</v>
       </c>
     </row>
     <row r="3763" spans="1:2" x14ac:dyDescent="0.25">
@@ -57372,7 +57372,7 @@
         <v>7225</v>
       </c>
       <c r="B3763" t="s">
-        <v>8793</v>
+        <v>8785</v>
       </c>
     </row>
     <row r="3764" spans="1:2" x14ac:dyDescent="0.25">
@@ -57380,7 +57380,7 @@
         <v>7226</v>
       </c>
       <c r="B3764" t="s">
-        <v>8794</v>
+        <v>8786</v>
       </c>
     </row>
     <row r="3765" spans="1:2" x14ac:dyDescent="0.25">
@@ -57388,7 +57388,7 @@
         <v>7227</v>
       </c>
       <c r="B3765" t="s">
-        <v>8795</v>
+        <v>8787</v>
       </c>
     </row>
     <row r="3766" spans="1:2" x14ac:dyDescent="0.25">
@@ -61105,130 +61105,130 @@
     </row>
     <row r="4230" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4230" t="s">
-        <v>8152</v>
+        <v>8164</v>
       </c>
       <c r="B4230" t="s">
-        <v>8153</v>
+        <v>8792</v>
       </c>
     </row>
     <row r="4231" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4231" t="s">
-        <v>8154</v>
+        <v>8165</v>
       </c>
       <c r="B4231" t="s">
-        <v>8155</v>
+        <v>8793</v>
       </c>
     </row>
     <row r="4232" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4232" t="s">
-        <v>8156</v>
+        <v>8166</v>
       </c>
       <c r="B4232" t="s">
-        <v>8157</v>
+        <v>8794</v>
       </c>
     </row>
     <row r="4233" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4233" t="s">
-        <v>8158</v>
+        <v>8167</v>
       </c>
       <c r="B4233" t="s">
-        <v>8159</v>
+        <v>8795</v>
       </c>
     </row>
     <row r="4234" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4234" t="s">
-        <v>8160</v>
+        <v>8156</v>
       </c>
       <c r="B4234" t="s">
-        <v>8161</v>
+        <v>8157</v>
       </c>
     </row>
     <row r="4235" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4235" t="s">
-        <v>8162</v>
+        <v>8158</v>
       </c>
       <c r="B4235" t="s">
-        <v>8163</v>
+        <v>8159</v>
       </c>
     </row>
     <row r="4236" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4236" t="s">
-        <v>8164</v>
+        <v>8160</v>
       </c>
       <c r="B4236" t="s">
-        <v>8165</v>
+        <v>8161</v>
       </c>
     </row>
     <row r="4237" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4237" t="s">
-        <v>8166</v>
+        <v>8162</v>
       </c>
       <c r="B4237" t="s">
-        <v>8167</v>
+        <v>8163</v>
       </c>
     </row>
     <row r="4238" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4238" t="s">
-        <v>8168</v>
+        <v>8152</v>
       </c>
       <c r="B4238" t="s">
-        <v>8169</v>
+        <v>8788</v>
       </c>
     </row>
     <row r="4239" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4239" t="s">
-        <v>8170</v>
+        <v>8153</v>
       </c>
       <c r="B4239" t="s">
-        <v>8171</v>
+        <v>8789</v>
       </c>
     </row>
     <row r="4240" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4240" t="s">
-        <v>8172</v>
+        <v>8154</v>
       </c>
       <c r="B4240" t="s">
-        <v>8173</v>
+        <v>8790</v>
       </c>
     </row>
     <row r="4241" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4241" t="s">
-        <v>8174</v>
+        <v>8155</v>
       </c>
       <c r="B4241" t="s">
-        <v>8175</v>
+        <v>8791</v>
       </c>
     </row>
     <row r="4242" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4242" t="s">
-        <v>8176</v>
+        <v>8168</v>
       </c>
       <c r="B4242" t="s">
-        <v>8177</v>
+        <v>8169</v>
       </c>
     </row>
     <row r="4243" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4243" t="s">
-        <v>8178</v>
+        <v>8170</v>
       </c>
       <c r="B4243" t="s">
-        <v>8179</v>
+        <v>8171</v>
       </c>
     </row>
     <row r="4244" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4244" t="s">
-        <v>8180</v>
+        <v>8172</v>
       </c>
       <c r="B4244" t="s">
-        <v>8181</v>
+        <v>8173</v>
       </c>
     </row>
     <row r="4245" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4245" t="s">
-        <v>8182</v>
+        <v>8174</v>
       </c>
       <c r="B4245" t="s">
-        <v>8183</v>
+        <v>8175</v>
       </c>
     </row>
     <row r="4246" spans="1:2" x14ac:dyDescent="0.25">
@@ -61236,7 +61236,7 @@
         <v>154</v>
       </c>
       <c r="B4246" t="s">
-        <v>8184</v>
+        <v>8176</v>
       </c>
     </row>
     <row r="4247" spans="1:2" x14ac:dyDescent="0.25">
@@ -61244,7 +61244,7 @@
         <v>156</v>
       </c>
       <c r="B4247" t="s">
-        <v>8185</v>
+        <v>8177</v>
       </c>
     </row>
     <row r="4248" spans="1:2" x14ac:dyDescent="0.25">
@@ -61252,7 +61252,7 @@
         <v>158</v>
       </c>
       <c r="B4248" t="s">
-        <v>8186</v>
+        <v>8178</v>
       </c>
     </row>
     <row r="4249" spans="1:2" x14ac:dyDescent="0.25">
@@ -61260,359 +61260,359 @@
         <v>160</v>
       </c>
       <c r="B4249" t="s">
-        <v>8187</v>
+        <v>8179</v>
       </c>
     </row>
     <row r="4250" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4250" t="s">
-        <v>8188</v>
+        <v>8180</v>
       </c>
       <c r="B4250" t="s">
-        <v>8189</v>
+        <v>8181</v>
       </c>
     </row>
     <row r="4251" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4251" t="s">
-        <v>8190</v>
+        <v>8182</v>
       </c>
       <c r="B4251" t="s">
-        <v>8191</v>
+        <v>8183</v>
       </c>
     </row>
     <row r="4252" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4252" t="s">
-        <v>8192</v>
+        <v>8184</v>
       </c>
       <c r="B4252" t="s">
-        <v>8193</v>
+        <v>8185</v>
       </c>
     </row>
     <row r="4253" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4253" t="s">
-        <v>8194</v>
+        <v>8186</v>
       </c>
       <c r="B4253" t="s">
-        <v>8195</v>
+        <v>8187</v>
       </c>
     </row>
     <row r="4254" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4254" t="s">
-        <v>8196</v>
+        <v>8188</v>
       </c>
       <c r="B4254" t="s">
-        <v>8197</v>
+        <v>8189</v>
       </c>
     </row>
     <row r="4255" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4255" t="s">
-        <v>8198</v>
+        <v>8190</v>
       </c>
       <c r="B4255" t="s">
-        <v>8199</v>
+        <v>8191</v>
       </c>
     </row>
     <row r="4256" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4256" t="s">
-        <v>8200</v>
+        <v>8192</v>
       </c>
       <c r="B4256" t="s">
-        <v>8201</v>
+        <v>8193</v>
       </c>
     </row>
     <row r="4257" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4257" t="s">
-        <v>8202</v>
+        <v>8194</v>
       </c>
       <c r="B4257" t="s">
-        <v>8203</v>
+        <v>8195</v>
       </c>
     </row>
     <row r="4258" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4258" t="s">
-        <v>8204</v>
+        <v>8196</v>
       </c>
       <c r="B4258" t="s">
-        <v>8205</v>
+        <v>8197</v>
       </c>
     </row>
     <row r="4259" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4259" t="s">
-        <v>8206</v>
+        <v>8198</v>
       </c>
       <c r="B4259" t="s">
-        <v>8207</v>
+        <v>8199</v>
       </c>
     </row>
     <row r="4260" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4260" t="s">
-        <v>8208</v>
+        <v>8200</v>
       </c>
       <c r="B4260" t="s">
-        <v>8209</v>
+        <v>8201</v>
       </c>
     </row>
     <row r="4261" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4261" t="s">
-        <v>8210</v>
+        <v>8202</v>
       </c>
       <c r="B4261" t="s">
-        <v>8211</v>
+        <v>8203</v>
       </c>
     </row>
     <row r="4262" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4262" t="s">
-        <v>8212</v>
+        <v>8204</v>
       </c>
       <c r="B4262" t="s">
-        <v>8213</v>
+        <v>8205</v>
       </c>
     </row>
     <row r="4263" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4263" t="s">
-        <v>8214</v>
+        <v>8206</v>
       </c>
       <c r="B4263" t="s">
-        <v>8215</v>
+        <v>8207</v>
       </c>
     </row>
     <row r="4264" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4264" t="s">
-        <v>8216</v>
+        <v>8208</v>
       </c>
       <c r="B4264" t="s">
-        <v>8217</v>
+        <v>8209</v>
       </c>
     </row>
     <row r="4265" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4265" t="s">
-        <v>8218</v>
+        <v>8210</v>
       </c>
       <c r="B4265" t="s">
-        <v>8219</v>
+        <v>8211</v>
       </c>
     </row>
     <row r="4266" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4266" t="s">
-        <v>8220</v>
+        <v>8212</v>
       </c>
       <c r="B4266" t="s">
-        <v>8221</v>
+        <v>8213</v>
       </c>
     </row>
     <row r="4267" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4267" t="s">
-        <v>8222</v>
+        <v>8214</v>
       </c>
       <c r="B4267" t="s">
-        <v>8223</v>
+        <v>8215</v>
       </c>
     </row>
     <row r="4268" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4268" t="s">
-        <v>8224</v>
+        <v>8216</v>
       </c>
       <c r="B4268" t="s">
-        <v>8225</v>
+        <v>8217</v>
       </c>
     </row>
     <row r="4269" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4269" t="s">
-        <v>8226</v>
+        <v>8218</v>
       </c>
       <c r="B4269" t="s">
-        <v>8227</v>
+        <v>8219</v>
       </c>
     </row>
     <row r="4270" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4270" t="s">
-        <v>8780</v>
+        <v>8772</v>
       </c>
       <c r="B4270" t="s">
-        <v>8784</v>
+        <v>8776</v>
       </c>
     </row>
     <row r="4271" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4271" t="s">
-        <v>8781</v>
+        <v>8773</v>
       </c>
       <c r="B4271" t="s">
-        <v>8784</v>
+        <v>8776</v>
       </c>
     </row>
     <row r="4272" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4272" t="s">
-        <v>8782</v>
+        <v>8774</v>
       </c>
       <c r="B4272" t="s">
-        <v>8784</v>
+        <v>8776</v>
       </c>
     </row>
     <row r="4273" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4273" t="s">
-        <v>8783</v>
+        <v>8775</v>
       </c>
       <c r="B4273" t="s">
-        <v>8784</v>
+        <v>8776</v>
       </c>
     </row>
     <row r="4274" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4274" t="s">
-        <v>8228</v>
+        <v>8220</v>
       </c>
       <c r="B4274" t="s">
-        <v>8229</v>
+        <v>8221</v>
       </c>
     </row>
     <row r="4275" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4275" t="s">
-        <v>8230</v>
+        <v>8222</v>
       </c>
       <c r="B4275" t="s">
-        <v>8231</v>
+        <v>8223</v>
       </c>
     </row>
     <row r="4276" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4276" t="s">
-        <v>8232</v>
+        <v>8224</v>
       </c>
       <c r="B4276" t="s">
-        <v>8233</v>
+        <v>8225</v>
       </c>
     </row>
     <row r="4277" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4277" t="s">
-        <v>8234</v>
+        <v>8226</v>
       </c>
       <c r="B4277" t="s">
-        <v>8235</v>
+        <v>8227</v>
       </c>
     </row>
     <row r="4278" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4278" t="s">
-        <v>8236</v>
+        <v>8228</v>
       </c>
       <c r="B4278" t="s">
-        <v>8237</v>
+        <v>8229</v>
       </c>
     </row>
     <row r="4279" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4279" t="s">
-        <v>8238</v>
+        <v>8230</v>
       </c>
       <c r="B4279" t="s">
-        <v>8239</v>
+        <v>8231</v>
       </c>
     </row>
     <row r="4280" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4280" t="s">
-        <v>8240</v>
+        <v>8232</v>
       </c>
       <c r="B4280" t="s">
-        <v>8241</v>
+        <v>8233</v>
       </c>
     </row>
     <row r="4281" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4281" t="s">
-        <v>8242</v>
+        <v>8234</v>
       </c>
       <c r="B4281" t="s">
-        <v>8243</v>
+        <v>8235</v>
       </c>
     </row>
     <row r="4282" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4282" t="s">
-        <v>8244</v>
+        <v>8236</v>
       </c>
       <c r="B4282" t="s">
-        <v>8245</v>
+        <v>8237</v>
       </c>
     </row>
     <row r="4283" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4283" t="s">
-        <v>8246</v>
+        <v>8238</v>
       </c>
       <c r="B4283" t="s">
-        <v>8247</v>
+        <v>8239</v>
       </c>
     </row>
     <row r="4284" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4284" t="s">
-        <v>8248</v>
+        <v>8240</v>
       </c>
       <c r="B4284" t="s">
-        <v>8249</v>
+        <v>8241</v>
       </c>
     </row>
     <row r="4285" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4285" t="s">
-        <v>8250</v>
+        <v>8242</v>
       </c>
       <c r="B4285" t="s">
-        <v>8251</v>
+        <v>8243</v>
       </c>
     </row>
     <row r="4286" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4286" t="s">
-        <v>8252</v>
+        <v>8244</v>
       </c>
       <c r="B4286" t="s">
-        <v>8253</v>
+        <v>8245</v>
       </c>
     </row>
     <row r="4287" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4287" t="s">
-        <v>8254</v>
+        <v>8246</v>
       </c>
       <c r="B4287" t="s">
-        <v>8255</v>
+        <v>8247</v>
       </c>
     </row>
     <row r="4288" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4288" t="s">
-        <v>8256</v>
+        <v>8248</v>
       </c>
       <c r="B4288" t="s">
-        <v>8257</v>
+        <v>8249</v>
       </c>
     </row>
     <row r="4289" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4289" t="s">
-        <v>8258</v>
+        <v>8250</v>
       </c>
       <c r="B4289" t="s">
-        <v>8259</v>
+        <v>8251</v>
       </c>
     </row>
     <row r="4290" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4290" t="s">
-        <v>8260</v>
+        <v>8252</v>
       </c>
       <c r="B4290" t="s">
-        <v>8261</v>
+        <v>8253</v>
       </c>
     </row>
     <row r="4291" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4291" t="s">
-        <v>8262</v>
+        <v>8254</v>
       </c>
       <c r="B4291" t="s">
-        <v>8263</v>
+        <v>8255</v>
       </c>
     </row>
     <row r="4292" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4292" t="s">
-        <v>8264</v>
+        <v>8256</v>
       </c>
       <c r="B4292" t="s">
-        <v>8265</v>
+        <v>8257</v>
       </c>
     </row>
     <row r="4293" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4293" t="s">
-        <v>8266</v>
+        <v>8258</v>
       </c>
       <c r="B4293" t="s">
-        <v>8267</v>
+        <v>8259</v>
       </c>
     </row>
     <row r="4294" spans="1:2" x14ac:dyDescent="0.25">
@@ -61620,7 +61620,7 @@
         <v>#N/A</v>
       </c>
       <c r="B4294" t="s">
-        <v>8268</v>
+        <v>8260</v>
       </c>
     </row>
     <row r="4295" spans="1:2" x14ac:dyDescent="0.25">
@@ -61628,7 +61628,7 @@
         <v>#N/A</v>
       </c>
       <c r="B4295" t="s">
-        <v>8269</v>
+        <v>8261</v>
       </c>
     </row>
     <row r="4296" spans="1:2" x14ac:dyDescent="0.25">
@@ -61636,7 +61636,7 @@
         <v>#N/A</v>
       </c>
       <c r="B4296" t="s">
-        <v>8270</v>
+        <v>8262</v>
       </c>
     </row>
     <row r="4297" spans="1:2" x14ac:dyDescent="0.25">
@@ -61644,7 +61644,7 @@
         <v>#N/A</v>
       </c>
       <c r="B4297" t="s">
-        <v>8271</v>
+        <v>8263</v>
       </c>
     </row>
     <row r="4298" spans="1:2" x14ac:dyDescent="0.25">
@@ -61652,7 +61652,7 @@
         <v>#N/A</v>
       </c>
       <c r="B4298" t="s">
-        <v>8272</v>
+        <v>8264</v>
       </c>
     </row>
     <row r="4299" spans="1:2" x14ac:dyDescent="0.25">
@@ -61660,7 +61660,7 @@
         <v>#N/A</v>
       </c>
       <c r="B4299" t="s">
-        <v>8273</v>
+        <v>8265</v>
       </c>
     </row>
     <row r="4300" spans="1:2" x14ac:dyDescent="0.25">
@@ -61668,7 +61668,7 @@
         <v>#N/A</v>
       </c>
       <c r="B4300" t="s">
-        <v>8274</v>
+        <v>8266</v>
       </c>
     </row>
     <row r="4301" spans="1:2" x14ac:dyDescent="0.25">
@@ -61676,7 +61676,7 @@
         <v>#N/A</v>
       </c>
       <c r="B4301" t="s">
-        <v>8275</v>
+        <v>8267</v>
       </c>
     </row>
     <row r="4302" spans="1:2" x14ac:dyDescent="0.25">
@@ -61684,7 +61684,7 @@
         <v>154</v>
       </c>
       <c r="B4302" t="s">
-        <v>8276</v>
+        <v>8268</v>
       </c>
     </row>
     <row r="4303" spans="1:2" x14ac:dyDescent="0.25">
@@ -61692,7 +61692,7 @@
         <v>156</v>
       </c>
       <c r="B4303" t="s">
-        <v>8277</v>
+        <v>8269</v>
       </c>
     </row>
     <row r="4304" spans="1:2" x14ac:dyDescent="0.25">
@@ -61700,7 +61700,7 @@
         <v>158</v>
       </c>
       <c r="B4304" t="s">
-        <v>8278</v>
+        <v>8270</v>
       </c>
     </row>
     <row r="4305" spans="1:2" x14ac:dyDescent="0.25">
@@ -61708,7 +61708,7 @@
         <v>160</v>
       </c>
       <c r="B4305" t="s">
-        <v>8279</v>
+        <v>8271</v>
       </c>
     </row>
     <row r="4306" spans="1:2" x14ac:dyDescent="0.25">
@@ -61716,7 +61716,7 @@
         <v>154</v>
       </c>
       <c r="B4306" t="s">
-        <v>8280</v>
+        <v>8272</v>
       </c>
     </row>
     <row r="4307" spans="1:2" x14ac:dyDescent="0.25">
@@ -61724,7 +61724,7 @@
         <v>156</v>
       </c>
       <c r="B4307" t="s">
-        <v>8281</v>
+        <v>8273</v>
       </c>
     </row>
     <row r="4308" spans="1:2" x14ac:dyDescent="0.25">
@@ -61732,7 +61732,7 @@
         <v>158</v>
       </c>
       <c r="B4308" t="s">
-        <v>8282</v>
+        <v>8274</v>
       </c>
     </row>
     <row r="4309" spans="1:2" x14ac:dyDescent="0.25">
@@ -61740,7 +61740,7 @@
         <v>160</v>
       </c>
       <c r="B4309" t="s">
-        <v>8283</v>
+        <v>8275</v>
       </c>
     </row>
     <row r="4310" spans="1:2" x14ac:dyDescent="0.25">
@@ -61748,7 +61748,7 @@
         <v>154</v>
       </c>
       <c r="B4310" t="s">
-        <v>8284</v>
+        <v>8276</v>
       </c>
     </row>
     <row r="4311" spans="1:2" x14ac:dyDescent="0.25">
@@ -61756,7 +61756,7 @@
         <v>156</v>
       </c>
       <c r="B4311" t="s">
-        <v>8285</v>
+        <v>8277</v>
       </c>
     </row>
     <row r="4312" spans="1:2" x14ac:dyDescent="0.25">
@@ -61764,7 +61764,7 @@
         <v>158</v>
       </c>
       <c r="B4312" t="s">
-        <v>8286</v>
+        <v>8278</v>
       </c>
     </row>
     <row r="4313" spans="1:2" x14ac:dyDescent="0.25">
@@ -61772,7 +61772,7 @@
         <v>160</v>
       </c>
       <c r="B4313" t="s">
-        <v>8287</v>
+        <v>8279</v>
       </c>
     </row>
     <row r="4314" spans="1:2" x14ac:dyDescent="0.25">
@@ -61780,7 +61780,7 @@
         <v>154</v>
       </c>
       <c r="B4314" t="s">
-        <v>8288</v>
+        <v>8280</v>
       </c>
     </row>
     <row r="4315" spans="1:2" x14ac:dyDescent="0.25">
@@ -61788,7 +61788,7 @@
         <v>156</v>
       </c>
       <c r="B4315" t="s">
-        <v>8289</v>
+        <v>8281</v>
       </c>
     </row>
     <row r="4316" spans="1:2" x14ac:dyDescent="0.25">
@@ -61796,7 +61796,7 @@
         <v>158</v>
       </c>
       <c r="B4316" t="s">
-        <v>8290</v>
+        <v>8282</v>
       </c>
     </row>
     <row r="4317" spans="1:2" x14ac:dyDescent="0.25">
@@ -61804,7 +61804,7 @@
         <v>160</v>
       </c>
       <c r="B4317" t="s">
-        <v>8291</v>
+        <v>8283</v>
       </c>
     </row>
     <row r="4318" spans="1:2" x14ac:dyDescent="0.25">
@@ -61812,7 +61812,7 @@
         <v>154</v>
       </c>
       <c r="B4318" t="s">
-        <v>8292</v>
+        <v>8284</v>
       </c>
     </row>
     <row r="4319" spans="1:2" x14ac:dyDescent="0.25">
@@ -61820,7 +61820,7 @@
         <v>156</v>
       </c>
       <c r="B4319" t="s">
-        <v>8293</v>
+        <v>8285</v>
       </c>
     </row>
     <row r="4320" spans="1:2" x14ac:dyDescent="0.25">
@@ -61828,7 +61828,7 @@
         <v>158</v>
       </c>
       <c r="B4320" t="s">
-        <v>8294</v>
+        <v>8286</v>
       </c>
     </row>
     <row r="4321" spans="1:2" x14ac:dyDescent="0.25">
@@ -61836,7 +61836,7 @@
         <v>160</v>
       </c>
       <c r="B4321" t="s">
-        <v>8295</v>
+        <v>8287</v>
       </c>
     </row>
     <row r="4322" spans="1:2" x14ac:dyDescent="0.25">
@@ -61844,7 +61844,7 @@
         <v>154</v>
       </c>
       <c r="B4322" t="s">
-        <v>8296</v>
+        <v>8288</v>
       </c>
     </row>
     <row r="4323" spans="1:2" x14ac:dyDescent="0.25">
@@ -61852,7 +61852,7 @@
         <v>156</v>
       </c>
       <c r="B4323" t="s">
-        <v>8297</v>
+        <v>8289</v>
       </c>
     </row>
     <row r="4324" spans="1:2" x14ac:dyDescent="0.25">
@@ -61860,7 +61860,7 @@
         <v>158</v>
       </c>
       <c r="B4324" t="s">
-        <v>8298</v>
+        <v>8290</v>
       </c>
     </row>
     <row r="4325" spans="1:2" x14ac:dyDescent="0.25">
@@ -61868,1383 +61868,1383 @@
         <v>160</v>
       </c>
       <c r="B4325" t="s">
-        <v>8299</v>
+        <v>8291</v>
       </c>
     </row>
     <row r="4326" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4326" t="s">
-        <v>8300</v>
+        <v>8292</v>
       </c>
       <c r="B4326" t="s">
-        <v>8301</v>
+        <v>8293</v>
       </c>
     </row>
     <row r="4327" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4327" t="s">
-        <v>8302</v>
+        <v>8294</v>
       </c>
       <c r="B4327" t="s">
-        <v>8303</v>
+        <v>8295</v>
       </c>
     </row>
     <row r="4328" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4328" t="s">
-        <v>8304</v>
+        <v>8296</v>
       </c>
       <c r="B4328" t="s">
-        <v>8305</v>
+        <v>8297</v>
       </c>
     </row>
     <row r="4329" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4329" t="s">
-        <v>8306</v>
+        <v>8298</v>
       </c>
       <c r="B4329" t="s">
-        <v>8307</v>
+        <v>8299</v>
       </c>
     </row>
     <row r="4330" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4330" t="s">
-        <v>8308</v>
+        <v>8300</v>
       </c>
       <c r="B4330" t="s">
-        <v>8309</v>
+        <v>8301</v>
       </c>
     </row>
     <row r="4331" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4331" t="s">
-        <v>8310</v>
+        <v>8302</v>
       </c>
       <c r="B4331" t="s">
-        <v>8311</v>
+        <v>8303</v>
       </c>
     </row>
     <row r="4332" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4332" t="s">
-        <v>8312</v>
+        <v>8304</v>
       </c>
       <c r="B4332" t="s">
-        <v>8313</v>
+        <v>8305</v>
       </c>
     </row>
     <row r="4333" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4333" t="s">
-        <v>8314</v>
+        <v>8306</v>
       </c>
       <c r="B4333" t="s">
-        <v>8315</v>
+        <v>8307</v>
       </c>
     </row>
     <row r="4334" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4334" t="s">
-        <v>8316</v>
+        <v>8308</v>
       </c>
       <c r="B4334" t="s">
-        <v>8317</v>
+        <v>8309</v>
       </c>
     </row>
     <row r="4335" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4335" t="s">
-        <v>8318</v>
+        <v>8310</v>
       </c>
       <c r="B4335" t="s">
-        <v>8319</v>
+        <v>8311</v>
       </c>
     </row>
     <row r="4336" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4336" t="s">
-        <v>8320</v>
+        <v>8312</v>
       </c>
       <c r="B4336" t="s">
-        <v>8321</v>
+        <v>8313</v>
       </c>
     </row>
     <row r="4337" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4337" t="s">
-        <v>8322</v>
+        <v>8314</v>
       </c>
       <c r="B4337" t="s">
-        <v>8323</v>
+        <v>8315</v>
       </c>
     </row>
     <row r="4338" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4338" t="s">
-        <v>8324</v>
+        <v>8316</v>
       </c>
       <c r="B4338" t="s">
-        <v>8325</v>
+        <v>8317</v>
       </c>
     </row>
     <row r="4339" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4339" t="s">
-        <v>8326</v>
+        <v>8318</v>
       </c>
       <c r="B4339" t="s">
-        <v>8327</v>
+        <v>8319</v>
       </c>
     </row>
     <row r="4340" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4340" t="s">
-        <v>8328</v>
+        <v>8320</v>
       </c>
       <c r="B4340" t="s">
-        <v>8329</v>
+        <v>8321</v>
       </c>
     </row>
     <row r="4341" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4341" t="s">
-        <v>8330</v>
+        <v>8322</v>
       </c>
       <c r="B4341" t="s">
-        <v>8331</v>
+        <v>8323</v>
       </c>
     </row>
     <row r="4342" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4342" t="s">
-        <v>8332</v>
+        <v>8324</v>
       </c>
       <c r="B4342" t="s">
-        <v>8333</v>
+        <v>8325</v>
       </c>
     </row>
     <row r="4343" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4343" t="s">
-        <v>8334</v>
+        <v>8326</v>
       </c>
       <c r="B4343" t="s">
-        <v>8335</v>
+        <v>8327</v>
       </c>
     </row>
     <row r="4344" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4344" t="s">
-        <v>8336</v>
+        <v>8328</v>
       </c>
       <c r="B4344" t="s">
-        <v>8337</v>
+        <v>8329</v>
       </c>
     </row>
     <row r="4345" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4345" t="s">
-        <v>8338</v>
+        <v>8330</v>
       </c>
       <c r="B4345" t="s">
-        <v>8339</v>
+        <v>8331</v>
       </c>
     </row>
     <row r="4346" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4346" t="s">
-        <v>8340</v>
+        <v>8332</v>
       </c>
       <c r="B4346" t="s">
-        <v>8341</v>
+        <v>8333</v>
       </c>
     </row>
     <row r="4347" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4347" t="s">
-        <v>8342</v>
+        <v>8334</v>
       </c>
       <c r="B4347" t="s">
-        <v>8343</v>
+        <v>8335</v>
       </c>
     </row>
     <row r="4348" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4348" t="s">
-        <v>8344</v>
+        <v>8336</v>
       </c>
       <c r="B4348" t="s">
-        <v>8345</v>
+        <v>8337</v>
       </c>
     </row>
     <row r="4349" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4349" t="s">
-        <v>8346</v>
+        <v>8338</v>
       </c>
       <c r="B4349" t="s">
-        <v>8347</v>
+        <v>8339</v>
       </c>
     </row>
     <row r="4350" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4350" t="s">
-        <v>8348</v>
+        <v>8340</v>
       </c>
       <c r="B4350" t="s">
-        <v>8349</v>
+        <v>8341</v>
       </c>
     </row>
     <row r="4351" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4351" t="s">
-        <v>8350</v>
+        <v>8342</v>
       </c>
       <c r="B4351" t="s">
-        <v>8351</v>
+        <v>8343</v>
       </c>
     </row>
     <row r="4352" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4352" t="s">
-        <v>8352</v>
+        <v>8344</v>
       </c>
       <c r="B4352" t="s">
-        <v>8353</v>
+        <v>8345</v>
       </c>
     </row>
     <row r="4353" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4353" t="s">
-        <v>8354</v>
+        <v>8346</v>
       </c>
       <c r="B4353" t="s">
-        <v>8355</v>
+        <v>8347</v>
       </c>
     </row>
     <row r="4354" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4354" t="s">
-        <v>8356</v>
+        <v>8348</v>
       </c>
       <c r="B4354" t="s">
-        <v>8357</v>
+        <v>8349</v>
       </c>
     </row>
     <row r="4355" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4355" t="s">
-        <v>8358</v>
+        <v>8350</v>
       </c>
       <c r="B4355" t="s">
-        <v>8359</v>
+        <v>8351</v>
       </c>
     </row>
     <row r="4356" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4356" t="s">
-        <v>8360</v>
+        <v>8352</v>
       </c>
       <c r="B4356" t="s">
-        <v>8361</v>
+        <v>8353</v>
       </c>
     </row>
     <row r="4357" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4357" t="s">
-        <v>8362</v>
+        <v>8354</v>
       </c>
       <c r="B4357" t="s">
-        <v>8363</v>
+        <v>8355</v>
       </c>
     </row>
     <row r="4358" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4358" t="s">
-        <v>8364</v>
+        <v>8356</v>
       </c>
       <c r="B4358" t="s">
-        <v>8365</v>
+        <v>8357</v>
       </c>
     </row>
     <row r="4359" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4359" t="s">
-        <v>8366</v>
+        <v>8358</v>
       </c>
       <c r="B4359" t="s">
-        <v>8367</v>
+        <v>8359</v>
       </c>
     </row>
     <row r="4360" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4360" t="s">
-        <v>8368</v>
+        <v>8360</v>
       </c>
       <c r="B4360" t="s">
-        <v>8369</v>
+        <v>8361</v>
       </c>
     </row>
     <row r="4361" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4361" t="s">
-        <v>8370</v>
+        <v>8362</v>
       </c>
       <c r="B4361" t="s">
-        <v>8371</v>
+        <v>8363</v>
       </c>
     </row>
     <row r="4362" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4362" t="s">
-        <v>8372</v>
+        <v>8364</v>
       </c>
       <c r="B4362" t="s">
-        <v>8373</v>
+        <v>8365</v>
       </c>
     </row>
     <row r="4363" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4363" t="s">
-        <v>8374</v>
+        <v>8366</v>
       </c>
       <c r="B4363" t="s">
-        <v>8375</v>
+        <v>8367</v>
       </c>
     </row>
     <row r="4364" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4364" t="s">
-        <v>8376</v>
+        <v>8368</v>
       </c>
       <c r="B4364" t="s">
-        <v>8377</v>
+        <v>8369</v>
       </c>
     </row>
     <row r="4365" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4365" t="s">
-        <v>8378</v>
+        <v>8370</v>
       </c>
       <c r="B4365" t="s">
-        <v>8379</v>
+        <v>8371</v>
       </c>
     </row>
     <row r="4366" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4366" t="s">
-        <v>8380</v>
+        <v>8372</v>
       </c>
       <c r="B4366" t="s">
-        <v>8381</v>
+        <v>8373</v>
       </c>
     </row>
     <row r="4367" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4367" t="s">
-        <v>8382</v>
+        <v>8374</v>
       </c>
       <c r="B4367" t="s">
-        <v>8383</v>
+        <v>8375</v>
       </c>
     </row>
     <row r="4368" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4368" t="s">
-        <v>8384</v>
+        <v>8376</v>
       </c>
       <c r="B4368" t="s">
-        <v>8385</v>
+        <v>8377</v>
       </c>
     </row>
     <row r="4369" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4369" t="s">
-        <v>8386</v>
+        <v>8378</v>
       </c>
       <c r="B4369" t="s">
-        <v>8387</v>
+        <v>8379</v>
       </c>
     </row>
     <row r="4370" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4370" t="s">
-        <v>8388</v>
+        <v>8380</v>
       </c>
       <c r="B4370" t="s">
-        <v>8389</v>
+        <v>8381</v>
       </c>
     </row>
     <row r="4371" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4371" t="s">
-        <v>8390</v>
+        <v>8382</v>
       </c>
       <c r="B4371" t="s">
-        <v>8391</v>
+        <v>8383</v>
       </c>
     </row>
     <row r="4372" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4372" t="s">
-        <v>8392</v>
+        <v>8384</v>
       </c>
       <c r="B4372" t="s">
-        <v>8393</v>
+        <v>8385</v>
       </c>
     </row>
     <row r="4373" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4373" t="s">
-        <v>8394</v>
+        <v>8386</v>
       </c>
       <c r="B4373" t="s">
-        <v>8395</v>
+        <v>8387</v>
       </c>
     </row>
     <row r="4374" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4374" t="s">
-        <v>8396</v>
+        <v>8388</v>
       </c>
       <c r="B4374" t="s">
-        <v>8397</v>
+        <v>8389</v>
       </c>
     </row>
     <row r="4375" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4375" t="s">
-        <v>8398</v>
+        <v>8390</v>
       </c>
       <c r="B4375" t="s">
-        <v>8399</v>
+        <v>8391</v>
       </c>
     </row>
     <row r="4376" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4376" t="s">
-        <v>8400</v>
+        <v>8392</v>
       </c>
       <c r="B4376" t="s">
-        <v>8401</v>
+        <v>8393</v>
       </c>
     </row>
     <row r="4377" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4377" t="s">
-        <v>8402</v>
+        <v>8394</v>
       </c>
       <c r="B4377" t="s">
-        <v>8403</v>
+        <v>8395</v>
       </c>
     </row>
     <row r="4378" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4378" t="s">
-        <v>8404</v>
+        <v>8396</v>
       </c>
       <c r="B4378" t="s">
-        <v>8405</v>
+        <v>8397</v>
       </c>
     </row>
     <row r="4379" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4379" t="s">
-        <v>8406</v>
+        <v>8398</v>
       </c>
       <c r="B4379" t="s">
-        <v>8407</v>
+        <v>8399</v>
       </c>
     </row>
     <row r="4380" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4380" t="s">
-        <v>8408</v>
+        <v>8400</v>
       </c>
       <c r="B4380" t="s">
-        <v>8409</v>
+        <v>8401</v>
       </c>
     </row>
     <row r="4381" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4381" t="s">
-        <v>8410</v>
+        <v>8402</v>
       </c>
       <c r="B4381" t="s">
-        <v>8411</v>
+        <v>8403</v>
       </c>
     </row>
     <row r="4382" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4382" t="s">
-        <v>8412</v>
+        <v>8404</v>
       </c>
       <c r="B4382" t="s">
-        <v>8413</v>
+        <v>8405</v>
       </c>
     </row>
     <row r="4383" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4383" t="s">
-        <v>8414</v>
+        <v>8406</v>
       </c>
       <c r="B4383" t="s">
-        <v>8415</v>
+        <v>8407</v>
       </c>
     </row>
     <row r="4384" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4384" t="s">
-        <v>8416</v>
+        <v>8408</v>
       </c>
       <c r="B4384" t="s">
-        <v>8417</v>
+        <v>8409</v>
       </c>
     </row>
     <row r="4385" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4385" t="s">
-        <v>8418</v>
+        <v>8410</v>
       </c>
       <c r="B4385" t="s">
-        <v>8419</v>
+        <v>8411</v>
       </c>
     </row>
     <row r="4386" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4386" t="s">
-        <v>8420</v>
+        <v>8412</v>
       </c>
       <c r="B4386" t="s">
-        <v>8421</v>
+        <v>8413</v>
       </c>
     </row>
     <row r="4387" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4387" t="s">
-        <v>8422</v>
+        <v>8414</v>
       </c>
       <c r="B4387" t="s">
-        <v>8423</v>
+        <v>8415</v>
       </c>
     </row>
     <row r="4388" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4388" t="s">
-        <v>8424</v>
+        <v>8416</v>
       </c>
       <c r="B4388" t="s">
-        <v>8425</v>
+        <v>8417</v>
       </c>
     </row>
     <row r="4389" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4389" t="s">
-        <v>8426</v>
+        <v>8418</v>
       </c>
       <c r="B4389" t="s">
-        <v>8427</v>
+        <v>8419</v>
       </c>
     </row>
     <row r="4390" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4390" t="s">
-        <v>8428</v>
+        <v>8420</v>
       </c>
       <c r="B4390" t="s">
-        <v>8429</v>
+        <v>8421</v>
       </c>
     </row>
     <row r="4391" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4391" t="s">
-        <v>8430</v>
+        <v>8422</v>
       </c>
       <c r="B4391" t="s">
-        <v>8431</v>
+        <v>8423</v>
       </c>
     </row>
     <row r="4392" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4392" t="s">
-        <v>8432</v>
+        <v>8424</v>
       </c>
       <c r="B4392" t="s">
-        <v>8433</v>
+        <v>8425</v>
       </c>
     </row>
     <row r="4393" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4393" t="s">
-        <v>8434</v>
+        <v>8426</v>
       </c>
       <c r="B4393" t="s">
-        <v>8435</v>
+        <v>8427</v>
       </c>
     </row>
     <row r="4394" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4394" t="s">
-        <v>8436</v>
+        <v>8428</v>
       </c>
       <c r="B4394" t="s">
-        <v>8437</v>
+        <v>8429</v>
       </c>
     </row>
     <row r="4395" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4395" t="s">
-        <v>8438</v>
+        <v>8430</v>
       </c>
       <c r="B4395" t="s">
-        <v>8439</v>
+        <v>8431</v>
       </c>
     </row>
     <row r="4396" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4396" t="s">
-        <v>8440</v>
+        <v>8432</v>
       </c>
       <c r="B4396" t="s">
-        <v>8441</v>
+        <v>8433</v>
       </c>
     </row>
     <row r="4397" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4397" t="s">
-        <v>8442</v>
+        <v>8434</v>
       </c>
       <c r="B4397" t="s">
-        <v>8443</v>
+        <v>8435</v>
       </c>
     </row>
     <row r="4398" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4398" t="s">
-        <v>8444</v>
+        <v>8436</v>
       </c>
       <c r="B4398" t="s">
-        <v>8445</v>
+        <v>8437</v>
       </c>
     </row>
     <row r="4399" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4399" t="s">
-        <v>8446</v>
+        <v>8438</v>
       </c>
       <c r="B4399" t="s">
-        <v>8447</v>
+        <v>8439</v>
       </c>
     </row>
     <row r="4400" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4400" t="s">
-        <v>8448</v>
+        <v>8440</v>
       </c>
       <c r="B4400" t="s">
-        <v>8449</v>
+        <v>8441</v>
       </c>
     </row>
     <row r="4401" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4401" t="s">
-        <v>8450</v>
+        <v>8442</v>
       </c>
       <c r="B4401" t="s">
-        <v>8451</v>
+        <v>8443</v>
       </c>
     </row>
     <row r="4402" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4402" t="s">
-        <v>8452</v>
+        <v>8444</v>
       </c>
       <c r="B4402" t="s">
-        <v>8301</v>
+        <v>8293</v>
       </c>
     </row>
     <row r="4403" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4403" t="s">
-        <v>8453</v>
+        <v>8445</v>
       </c>
       <c r="B4403" t="s">
-        <v>8303</v>
+        <v>8295</v>
       </c>
     </row>
     <row r="4404" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4404" t="s">
-        <v>8454</v>
+        <v>8446</v>
       </c>
       <c r="B4404" t="s">
-        <v>8305</v>
+        <v>8297</v>
       </c>
     </row>
     <row r="4405" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4405" t="s">
-        <v>8455</v>
+        <v>8447</v>
       </c>
       <c r="B4405" t="s">
-        <v>8307</v>
+        <v>8299</v>
       </c>
     </row>
     <row r="4406" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4406" t="s">
-        <v>8456</v>
+        <v>8448</v>
       </c>
       <c r="B4406" t="s">
-        <v>8457</v>
+        <v>8449</v>
       </c>
     </row>
     <row r="4407" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4407" t="s">
-        <v>8458</v>
+        <v>8450</v>
       </c>
       <c r="B4407" t="s">
-        <v>8459</v>
+        <v>8451</v>
       </c>
     </row>
     <row r="4408" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4408" t="s">
-        <v>8460</v>
+        <v>8452</v>
       </c>
       <c r="B4408" t="s">
-        <v>8461</v>
+        <v>8453</v>
       </c>
     </row>
     <row r="4409" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4409" t="s">
-        <v>8462</v>
+        <v>8454</v>
       </c>
       <c r="B4409" t="s">
-        <v>8463</v>
+        <v>8455</v>
       </c>
     </row>
     <row r="4410" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4410" t="s">
-        <v>8464</v>
+        <v>8456</v>
       </c>
       <c r="B4410" t="s">
-        <v>8465</v>
+        <v>8457</v>
       </c>
     </row>
     <row r="4411" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4411" t="s">
-        <v>8466</v>
+        <v>8458</v>
       </c>
       <c r="B4411" t="s">
-        <v>8467</v>
+        <v>8459</v>
       </c>
     </row>
     <row r="4412" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4412" t="s">
-        <v>8468</v>
+        <v>8460</v>
       </c>
       <c r="B4412" t="s">
-        <v>8469</v>
+        <v>8461</v>
       </c>
     </row>
     <row r="4413" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4413" t="s">
-        <v>8470</v>
+        <v>8462</v>
       </c>
       <c r="B4413" t="s">
-        <v>8471</v>
+        <v>8463</v>
       </c>
     </row>
     <row r="4414" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4414" t="s">
-        <v>8472</v>
+        <v>8464</v>
       </c>
       <c r="B4414" t="s">
-        <v>8473</v>
+        <v>8465</v>
       </c>
     </row>
     <row r="4415" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4415" t="s">
-        <v>8474</v>
+        <v>8466</v>
       </c>
       <c r="B4415" t="s">
-        <v>8475</v>
+        <v>8467</v>
       </c>
     </row>
     <row r="4416" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4416" t="s">
-        <v>8476</v>
+        <v>8468</v>
       </c>
       <c r="B4416" t="s">
-        <v>8477</v>
+        <v>8469</v>
       </c>
     </row>
     <row r="4417" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4417" t="s">
-        <v>8478</v>
+        <v>8470</v>
       </c>
       <c r="B4417" t="s">
-        <v>8479</v>
+        <v>8471</v>
       </c>
     </row>
     <row r="4418" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4418" t="s">
-        <v>8480</v>
+        <v>8472</v>
       </c>
       <c r="B4418" t="s">
-        <v>8481</v>
+        <v>8473</v>
       </c>
     </row>
     <row r="4419" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4419" t="s">
-        <v>8482</v>
+        <v>8474</v>
       </c>
       <c r="B4419" t="s">
-        <v>8483</v>
+        <v>8475</v>
       </c>
     </row>
     <row r="4420" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4420" t="s">
-        <v>8484</v>
+        <v>8476</v>
       </c>
       <c r="B4420" t="s">
-        <v>8485</v>
+        <v>8477</v>
       </c>
     </row>
     <row r="4421" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4421" t="s">
-        <v>8486</v>
+        <v>8478</v>
       </c>
       <c r="B4421" t="s">
-        <v>8487</v>
+        <v>8479</v>
       </c>
     </row>
     <row r="4422" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4422" t="s">
-        <v>8488</v>
+        <v>8480</v>
       </c>
       <c r="B4422" t="s">
-        <v>8489</v>
+        <v>8481</v>
       </c>
     </row>
     <row r="4423" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4423" t="s">
-        <v>8490</v>
+        <v>8482</v>
       </c>
       <c r="B4423" t="s">
-        <v>8491</v>
+        <v>8483</v>
       </c>
     </row>
     <row r="4424" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4424" t="s">
-        <v>8492</v>
+        <v>8484</v>
       </c>
       <c r="B4424" t="s">
-        <v>8493</v>
+        <v>8485</v>
       </c>
     </row>
     <row r="4425" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4425" t="s">
-        <v>8494</v>
+        <v>8486</v>
       </c>
       <c r="B4425" t="s">
-        <v>8495</v>
+        <v>8487</v>
       </c>
     </row>
     <row r="4426" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4426" t="s">
-        <v>8496</v>
+        <v>8488</v>
       </c>
       <c r="B4426" t="s">
-        <v>8497</v>
+        <v>8489</v>
       </c>
     </row>
     <row r="4427" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4427" t="s">
-        <v>8498</v>
+        <v>8490</v>
       </c>
       <c r="B4427" t="s">
-        <v>8499</v>
+        <v>8491</v>
       </c>
     </row>
     <row r="4428" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4428" t="s">
-        <v>8500</v>
+        <v>8492</v>
       </c>
       <c r="B4428" t="s">
-        <v>8501</v>
+        <v>8493</v>
       </c>
     </row>
     <row r="4429" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4429" t="s">
-        <v>8502</v>
+        <v>8494</v>
       </c>
       <c r="B4429" t="s">
-        <v>8503</v>
+        <v>8495</v>
       </c>
     </row>
     <row r="4430" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4430" t="s">
-        <v>8504</v>
+        <v>8496</v>
       </c>
       <c r="B4430" t="s">
-        <v>8505</v>
+        <v>8497</v>
       </c>
     </row>
     <row r="4431" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4431" t="s">
-        <v>8506</v>
+        <v>8498</v>
       </c>
       <c r="B4431" t="s">
-        <v>8507</v>
+        <v>8499</v>
       </c>
     </row>
     <row r="4432" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4432" t="s">
-        <v>8508</v>
+        <v>8500</v>
       </c>
       <c r="B4432" t="s">
-        <v>8509</v>
+        <v>8501</v>
       </c>
     </row>
     <row r="4433" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4433" t="s">
-        <v>8510</v>
+        <v>8502</v>
       </c>
       <c r="B4433" t="s">
-        <v>8511</v>
+        <v>8503</v>
       </c>
     </row>
     <row r="4434" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4434" t="s">
-        <v>8512</v>
+        <v>8504</v>
       </c>
       <c r="B4434" t="s">
-        <v>8513</v>
+        <v>8505</v>
       </c>
     </row>
     <row r="4435" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4435" t="s">
-        <v>8514</v>
+        <v>8506</v>
       </c>
       <c r="B4435" t="s">
-        <v>8515</v>
+        <v>8507</v>
       </c>
     </row>
     <row r="4436" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4436" t="s">
-        <v>8516</v>
+        <v>8508</v>
       </c>
       <c r="B4436" t="s">
-        <v>8517</v>
+        <v>8509</v>
       </c>
     </row>
     <row r="4437" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4437" t="s">
-        <v>8518</v>
+        <v>8510</v>
       </c>
       <c r="B4437" t="s">
-        <v>8519</v>
+        <v>8511</v>
       </c>
     </row>
     <row r="4438" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4438" t="s">
-        <v>8520</v>
+        <v>8512</v>
       </c>
       <c r="B4438" t="s">
-        <v>8521</v>
+        <v>8513</v>
       </c>
     </row>
     <row r="4439" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4439" t="s">
-        <v>8522</v>
+        <v>8514</v>
       </c>
       <c r="B4439" t="s">
-        <v>8523</v>
+        <v>8515</v>
       </c>
     </row>
     <row r="4440" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4440" t="s">
-        <v>8524</v>
+        <v>8516</v>
       </c>
       <c r="B4440" t="s">
-        <v>8525</v>
+        <v>8517</v>
       </c>
     </row>
     <row r="4441" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4441" t="s">
-        <v>8526</v>
+        <v>8518</v>
       </c>
       <c r="B4441" t="s">
-        <v>8527</v>
+        <v>8519</v>
       </c>
     </row>
     <row r="4442" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4442" t="s">
-        <v>8528</v>
+        <v>8520</v>
       </c>
       <c r="B4442" t="s">
-        <v>8529</v>
+        <v>8521</v>
       </c>
     </row>
     <row r="4443" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4443" t="s">
-        <v>8530</v>
+        <v>8522</v>
       </c>
       <c r="B4443" t="s">
-        <v>8531</v>
+        <v>8523</v>
       </c>
     </row>
     <row r="4444" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4444" t="s">
-        <v>8532</v>
+        <v>8524</v>
       </c>
       <c r="B4444" t="s">
-        <v>8533</v>
+        <v>8525</v>
       </c>
     </row>
     <row r="4445" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4445" t="s">
-        <v>8534</v>
+        <v>8526</v>
       </c>
       <c r="B4445" t="s">
-        <v>8535</v>
+        <v>8527</v>
       </c>
     </row>
     <row r="4446" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4446" t="s">
-        <v>8536</v>
+        <v>8528</v>
       </c>
       <c r="B4446" t="s">
-        <v>8537</v>
+        <v>8529</v>
       </c>
     </row>
     <row r="4447" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4447" t="s">
-        <v>8538</v>
+        <v>8530</v>
       </c>
       <c r="B4447" t="s">
-        <v>8539</v>
+        <v>8531</v>
       </c>
     </row>
     <row r="4448" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4448" t="s">
-        <v>8540</v>
+        <v>8532</v>
       </c>
       <c r="B4448" t="s">
-        <v>8541</v>
+        <v>8533</v>
       </c>
     </row>
     <row r="4449" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4449" t="s">
-        <v>8542</v>
+        <v>8534</v>
       </c>
       <c r="B4449" t="s">
-        <v>8543</v>
+        <v>8535</v>
       </c>
     </row>
     <row r="4450" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4450" t="s">
-        <v>8544</v>
+        <v>8536</v>
       </c>
       <c r="B4450" t="s">
-        <v>8545</v>
+        <v>8537</v>
       </c>
     </row>
     <row r="4451" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4451" t="s">
-        <v>8546</v>
+        <v>8538</v>
       </c>
       <c r="B4451" t="s">
-        <v>8547</v>
+        <v>8539</v>
       </c>
     </row>
     <row r="4452" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4452" t="s">
-        <v>8548</v>
+        <v>8540</v>
       </c>
       <c r="B4452" t="s">
-        <v>8549</v>
+        <v>8541</v>
       </c>
     </row>
     <row r="4453" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4453" t="s">
-        <v>8550</v>
+        <v>8542</v>
       </c>
       <c r="B4453" t="s">
-        <v>8551</v>
+        <v>8543</v>
       </c>
     </row>
     <row r="4454" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4454" t="s">
-        <v>8552</v>
+        <v>8544</v>
       </c>
       <c r="B4454" t="s">
-        <v>8553</v>
+        <v>8545</v>
       </c>
     </row>
     <row r="4455" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4455" t="s">
-        <v>8554</v>
+        <v>8546</v>
       </c>
       <c r="B4455" t="s">
-        <v>8555</v>
+        <v>8547</v>
       </c>
     </row>
     <row r="4456" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4456" t="s">
-        <v>8556</v>
+        <v>8548</v>
       </c>
       <c r="B4456" t="s">
-        <v>8557</v>
+        <v>8549</v>
       </c>
     </row>
     <row r="4457" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4457" t="s">
-        <v>8558</v>
+        <v>8550</v>
       </c>
       <c r="B4457" t="s">
-        <v>8559</v>
+        <v>8551</v>
       </c>
     </row>
     <row r="4458" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4458" t="s">
-        <v>8560</v>
+        <v>8552</v>
       </c>
       <c r="B4458" t="s">
-        <v>8561</v>
+        <v>8553</v>
       </c>
     </row>
     <row r="4459" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4459" t="s">
-        <v>8562</v>
+        <v>8554</v>
       </c>
       <c r="B4459" t="s">
-        <v>8563</v>
+        <v>8555</v>
       </c>
     </row>
     <row r="4460" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4460" t="s">
-        <v>8564</v>
+        <v>8556</v>
       </c>
       <c r="B4460" t="s">
-        <v>8565</v>
+        <v>8557</v>
       </c>
     </row>
     <row r="4461" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4461" t="s">
-        <v>8566</v>
+        <v>8558</v>
       </c>
       <c r="B4461" t="s">
-        <v>8567</v>
+        <v>8559</v>
       </c>
     </row>
     <row r="4462" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4462" t="s">
-        <v>8568</v>
+        <v>8560</v>
       </c>
       <c r="B4462" t="s">
-        <v>8569</v>
+        <v>8561</v>
       </c>
     </row>
     <row r="4463" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4463" t="s">
-        <v>8570</v>
+        <v>8562</v>
       </c>
       <c r="B4463" t="s">
-        <v>8571</v>
+        <v>8563</v>
       </c>
     </row>
     <row r="4464" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4464" t="s">
-        <v>8572</v>
+        <v>8564</v>
       </c>
       <c r="B4464" t="s">
-        <v>8573</v>
+        <v>8565</v>
       </c>
     </row>
     <row r="4465" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4465" t="s">
-        <v>8574</v>
+        <v>8566</v>
       </c>
       <c r="B4465" t="s">
-        <v>8575</v>
+        <v>8567</v>
       </c>
     </row>
     <row r="4466" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4466" t="s">
-        <v>8576</v>
+        <v>8568</v>
       </c>
       <c r="B4466" t="s">
-        <v>8577</v>
+        <v>8569</v>
       </c>
     </row>
     <row r="4467" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4467" t="s">
-        <v>8578</v>
+        <v>8570</v>
       </c>
       <c r="B4467" t="s">
-        <v>8579</v>
+        <v>8571</v>
       </c>
     </row>
     <row r="4468" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4468" t="s">
-        <v>8580</v>
+        <v>8572</v>
       </c>
       <c r="B4468" t="s">
-        <v>8581</v>
+        <v>8573</v>
       </c>
     </row>
     <row r="4469" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4469" t="s">
-        <v>8582</v>
+        <v>8574</v>
       </c>
       <c r="B4469" t="s">
-        <v>8583</v>
+        <v>8575</v>
       </c>
     </row>
     <row r="4470" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4470" t="s">
-        <v>8584</v>
+        <v>8576</v>
       </c>
       <c r="B4470" t="s">
-        <v>8585</v>
+        <v>8577</v>
       </c>
     </row>
     <row r="4471" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4471" t="s">
-        <v>8586</v>
+        <v>8578</v>
       </c>
       <c r="B4471" t="s">
-        <v>8587</v>
+        <v>8579</v>
       </c>
     </row>
     <row r="4472" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4472" t="s">
-        <v>8588</v>
+        <v>8580</v>
       </c>
       <c r="B4472" t="s">
-        <v>8589</v>
+        <v>8581</v>
       </c>
     </row>
     <row r="4473" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4473" t="s">
-        <v>8590</v>
+        <v>8582</v>
       </c>
       <c r="B4473" t="s">
-        <v>8591</v>
+        <v>8583</v>
       </c>
     </row>
     <row r="4474" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4474" t="s">
-        <v>8592</v>
+        <v>8584</v>
       </c>
       <c r="B4474" t="s">
-        <v>8593</v>
+        <v>8585</v>
       </c>
     </row>
     <row r="4475" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4475" t="s">
-        <v>8594</v>
+        <v>8586</v>
       </c>
       <c r="B4475" t="s">
-        <v>8595</v>
+        <v>8587</v>
       </c>
     </row>
     <row r="4476" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4476" t="s">
-        <v>8596</v>
+        <v>8588</v>
       </c>
       <c r="B4476" t="s">
-        <v>8597</v>
+        <v>8589</v>
       </c>
     </row>
     <row r="4477" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4477" t="s">
-        <v>8598</v>
+        <v>8590</v>
       </c>
       <c r="B4477" t="s">
-        <v>8599</v>
+        <v>8591</v>
       </c>
     </row>
     <row r="4478" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4478" t="s">
-        <v>8600</v>
+        <v>8592</v>
       </c>
       <c r="B4478" t="s">
-        <v>8601</v>
+        <v>8593</v>
       </c>
     </row>
     <row r="4479" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4479" t="s">
-        <v>8602</v>
+        <v>8594</v>
       </c>
       <c r="B4479" t="s">
-        <v>8603</v>
+        <v>8595</v>
       </c>
     </row>
     <row r="4480" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4480" t="s">
-        <v>8604</v>
+        <v>8596</v>
       </c>
       <c r="B4480" t="s">
-        <v>8605</v>
+        <v>8597</v>
       </c>
     </row>
     <row r="4481" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4481" t="s">
-        <v>8606</v>
+        <v>8598</v>
       </c>
       <c r="B4481" t="s">
-        <v>8607</v>
+        <v>8599</v>
       </c>
     </row>
     <row r="4482" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4482" t="s">
-        <v>8608</v>
+        <v>8600</v>
       </c>
       <c r="B4482" t="s">
-        <v>8609</v>
+        <v>8601</v>
       </c>
     </row>
     <row r="4483" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4483" t="s">
-        <v>8610</v>
+        <v>8602</v>
       </c>
       <c r="B4483" t="s">
-        <v>8611</v>
+        <v>8603</v>
       </c>
     </row>
     <row r="4484" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4484" t="s">
-        <v>8612</v>
+        <v>8604</v>
       </c>
       <c r="B4484" t="s">
-        <v>8613</v>
+        <v>8605</v>
       </c>
     </row>
     <row r="4485" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4485" t="s">
-        <v>8614</v>
+        <v>8606</v>
       </c>
       <c r="B4485" t="s">
-        <v>8615</v>
+        <v>8607</v>
       </c>
     </row>
     <row r="4486" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4486" t="s">
-        <v>8616</v>
+        <v>8608</v>
       </c>
       <c r="B4486" t="s">
-        <v>8617</v>
+        <v>8609</v>
       </c>
     </row>
     <row r="4487" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4487" t="s">
-        <v>8618</v>
+        <v>8610</v>
       </c>
       <c r="B4487" t="s">
-        <v>8619</v>
+        <v>8611</v>
       </c>
     </row>
     <row r="4488" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4488" t="s">
-        <v>8620</v>
+        <v>8612</v>
       </c>
       <c r="B4488" t="s">
-        <v>8621</v>
+        <v>8613</v>
       </c>
     </row>
     <row r="4489" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4489" t="s">
-        <v>8622</v>
+        <v>8614</v>
       </c>
       <c r="B4489" t="s">
-        <v>8623</v>
+        <v>8615</v>
       </c>
     </row>
     <row r="4490" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4490" t="s">
-        <v>8624</v>
+        <v>8616</v>
       </c>
       <c r="B4490" t="s">
-        <v>8625</v>
+        <v>8617</v>
       </c>
     </row>
     <row r="4491" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4491" t="s">
-        <v>8626</v>
+        <v>8618</v>
       </c>
       <c r="B4491" t="s">
-        <v>8627</v>
+        <v>8619</v>
       </c>
     </row>
     <row r="4492" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4492" t="s">
-        <v>8628</v>
+        <v>8620</v>
       </c>
       <c r="B4492" t="s">
-        <v>8629</v>
+        <v>8621</v>
       </c>
     </row>
     <row r="4493" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4493" t="s">
-        <v>8630</v>
+        <v>8622</v>
       </c>
       <c r="B4493" t="s">
-        <v>8631</v>
+        <v>8623</v>
       </c>
     </row>
     <row r="4494" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4494" t="s">
-        <v>8632</v>
+        <v>8624</v>
       </c>
       <c r="B4494" t="s">
-        <v>8633</v>
+        <v>8625</v>
       </c>
     </row>
     <row r="4495" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4495" t="s">
-        <v>8634</v>
+        <v>8626</v>
       </c>
       <c r="B4495" t="s">
-        <v>8635</v>
+        <v>8627</v>
       </c>
     </row>
     <row r="4496" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4496" t="s">
-        <v>8636</v>
+        <v>8628</v>
       </c>
       <c r="B4496" t="s">
-        <v>8637</v>
+        <v>8629</v>
       </c>
     </row>
     <row r="4497" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4497" t="s">
-        <v>8638</v>
+        <v>8630</v>
       </c>
       <c r="B4497" t="s">
-        <v>8639</v>
+        <v>8631</v>
       </c>
     </row>
     <row r="4498" spans="1:2" x14ac:dyDescent="0.25">
@@ -63252,7 +63252,7 @@
         <v>5404</v>
       </c>
       <c r="B4498" t="s">
-        <v>8640</v>
+        <v>8632</v>
       </c>
     </row>
     <row r="4499" spans="1:2" x14ac:dyDescent="0.25">
@@ -63260,7 +63260,7 @@
         <v>5406</v>
       </c>
       <c r="B4499" t="s">
-        <v>8641</v>
+        <v>8633</v>
       </c>
     </row>
     <row r="4500" spans="1:2" x14ac:dyDescent="0.25">
@@ -63268,7 +63268,7 @@
         <v>5408</v>
       </c>
       <c r="B4500" t="s">
-        <v>8642</v>
+        <v>8634</v>
       </c>
     </row>
     <row r="4501" spans="1:2" x14ac:dyDescent="0.25">
@@ -63276,556 +63276,556 @@
         <v>5410</v>
       </c>
       <c r="B4501" t="s">
-        <v>8643</v>
+        <v>8635</v>
       </c>
     </row>
     <row r="4502" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4502" t="s">
-        <v>8644</v>
+        <v>8636</v>
       </c>
       <c r="B4502" t="s">
-        <v>8645</v>
+        <v>8637</v>
       </c>
     </row>
     <row r="4503" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4503" t="s">
-        <v>8646</v>
+        <v>8638</v>
       </c>
       <c r="B4503" t="s">
-        <v>8647</v>
+        <v>8639</v>
       </c>
     </row>
     <row r="4504" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4504" t="s">
-        <v>8648</v>
+        <v>8640</v>
       </c>
       <c r="B4504" t="s">
-        <v>8649</v>
+        <v>8641</v>
       </c>
     </row>
     <row r="4505" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4505" t="s">
-        <v>8650</v>
+        <v>8642</v>
       </c>
       <c r="B4505" t="s">
-        <v>8651</v>
+        <v>8643</v>
       </c>
     </row>
     <row r="4506" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4506" t="s">
-        <v>8652</v>
+        <v>8644</v>
       </c>
       <c r="B4506" t="s">
-        <v>8653</v>
+        <v>8645</v>
       </c>
     </row>
     <row r="4507" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4507" t="s">
-        <v>8654</v>
+        <v>8646</v>
       </c>
       <c r="B4507" t="s">
-        <v>8655</v>
+        <v>8647</v>
       </c>
     </row>
     <row r="4508" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4508" t="s">
-        <v>8656</v>
+        <v>8648</v>
       </c>
       <c r="B4508" t="s">
-        <v>8657</v>
+        <v>8649</v>
       </c>
     </row>
     <row r="4509" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4509" t="s">
-        <v>8658</v>
+        <v>8650</v>
       </c>
       <c r="B4509" t="s">
-        <v>8659</v>
+        <v>8651</v>
       </c>
     </row>
     <row r="4510" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4510" t="s">
-        <v>8660</v>
+        <v>8652</v>
       </c>
       <c r="B4510" t="s">
-        <v>8661</v>
+        <v>8653</v>
       </c>
     </row>
     <row r="4511" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4511" t="s">
-        <v>8662</v>
+        <v>8654</v>
       </c>
       <c r="B4511" t="s">
-        <v>8663</v>
+        <v>8655</v>
       </c>
     </row>
     <row r="4512" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4512" t="s">
-        <v>8664</v>
+        <v>8656</v>
       </c>
       <c r="B4512" t="s">
-        <v>8665</v>
+        <v>8657</v>
       </c>
     </row>
     <row r="4513" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4513" t="s">
-        <v>8666</v>
+        <v>8658</v>
       </c>
       <c r="B4513" t="s">
-        <v>8667</v>
+        <v>8659</v>
       </c>
     </row>
     <row r="4514" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4514" t="s">
-        <v>8668</v>
+        <v>8660</v>
       </c>
       <c r="B4514" t="s">
-        <v>8669</v>
+        <v>8661</v>
       </c>
     </row>
     <row r="4515" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4515" t="s">
-        <v>8670</v>
+        <v>8662</v>
       </c>
       <c r="B4515" t="s">
-        <v>8671</v>
+        <v>8663</v>
       </c>
     </row>
     <row r="4516" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4516" t="s">
-        <v>8672</v>
+        <v>8664</v>
       </c>
       <c r="B4516" t="s">
-        <v>8673</v>
+        <v>8665</v>
       </c>
     </row>
     <row r="4517" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4517" t="s">
-        <v>8674</v>
+        <v>8666</v>
       </c>
       <c r="B4517" t="s">
-        <v>8675</v>
+        <v>8667</v>
       </c>
     </row>
     <row r="4518" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4518" t="s">
-        <v>8676</v>
+        <v>8668</v>
       </c>
       <c r="B4518" t="s">
-        <v>8677</v>
+        <v>8669</v>
       </c>
     </row>
     <row r="4519" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4519" t="s">
-        <v>8678</v>
+        <v>8670</v>
       </c>
       <c r="B4519" t="s">
-        <v>8679</v>
+        <v>8671</v>
       </c>
     </row>
     <row r="4520" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4520" t="s">
-        <v>8680</v>
+        <v>8672</v>
       </c>
       <c r="B4520" t="s">
-        <v>8681</v>
+        <v>8673</v>
       </c>
     </row>
     <row r="4521" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4521" t="s">
-        <v>8682</v>
+        <v>8674</v>
       </c>
       <c r="B4521" t="s">
-        <v>8683</v>
+        <v>8675</v>
       </c>
     </row>
     <row r="4522" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4522" t="s">
-        <v>8684</v>
+        <v>8676</v>
       </c>
       <c r="B4522" t="s">
-        <v>8685</v>
+        <v>8677</v>
       </c>
     </row>
     <row r="4523" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4523" t="s">
-        <v>8686</v>
+        <v>8678</v>
       </c>
       <c r="B4523" t="s">
-        <v>8687</v>
+        <v>8679</v>
       </c>
     </row>
     <row r="4524" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4524" t="s">
-        <v>8688</v>
+        <v>8680</v>
       </c>
       <c r="B4524" t="s">
-        <v>8689</v>
+        <v>8681</v>
       </c>
     </row>
     <row r="4525" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4525" t="s">
-        <v>8690</v>
+        <v>8682</v>
       </c>
       <c r="B4525" t="s">
-        <v>8691</v>
+        <v>8683</v>
       </c>
     </row>
     <row r="4526" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4526" t="s">
-        <v>8692</v>
+        <v>8684</v>
       </c>
       <c r="B4526" t="s">
-        <v>8693</v>
+        <v>8685</v>
       </c>
     </row>
     <row r="4527" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4527" t="s">
-        <v>8694</v>
+        <v>8686</v>
       </c>
       <c r="B4527" t="s">
-        <v>8695</v>
+        <v>8687</v>
       </c>
     </row>
     <row r="4528" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4528" t="s">
-        <v>8696</v>
+        <v>8688</v>
       </c>
       <c r="B4528" t="s">
-        <v>8697</v>
+        <v>8689</v>
       </c>
     </row>
     <row r="4529" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4529" t="s">
-        <v>8698</v>
+        <v>8690</v>
       </c>
       <c r="B4529" t="s">
-        <v>8699</v>
+        <v>8691</v>
       </c>
     </row>
     <row r="4530" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4530" t="s">
-        <v>8700</v>
+        <v>8692</v>
       </c>
       <c r="B4530" t="s">
-        <v>8701</v>
+        <v>8693</v>
       </c>
     </row>
     <row r="4531" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4531" t="s">
-        <v>8702</v>
+        <v>8694</v>
       </c>
       <c r="B4531" t="s">
-        <v>8703</v>
+        <v>8695</v>
       </c>
     </row>
     <row r="4532" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4532" t="s">
-        <v>8704</v>
+        <v>8696</v>
       </c>
       <c r="B4532" t="s">
-        <v>8705</v>
+        <v>8697</v>
       </c>
     </row>
     <row r="4533" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4533" t="s">
-        <v>8706</v>
+        <v>8698</v>
       </c>
       <c r="B4533" t="s">
-        <v>8707</v>
+        <v>8699</v>
       </c>
     </row>
     <row r="4534" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4534" t="s">
-        <v>8708</v>
+        <v>8700</v>
       </c>
       <c r="B4534" t="s">
-        <v>8709</v>
+        <v>8701</v>
       </c>
     </row>
     <row r="4535" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4535" t="s">
-        <v>8710</v>
+        <v>8702</v>
       </c>
       <c r="B4535" t="s">
-        <v>8711</v>
+        <v>8703</v>
       </c>
     </row>
     <row r="4536" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4536" t="s">
-        <v>8712</v>
+        <v>8704</v>
       </c>
       <c r="B4536" t="s">
-        <v>8713</v>
+        <v>8705</v>
       </c>
     </row>
     <row r="4537" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4537" t="s">
-        <v>8714</v>
+        <v>8706</v>
       </c>
       <c r="B4537" t="s">
-        <v>8715</v>
+        <v>8707</v>
       </c>
     </row>
     <row r="4538" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4538" t="s">
-        <v>8716</v>
+        <v>8708</v>
       </c>
       <c r="B4538" t="s">
-        <v>8717</v>
+        <v>8709</v>
       </c>
     </row>
     <row r="4539" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4539" t="s">
-        <v>8718</v>
+        <v>8710</v>
       </c>
       <c r="B4539" t="s">
-        <v>8719</v>
+        <v>8711</v>
       </c>
     </row>
     <row r="4540" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4540" t="s">
-        <v>8720</v>
+        <v>8712</v>
       </c>
       <c r="B4540" t="s">
-        <v>8721</v>
+        <v>8713</v>
       </c>
     </row>
     <row r="4541" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4541" t="s">
-        <v>8722</v>
+        <v>8714</v>
       </c>
       <c r="B4541" t="s">
-        <v>8723</v>
+        <v>8715</v>
       </c>
     </row>
     <row r="4542" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4542" t="s">
-        <v>8724</v>
+        <v>8716</v>
       </c>
       <c r="B4542" t="s">
-        <v>8725</v>
+        <v>8717</v>
       </c>
     </row>
     <row r="4543" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4543" t="s">
-        <v>8726</v>
+        <v>8718</v>
       </c>
       <c r="B4543" t="s">
-        <v>8727</v>
+        <v>8719</v>
       </c>
     </row>
     <row r="4544" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4544" t="s">
-        <v>8728</v>
+        <v>8720</v>
       </c>
       <c r="B4544" t="s">
-        <v>8729</v>
+        <v>8721</v>
       </c>
     </row>
     <row r="4545" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4545" t="s">
-        <v>8730</v>
+        <v>8722</v>
       </c>
       <c r="B4545" t="s">
-        <v>8731</v>
+        <v>8723</v>
       </c>
     </row>
     <row r="4546" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4546" t="s">
-        <v>8732</v>
+        <v>8724</v>
       </c>
       <c r="B4546" t="s">
-        <v>8733</v>
+        <v>8725</v>
       </c>
     </row>
     <row r="4547" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4547" t="s">
-        <v>8734</v>
+        <v>8726</v>
       </c>
       <c r="B4547" t="s">
-        <v>8735</v>
+        <v>8727</v>
       </c>
     </row>
     <row r="4548" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4548" t="s">
-        <v>8736</v>
+        <v>8728</v>
       </c>
       <c r="B4548" t="s">
-        <v>8737</v>
+        <v>8729</v>
       </c>
     </row>
     <row r="4549" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4549" t="s">
-        <v>8738</v>
+        <v>8730</v>
       </c>
       <c r="B4549" t="s">
-        <v>8739</v>
+        <v>8731</v>
       </c>
     </row>
     <row r="4550" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4550" t="s">
-        <v>8740</v>
+        <v>8732</v>
       </c>
       <c r="B4550" t="s">
-        <v>8741</v>
+        <v>8733</v>
       </c>
     </row>
     <row r="4551" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4551" t="s">
-        <v>8742</v>
+        <v>8734</v>
       </c>
       <c r="B4551" t="s">
-        <v>8743</v>
+        <v>8735</v>
       </c>
     </row>
     <row r="4552" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4552" t="s">
-        <v>8744</v>
+        <v>8736</v>
       </c>
       <c r="B4552" t="s">
-        <v>8745</v>
+        <v>8737</v>
       </c>
     </row>
     <row r="4553" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4553" t="s">
-        <v>8746</v>
+        <v>8738</v>
       </c>
       <c r="B4553" t="s">
-        <v>8747</v>
+        <v>8739</v>
       </c>
     </row>
     <row r="4554" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4554" t="s">
-        <v>8748</v>
+        <v>8740</v>
       </c>
       <c r="B4554" t="s">
-        <v>8749</v>
+        <v>8741</v>
       </c>
     </row>
     <row r="4555" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4555" t="s">
-        <v>8750</v>
+        <v>8742</v>
       </c>
       <c r="B4555" t="s">
-        <v>8751</v>
+        <v>8743</v>
       </c>
     </row>
     <row r="4556" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4556" t="s">
-        <v>8752</v>
+        <v>8744</v>
       </c>
       <c r="B4556" t="s">
-        <v>8753</v>
+        <v>8745</v>
       </c>
     </row>
     <row r="4557" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4557" t="s">
-        <v>8754</v>
+        <v>8746</v>
       </c>
       <c r="B4557" t="s">
-        <v>8755</v>
+        <v>8747</v>
       </c>
     </row>
     <row r="4558" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4558" t="s">
-        <v>8756</v>
+        <v>8748</v>
       </c>
       <c r="B4558" t="s">
-        <v>8757</v>
+        <v>8749</v>
       </c>
     </row>
     <row r="4559" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4559" t="s">
-        <v>8758</v>
+        <v>8750</v>
       </c>
       <c r="B4559" t="s">
-        <v>8759</v>
+        <v>8751</v>
       </c>
     </row>
     <row r="4560" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4560" t="s">
-        <v>8760</v>
+        <v>8752</v>
       </c>
       <c r="B4560" t="s">
-        <v>8761</v>
+        <v>8753</v>
       </c>
     </row>
     <row r="4561" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4561" t="s">
-        <v>8762</v>
+        <v>8754</v>
       </c>
       <c r="B4561" t="s">
-        <v>8763</v>
+        <v>8755</v>
       </c>
     </row>
     <row r="4562" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4562" t="s">
-        <v>8764</v>
+        <v>8756</v>
       </c>
       <c r="B4562" t="s">
-        <v>8765</v>
+        <v>8757</v>
       </c>
     </row>
     <row r="4563" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4563" t="s">
-        <v>8766</v>
+        <v>8758</v>
       </c>
       <c r="B4563" t="s">
-        <v>8767</v>
+        <v>8759</v>
       </c>
     </row>
     <row r="4564" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4564" t="s">
-        <v>8768</v>
+        <v>8760</v>
       </c>
       <c r="B4564" t="s">
-        <v>8769</v>
+        <v>8761</v>
       </c>
     </row>
     <row r="4565" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4565" t="s">
-        <v>8770</v>
+        <v>8762</v>
       </c>
       <c r="B4565" t="s">
-        <v>8771</v>
+        <v>8763</v>
       </c>
     </row>
     <row r="4566" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4566" t="s">
-        <v>8772</v>
+        <v>8764</v>
       </c>
       <c r="B4566" t="s">
-        <v>8773</v>
+        <v>8765</v>
       </c>
     </row>
     <row r="4567" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4567" t="s">
-        <v>8774</v>
+        <v>8766</v>
       </c>
       <c r="B4567" t="s">
-        <v>8775</v>
+        <v>8767</v>
       </c>
     </row>
     <row r="4568" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4568" t="s">
-        <v>8776</v>
+        <v>8768</v>
       </c>
       <c r="B4568" t="s">
-        <v>8777</v>
+        <v>8769</v>
       </c>
     </row>
     <row r="4569" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4569" t="s">
-        <v>8778</v>
+        <v>8770</v>
       </c>
       <c r="B4569" t="s">
-        <v>8779</v>
+        <v>8771</v>
       </c>
     </row>
     <row r="4570" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4570" t="s">
-        <v>8785</v>
+        <v>8777</v>
       </c>
       <c r="B4570" t="s">
         <v>979</v>
@@ -63833,7 +63833,7 @@
     </row>
     <row r="4571" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4571" t="s">
-        <v>8786</v>
+        <v>8778</v>
       </c>
       <c r="B4571" t="s">
         <v>981</v>
@@ -63841,7 +63841,7 @@
     </row>
     <row r="4572" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4572" t="s">
-        <v>8787</v>
+        <v>8779</v>
       </c>
       <c r="B4572" t="s">
         <v>983</v>
@@ -63849,14 +63849,13 @@
     </row>
     <row r="4573" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4573" t="s">
-        <v>8785</v>
+        <v>8777</v>
       </c>
       <c r="B4573" t="s">
         <v>985</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B4573" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>